--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR213"/>
+  <dimension ref="A1:AR215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29611,6 +29611,282 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="C214" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="D214" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="E214" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="F214" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="G214" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="H214" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="I214" t="n">
+        <v>348.71</v>
+      </c>
+      <c r="J214" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="K214" t="n">
+        <v>323.36</v>
+      </c>
+      <c r="L214" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="M214" t="n">
+        <v>419.46</v>
+      </c>
+      <c r="N214" t="n">
+        <v>436.93</v>
+      </c>
+      <c r="O214" t="n">
+        <v>436.06</v>
+      </c>
+      <c r="P214" t="n">
+        <v>434.4</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>416.49</v>
+      </c>
+      <c r="R214" t="n">
+        <v>408.22</v>
+      </c>
+      <c r="S214" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="T214" t="n">
+        <v>394.87</v>
+      </c>
+      <c r="U214" t="n">
+        <v>390.93</v>
+      </c>
+      <c r="V214" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="W214" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="X214" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>403.13</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>408.29</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>397.34</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>376.49</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>404.73</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>415.55</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>420.43</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>414.73</v>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>364.14</v>
+      </c>
+      <c r="C215" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="D215" t="n">
+        <v>336.98</v>
+      </c>
+      <c r="E215" t="n">
+        <v>331.18</v>
+      </c>
+      <c r="F215" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="G215" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="H215" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="I215" t="n">
+        <v>348.4</v>
+      </c>
+      <c r="J215" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="K215" t="n">
+        <v>321.99</v>
+      </c>
+      <c r="L215" t="n">
+        <v>365.43</v>
+      </c>
+      <c r="M215" t="n">
+        <v>417.87</v>
+      </c>
+      <c r="N215" t="n">
+        <v>436.21</v>
+      </c>
+      <c r="O215" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="P215" t="n">
+        <v>434.56</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>416.14</v>
+      </c>
+      <c r="R215" t="n">
+        <v>408.39</v>
+      </c>
+      <c r="S215" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="T215" t="n">
+        <v>395.51</v>
+      </c>
+      <c r="U215" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="V215" t="n">
+        <v>388.34</v>
+      </c>
+      <c r="W215" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="X215" t="n">
+        <v>383.92</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>391.62</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>399.93</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>409.17</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>411.24</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>408.75</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>399.51</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>382.06</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>372.43</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>404.13</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>419.61</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>418.4</v>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29622,7 +29898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31785,6 +32061,26 @@
       </c>
       <c r="B216" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -31953,28 +32249,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04609303470994203</v>
+        <v>0.02333005100685901</v>
       </c>
       <c r="J2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00136775873298578</v>
+        <v>0.0003523868178001432</v>
       </c>
       <c r="M2" t="n">
-        <v>7.080864560799371</v>
+        <v>7.13122599159618</v>
       </c>
       <c r="N2" t="n">
-        <v>95.96884753215436</v>
+        <v>96.61440845852528</v>
       </c>
       <c r="O2" t="n">
-        <v>9.796369099424254</v>
+        <v>9.829262864453533</v>
       </c>
       <c r="P2" t="n">
-        <v>376.3216750271878</v>
+        <v>376.5333056177416</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32031,28 +32327,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4218548634677411</v>
+        <v>0.3943627974434177</v>
       </c>
       <c r="J3" t="n">
+        <v>214</v>
+      </c>
+      <c r="K3" t="n">
         <v>212</v>
       </c>
-      <c r="K3" t="n">
-        <v>210</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06640867456958877</v>
+        <v>0.05886413119306533</v>
       </c>
       <c r="M3" t="n">
-        <v>9.472154467975818</v>
+        <v>9.508564083999088</v>
       </c>
       <c r="N3" t="n">
-        <v>155.5035458289389</v>
+        <v>156.3032663357583</v>
       </c>
       <c r="O3" t="n">
-        <v>12.47010608731693</v>
+        <v>12.50213047187392</v>
       </c>
       <c r="P3" t="n">
-        <v>351.619614978093</v>
+        <v>351.874617031977</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32109,28 +32405,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09382662571492303</v>
+        <v>0.06499507398553726</v>
       </c>
       <c r="J4" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K4" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004355701487599783</v>
+        <v>0.002096956413537798</v>
       </c>
       <c r="M4" t="n">
-        <v>9.201580672818396</v>
+        <v>9.239925694816018</v>
       </c>
       <c r="N4" t="n">
-        <v>125.5051811801828</v>
+        <v>126.8055752852435</v>
       </c>
       <c r="O4" t="n">
-        <v>11.20290949620601</v>
+        <v>11.26079816377345</v>
       </c>
       <c r="P4" t="n">
-        <v>351.1512059503635</v>
+        <v>351.4177951480759</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32187,28 +32483,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3114621992918873</v>
+        <v>-0.3405319195413817</v>
       </c>
       <c r="J5" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K5" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03708438179147255</v>
+        <v>0.04421237182894144</v>
       </c>
       <c r="M5" t="n">
-        <v>10.57949263584884</v>
+        <v>10.59029233033825</v>
       </c>
       <c r="N5" t="n">
-        <v>156.1923070815726</v>
+        <v>157.2235163248523</v>
       </c>
       <c r="O5" t="n">
-        <v>12.49769207020131</v>
+        <v>12.53888018623881</v>
       </c>
       <c r="P5" t="n">
-        <v>355.9733806639213</v>
+        <v>356.2434221071056</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32265,28 +32561,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5800429325271842</v>
+        <v>-0.6085911514296448</v>
       </c>
       <c r="J6" t="n">
+        <v>214</v>
+      </c>
+      <c r="K6" t="n">
         <v>212</v>
       </c>
-      <c r="K6" t="n">
-        <v>210</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.09687338500175868</v>
+        <v>0.106409412891315</v>
       </c>
       <c r="M6" t="n">
-        <v>11.68802860543109</v>
+        <v>11.68369687363698</v>
       </c>
       <c r="N6" t="n">
-        <v>193.59238840188</v>
+        <v>194.1751617042243</v>
       </c>
       <c r="O6" t="n">
-        <v>13.9137481794763</v>
+        <v>13.93467479721806</v>
       </c>
       <c r="P6" t="n">
-        <v>361.9632986681327</v>
+        <v>362.2291099342718</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32343,28 +32639,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.53534347239041</v>
+        <v>-0.565708479872278</v>
       </c>
       <c r="J7" t="n">
+        <v>214</v>
+      </c>
+      <c r="K7" t="n">
         <v>212</v>
       </c>
-      <c r="K7" t="n">
-        <v>210</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.07605869381024577</v>
+        <v>0.08481634445782871</v>
       </c>
       <c r="M7" t="n">
-        <v>12.25620590331128</v>
+        <v>12.26849565579967</v>
       </c>
       <c r="N7" t="n">
-        <v>214.8742514261938</v>
+        <v>215.5747802520949</v>
       </c>
       <c r="O7" t="n">
-        <v>14.65858968066825</v>
+        <v>14.68246506047588</v>
       </c>
       <c r="P7" t="n">
-        <v>364.1755771459229</v>
+        <v>364.4582999745065</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32421,28 +32717,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01637400959342694</v>
+        <v>0.0003340668205440934</v>
       </c>
       <c r="J8" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003084576399186023</v>
+        <v>1.292972263700065e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>5.421556164116137</v>
+        <v>5.450444954295268</v>
       </c>
       <c r="N8" t="n">
-        <v>53.8115187665108</v>
+        <v>54.06963403778859</v>
       </c>
       <c r="O8" t="n">
-        <v>7.335633494560017</v>
+        <v>7.353205698046845</v>
       </c>
       <c r="P8" t="n">
-        <v>387.950534023094</v>
+        <v>388.0991594036655</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32503,28 +32799,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3283612629252166</v>
+        <v>-0.3402286806388532</v>
       </c>
       <c r="J9" t="n">
+        <v>214</v>
+      </c>
+      <c r="K9" t="n">
         <v>212</v>
       </c>
-      <c r="K9" t="n">
-        <v>210</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1038140211150149</v>
+        <v>0.1119684505952826</v>
       </c>
       <c r="M9" t="n">
-        <v>5.374397715464248</v>
+        <v>5.388242682437738</v>
       </c>
       <c r="N9" t="n">
-        <v>57.83260268775665</v>
+        <v>57.70420732722595</v>
       </c>
       <c r="O9" t="n">
-        <v>7.604774992579113</v>
+        <v>7.596328542607011</v>
       </c>
       <c r="P9" t="n">
-        <v>363.9494356668194</v>
+        <v>364.0590593595796</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32585,28 +32881,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3532158655893404</v>
+        <v>-0.356201674046045</v>
       </c>
       <c r="J10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04009095113463768</v>
+        <v>0.04156025389137774</v>
       </c>
       <c r="M10" t="n">
-        <v>10.56587190478026</v>
+        <v>10.48254413440459</v>
       </c>
       <c r="N10" t="n">
-        <v>184.9782438969576</v>
+        <v>183.2516821264085</v>
       </c>
       <c r="O10" t="n">
-        <v>13.60067071496688</v>
+        <v>13.53704850129483</v>
       </c>
       <c r="P10" t="n">
-        <v>333.1708092365526</v>
+        <v>333.1986000677755</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32667,28 +32963,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1335752629714539</v>
+        <v>-0.1628317202449782</v>
       </c>
       <c r="J11" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001108111291342695</v>
+        <v>0.001675642804577437</v>
       </c>
       <c r="M11" t="n">
-        <v>24.13222541191148</v>
+        <v>24.06443792143229</v>
       </c>
       <c r="N11" t="n">
-        <v>1017.597237572963</v>
+        <v>1010.253493961542</v>
       </c>
       <c r="O11" t="n">
-        <v>31.89979996133147</v>
+        <v>31.78448511399141</v>
       </c>
       <c r="P11" t="n">
-        <v>342.8118870822019</v>
+        <v>343.0829708078476</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -32749,28 +33045,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8569240038982204</v>
+        <v>0.809731458425924</v>
       </c>
       <c r="J12" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K12" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05501143389910301</v>
+        <v>0.04998478579115673</v>
       </c>
       <c r="M12" t="n">
-        <v>21.00517570330964</v>
+        <v>21.05814818793743</v>
       </c>
       <c r="N12" t="n">
-        <v>795.0197942414925</v>
+        <v>794.2258047608185</v>
       </c>
       <c r="O12" t="n">
-        <v>28.19609537225842</v>
+        <v>28.18201207793401</v>
       </c>
       <c r="P12" t="n">
-        <v>372.2589934136143</v>
+        <v>372.6930296627304</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -32831,28 +33127,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.582369942595395</v>
+        <v>1.558824135119241</v>
       </c>
       <c r="J13" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K13" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3077753108815118</v>
+        <v>0.3048567105568303</v>
       </c>
       <c r="M13" t="n">
-        <v>14.12901209872516</v>
+        <v>14.10609031848683</v>
       </c>
       <c r="N13" t="n">
-        <v>354.6267878625883</v>
+        <v>352.8873604818845</v>
       </c>
       <c r="O13" t="n">
-        <v>18.83153705523233</v>
+        <v>18.78529639057858</v>
       </c>
       <c r="P13" t="n">
-        <v>390.3822037744214</v>
+        <v>390.5985191771531</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -32913,28 +33209,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.666218619045839</v>
+        <v>1.646242946527087</v>
       </c>
       <c r="J14" t="n">
+        <v>214</v>
+      </c>
+      <c r="K14" t="n">
         <v>212</v>
       </c>
-      <c r="K14" t="n">
-        <v>210</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.4049101220228719</v>
+        <v>0.402989013282321</v>
       </c>
       <c r="M14" t="n">
-        <v>12.21338272631861</v>
+        <v>12.19114510086151</v>
       </c>
       <c r="N14" t="n">
-        <v>253.7731837485419</v>
+        <v>252.570549496519</v>
       </c>
       <c r="O14" t="n">
-        <v>15.93026000254051</v>
+        <v>15.89246832611344</v>
       </c>
       <c r="P14" t="n">
-        <v>404.1268089406278</v>
+        <v>404.3115863527188</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32991,28 +33287,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.889695406648624</v>
+        <v>1.868910353613108</v>
       </c>
       <c r="J15" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K15" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4891074340456985</v>
+        <v>0.4874073424262881</v>
       </c>
       <c r="M15" t="n">
-        <v>11.56774645351802</v>
+        <v>11.56002284744896</v>
       </c>
       <c r="N15" t="n">
-        <v>230.9955515494285</v>
+        <v>230.1088172378417</v>
       </c>
       <c r="O15" t="n">
-        <v>15.19853780958644</v>
+        <v>15.16933806195385</v>
       </c>
       <c r="P15" t="n">
-        <v>397.857503183768</v>
+        <v>398.0501019339849</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33069,28 +33365,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.886793847772434</v>
+        <v>1.864329235205987</v>
       </c>
       <c r="J16" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K16" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5084309728052465</v>
+        <v>0.5058508657988827</v>
       </c>
       <c r="M16" t="n">
-        <v>11.18017482317657</v>
+        <v>11.19123094735725</v>
       </c>
       <c r="N16" t="n">
-        <v>216.0539574241127</v>
+        <v>215.5144347852013</v>
       </c>
       <c r="O16" t="n">
-        <v>14.69877401092053</v>
+        <v>14.68040989840547</v>
       </c>
       <c r="P16" t="n">
-        <v>397.6571389158393</v>
+        <v>397.8646343595777</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33147,28 +33443,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.817023572545565</v>
+        <v>1.770520899238911</v>
       </c>
       <c r="J17" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K17" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4279391519663549</v>
+        <v>0.4145977795847852</v>
       </c>
       <c r="M17" t="n">
-        <v>13.73301972824274</v>
+        <v>13.82923540416726</v>
       </c>
       <c r="N17" t="n">
-        <v>278.3544142625364</v>
+        <v>282.2621988250788</v>
       </c>
       <c r="O17" t="n">
-        <v>16.68395679275562</v>
+        <v>16.80066066632735</v>
       </c>
       <c r="P17" t="n">
-        <v>395.065739905019</v>
+        <v>395.4942304073114</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33225,28 +33521,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.731011083415209</v>
+        <v>1.689347742050563</v>
       </c>
       <c r="J18" t="n">
+        <v>214</v>
+      </c>
+      <c r="K18" t="n">
         <v>212</v>
       </c>
-      <c r="K18" t="n">
-        <v>210</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3715251651067056</v>
+        <v>0.3612479570422574</v>
       </c>
       <c r="M18" t="n">
-        <v>14.19710502609737</v>
+        <v>14.26493291403233</v>
       </c>
       <c r="N18" t="n">
-        <v>315.3669519838912</v>
+        <v>317.5675812296464</v>
       </c>
       <c r="O18" t="n">
-        <v>17.75857404140015</v>
+        <v>17.82042595533694</v>
       </c>
       <c r="P18" t="n">
-        <v>386.5359721532873</v>
+        <v>386.9211282971442</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33303,28 +33599,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.338126759690325</v>
+        <v>1.297459048394598</v>
       </c>
       <c r="J19" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2756415955563809</v>
+        <v>0.2642380226332829</v>
       </c>
       <c r="M19" t="n">
-        <v>14.42168116626029</v>
+        <v>14.46318401686464</v>
       </c>
       <c r="N19" t="n">
-        <v>293.6983748550272</v>
+        <v>295.856830821217</v>
       </c>
       <c r="O19" t="n">
-        <v>17.13763037455958</v>
+        <v>17.20048926110002</v>
       </c>
       <c r="P19" t="n">
-        <v>386.4611609237846</v>
+        <v>386.8384777885892</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33381,28 +33677,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.93039118404476</v>
+        <v>0.899657993248679</v>
       </c>
       <c r="J20" t="n">
+        <v>214</v>
+      </c>
+      <c r="K20" t="n">
         <v>212</v>
       </c>
-      <c r="K20" t="n">
-        <v>210</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1417781228001087</v>
+        <v>0.1352212678219439</v>
       </c>
       <c r="M20" t="n">
-        <v>15.45542633931384</v>
+        <v>15.44215033159031</v>
       </c>
       <c r="N20" t="n">
-        <v>323.4039838545984</v>
+        <v>323.1459761431012</v>
       </c>
       <c r="O20" t="n">
-        <v>17.98343637502573</v>
+        <v>17.97626146180293</v>
       </c>
       <c r="P20" t="n">
-        <v>388.1735504634265</v>
+        <v>388.4597027997139</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33459,28 +33755,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3568626927880827</v>
+        <v>0.340064064356739</v>
       </c>
       <c r="J21" t="n">
+        <v>214</v>
+      </c>
+      <c r="K21" t="n">
         <v>212</v>
       </c>
-      <c r="K21" t="n">
-        <v>210</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02694264991576922</v>
+        <v>0.02496149367681044</v>
       </c>
       <c r="M21" t="n">
-        <v>13.76725316313447</v>
+        <v>13.69836510549769</v>
       </c>
       <c r="N21" t="n">
-        <v>281.5575774514953</v>
+        <v>279.7320630423761</v>
       </c>
       <c r="O21" t="n">
-        <v>16.77967751333426</v>
+        <v>16.72519246652714</v>
       </c>
       <c r="P21" t="n">
-        <v>391.8921529236111</v>
+        <v>392.0494647652192</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33537,28 +33833,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.05270122804101078</v>
+        <v>0.03969689690862808</v>
       </c>
       <c r="J22" t="n">
+        <v>214</v>
+      </c>
+      <c r="K22" t="n">
         <v>212</v>
       </c>
-      <c r="K22" t="n">
-        <v>210</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0006877476224621537</v>
+        <v>0.0003977798014465073</v>
       </c>
       <c r="M22" t="n">
-        <v>12.60269484023</v>
+        <v>12.53888251014947</v>
       </c>
       <c r="N22" t="n">
-        <v>247.0474519685487</v>
+        <v>245.2263719021948</v>
       </c>
       <c r="O22" t="n">
-        <v>15.71774322123086</v>
+        <v>15.65970535809007</v>
       </c>
       <c r="P22" t="n">
-        <v>393.0036745947151</v>
+        <v>393.1254489043208</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33615,28 +33911,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1159665618195017</v>
+        <v>-0.1272352247677281</v>
       </c>
       <c r="J23" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K23" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00429673337644676</v>
+        <v>0.005265248372495757</v>
       </c>
       <c r="M23" t="n">
-        <v>11.04217898818118</v>
+        <v>10.98965165106628</v>
       </c>
       <c r="N23" t="n">
-        <v>192.3524322443381</v>
+        <v>190.9421468153198</v>
       </c>
       <c r="O23" t="n">
-        <v>13.86911793317578</v>
+        <v>13.81818174780314</v>
       </c>
       <c r="P23" t="n">
-        <v>393.4785622202751</v>
+        <v>393.583292742193</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33693,28 +33989,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2074992092855181</v>
+        <v>-0.2157772605549372</v>
       </c>
       <c r="J24" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K24" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01443386691481752</v>
+        <v>0.01589481313029661</v>
       </c>
       <c r="M24" t="n">
-        <v>11.0066405991588</v>
+        <v>10.94299868044795</v>
       </c>
       <c r="N24" t="n">
-        <v>181.4581838837397</v>
+        <v>179.9683334954165</v>
       </c>
       <c r="O24" t="n">
-        <v>13.47064155427423</v>
+        <v>13.41522767214245</v>
       </c>
       <c r="P24" t="n">
-        <v>393.602131177485</v>
+        <v>393.6790692751603</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33771,28 +34067,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1368821400105505</v>
+        <v>-0.1352785704278995</v>
       </c>
       <c r="J25" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K25" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L25" t="n">
-        <v>0.007334081144017679</v>
+        <v>0.007312114898842426</v>
       </c>
       <c r="M25" t="n">
-        <v>10.36199151510634</v>
+        <v>10.28112610655618</v>
       </c>
       <c r="N25" t="n">
-        <v>156.5278307041693</v>
+        <v>155.1052062145096</v>
       </c>
       <c r="O25" t="n">
-        <v>12.51110829240037</v>
+        <v>12.45412406452214</v>
       </c>
       <c r="P25" t="n">
-        <v>392.4363221832207</v>
+        <v>392.4214009777571</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33849,28 +34145,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1902862754797813</v>
+        <v>-0.179079469521701</v>
       </c>
       <c r="J26" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K26" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0144456356342566</v>
+        <v>0.01304415325827357</v>
       </c>
       <c r="M26" t="n">
-        <v>10.28136540938133</v>
+        <v>10.22636119762579</v>
       </c>
       <c r="N26" t="n">
-        <v>152.4752848519509</v>
+        <v>151.48585424996</v>
       </c>
       <c r="O26" t="n">
-        <v>12.34808830758636</v>
+        <v>12.30795897986177</v>
       </c>
       <c r="P26" t="n">
-        <v>395.9306402720696</v>
+        <v>395.8264527841856</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33927,28 +34223,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09969360481339253</v>
+        <v>0.1167147806873338</v>
       </c>
       <c r="J27" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K27" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L27" t="n">
-        <v>0.004086060866089092</v>
+        <v>0.005672532493470661</v>
       </c>
       <c r="M27" t="n">
-        <v>9.991440274806726</v>
+        <v>9.969623452904283</v>
       </c>
       <c r="N27" t="n">
-        <v>149.9253239000962</v>
+        <v>149.4542763112129</v>
       </c>
       <c r="O27" t="n">
-        <v>12.24439969537487</v>
+        <v>12.22514933696979</v>
       </c>
       <c r="P27" t="n">
-        <v>393.8336357661624</v>
+        <v>393.6748987944358</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34005,28 +34301,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3436368233092483</v>
+        <v>0.3594379509664843</v>
       </c>
       <c r="J28" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K28" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04404907755400589</v>
+        <v>0.04872355830812503</v>
       </c>
       <c r="M28" t="n">
-        <v>10.07631200261793</v>
+        <v>10.05291548374827</v>
       </c>
       <c r="N28" t="n">
-        <v>158.9761735084643</v>
+        <v>158.2306981565412</v>
       </c>
       <c r="O28" t="n">
-        <v>12.60857539567672</v>
+        <v>12.57897842261212</v>
       </c>
       <c r="P28" t="n">
-        <v>391.7281818109619</v>
+        <v>391.5807955032782</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34083,28 +34379,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5844654764612216</v>
+        <v>0.6023320452583092</v>
       </c>
       <c r="J29" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K29" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1119908566272996</v>
+        <v>0.1196788923237634</v>
       </c>
       <c r="M29" t="n">
-        <v>10.5464279412779</v>
+        <v>10.53446919455799</v>
       </c>
       <c r="N29" t="n">
-        <v>168.8215503315564</v>
+        <v>168.1835907893879</v>
       </c>
       <c r="O29" t="n">
-        <v>12.99313473845155</v>
+        <v>12.96856163147586</v>
       </c>
       <c r="P29" t="n">
-        <v>381.8979020962741</v>
+        <v>381.7316429332078</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34161,28 +34457,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6238001790708678</v>
+        <v>0.6387208717677884</v>
       </c>
       <c r="J30" t="n">
+        <v>214</v>
+      </c>
+      <c r="K30" t="n">
         <v>212</v>
       </c>
-      <c r="K30" t="n">
-        <v>210</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.1177516748098599</v>
+        <v>0.124600006760557</v>
       </c>
       <c r="M30" t="n">
-        <v>10.91759954223026</v>
+        <v>10.88372314098166</v>
       </c>
       <c r="N30" t="n">
-        <v>179.740063424414</v>
+        <v>178.715346479641</v>
       </c>
       <c r="O30" t="n">
-        <v>13.40671710093168</v>
+        <v>13.36844592612174</v>
       </c>
       <c r="P30" t="n">
-        <v>373.5172160161242</v>
+        <v>373.3779259414291</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34239,28 +34535,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5457124657631273</v>
+        <v>0.5583432042325391</v>
       </c>
       <c r="J31" t="n">
+        <v>214</v>
+      </c>
+      <c r="K31" t="n">
         <v>212</v>
       </c>
-      <c r="K31" t="n">
-        <v>210</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.07890399416983707</v>
+        <v>0.08370032457017906</v>
       </c>
       <c r="M31" t="n">
-        <v>11.84897302085101</v>
+        <v>11.80014319058608</v>
       </c>
       <c r="N31" t="n">
-        <v>212.5648714063987</v>
+        <v>211.0564369157446</v>
       </c>
       <c r="O31" t="n">
-        <v>14.57960463820603</v>
+        <v>14.52778155520465</v>
       </c>
       <c r="P31" t="n">
-        <v>369.1083891336128</v>
+        <v>368.98962029923</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34317,28 +34613,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.431544051099129</v>
+        <v>0.4357121293745171</v>
       </c>
       <c r="J32" t="n">
+        <v>214</v>
+      </c>
+      <c r="K32" t="n">
         <v>212</v>
       </c>
-      <c r="K32" t="n">
-        <v>210</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.04195512379234256</v>
+        <v>0.04358652745253588</v>
       </c>
       <c r="M32" t="n">
-        <v>12.3950986950493</v>
+        <v>12.29614909415661</v>
       </c>
       <c r="N32" t="n">
-        <v>260.0213137916191</v>
+        <v>257.6193365225528</v>
       </c>
       <c r="O32" t="n">
-        <v>16.12517639567453</v>
+        <v>16.05052449369031</v>
       </c>
       <c r="P32" t="n">
-        <v>368.3344207766006</v>
+        <v>368.2952327960272</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34395,28 +34691,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3513076223670047</v>
+        <v>0.346739558018231</v>
       </c>
       <c r="J33" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K33" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04434986205873725</v>
+        <v>0.04411508037968215</v>
       </c>
       <c r="M33" t="n">
-        <v>10.11994020004817</v>
+        <v>10.04751027425045</v>
       </c>
       <c r="N33" t="n">
-        <v>162.9440962611722</v>
+        <v>161.4386213927959</v>
       </c>
       <c r="O33" t="n">
-        <v>12.76495578767009</v>
+        <v>12.70584988864562</v>
       </c>
       <c r="P33" t="n">
-        <v>369.9936828804194</v>
+        <v>370.0367032006201</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34473,28 +34769,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2773565891528157</v>
+        <v>0.2862821891739934</v>
       </c>
       <c r="J34" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K34" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01928774893231011</v>
+        <v>0.02091074988449881</v>
       </c>
       <c r="M34" t="n">
-        <v>12.34136583793934</v>
+        <v>12.26239292047158</v>
       </c>
       <c r="N34" t="n">
-        <v>241.1603829625291</v>
+        <v>239.3005584181491</v>
       </c>
       <c r="O34" t="n">
-        <v>15.52933942453861</v>
+        <v>15.46934253348051</v>
       </c>
       <c r="P34" t="n">
-        <v>365.9378313198892</v>
+        <v>365.8544467491568</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -34551,28 +34847,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06398643281151012</v>
+        <v>-0.06027200841795783</v>
       </c>
       <c r="J35" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K35" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0009677268720769128</v>
+        <v>0.0008766928046854972</v>
       </c>
       <c r="M35" t="n">
-        <v>12.7245106762765</v>
+        <v>12.62098156438442</v>
       </c>
       <c r="N35" t="n">
-        <v>260.5982222198338</v>
+        <v>258.1697493416515</v>
       </c>
       <c r="O35" t="n">
-        <v>16.14305492215875</v>
+        <v>16.06766160154151</v>
       </c>
       <c r="P35" t="n">
-        <v>371.7048902430566</v>
+        <v>371.6702033825337</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -34629,28 +34925,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1839773902524248</v>
+        <v>0.1820442737981032</v>
       </c>
       <c r="J36" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K36" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L36" t="n">
-        <v>0.007182210897414665</v>
+        <v>0.007179812339306868</v>
       </c>
       <c r="M36" t="n">
-        <v>12.74081361531667</v>
+        <v>12.6314125710958</v>
       </c>
       <c r="N36" t="n">
-        <v>287.1140988695744</v>
+        <v>284.4292279471686</v>
       </c>
       <c r="O36" t="n">
-        <v>16.94444153312745</v>
+        <v>16.86502973454742</v>
       </c>
       <c r="P36" t="n">
-        <v>370.1182466849293</v>
+        <v>370.1363332062928</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -34707,28 +35003,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2891529816435442</v>
+        <v>0.2845361686280236</v>
       </c>
       <c r="J37" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K37" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02300632609351516</v>
+        <v>0.02275117059771981</v>
       </c>
       <c r="M37" t="n">
-        <v>11.13721695273234</v>
+        <v>11.05700001083959</v>
       </c>
       <c r="N37" t="n">
-        <v>221.1819505066935</v>
+        <v>219.1284674512313</v>
       </c>
       <c r="O37" t="n">
-        <v>14.87218714603516</v>
+        <v>14.80298846352422</v>
       </c>
       <c r="P37" t="n">
-        <v>376.8086407890495</v>
+        <v>376.8513573347651</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -34785,28 +35081,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.03039720706314364</v>
+        <v>-0.03338591120272878</v>
       </c>
       <c r="J38" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K38" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0001711250328980674</v>
+        <v>0.0002107612716953922</v>
       </c>
       <c r="M38" t="n">
-        <v>13.58506026230372</v>
+        <v>13.4695808070411</v>
       </c>
       <c r="N38" t="n">
-        <v>332.6523812186057</v>
+        <v>329.5118576082284</v>
       </c>
       <c r="O38" t="n">
-        <v>18.23876040795004</v>
+        <v>18.15246147518921</v>
       </c>
       <c r="P38" t="n">
-        <v>377.924950579688</v>
+        <v>377.9529133722219</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -34863,28 +35159,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05357896897241152</v>
+        <v>0.05405674787874182</v>
       </c>
       <c r="J39" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K39" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0007376840833638321</v>
+        <v>0.0007668307334705027</v>
       </c>
       <c r="M39" t="n">
-        <v>12.06778141927916</v>
+        <v>11.95461479084533</v>
       </c>
       <c r="N39" t="n">
-        <v>240.060728561679</v>
+        <v>237.7534418472226</v>
       </c>
       <c r="O39" t="n">
-        <v>15.49389326675768</v>
+        <v>15.41925555424848</v>
       </c>
       <c r="P39" t="n">
-        <v>389.4828876335623</v>
+        <v>389.4784218464627</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -34941,28 +35237,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.006227343152909456</v>
+        <v>0.002758031579091355</v>
       </c>
       <c r="J40" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K40" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L40" t="n">
-        <v>9.873352631584176e-06</v>
+        <v>1.975752289773425e-06</v>
       </c>
       <c r="M40" t="n">
-        <v>12.08080363665038</v>
+        <v>12.00829937205672</v>
       </c>
       <c r="N40" t="n">
-        <v>244.1982134712624</v>
+        <v>242.0679112301641</v>
       </c>
       <c r="O40" t="n">
-        <v>15.62684272242037</v>
+        <v>15.55853178259967</v>
       </c>
       <c r="P40" t="n">
-        <v>399.5460224750317</v>
+        <v>399.4621815559846</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -35019,28 +35315,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.07781009196736648</v>
+        <v>0.09508815720771625</v>
       </c>
       <c r="J41" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K41" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L41" t="n">
-        <v>0.001434551811976492</v>
+        <v>0.002178684842472189</v>
       </c>
       <c r="M41" t="n">
-        <v>12.9359447531265</v>
+        <v>12.88321579947571</v>
       </c>
       <c r="N41" t="n">
-        <v>262.0221323433126</v>
+        <v>260.3654373671948</v>
       </c>
       <c r="O41" t="n">
-        <v>16.18709771216918</v>
+        <v>16.13584324933763</v>
       </c>
       <c r="P41" t="n">
-        <v>403.4737949109872</v>
+        <v>403.3125740661388</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -35097,28 +35393,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.299809102250739</v>
+        <v>0.3124164529831813</v>
       </c>
       <c r="J42" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K42" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L42" t="n">
-        <v>0.01862689777953719</v>
+        <v>0.02058690938817775</v>
       </c>
       <c r="M42" t="n">
-        <v>13.44895466008353</v>
+        <v>13.36814586469671</v>
       </c>
       <c r="N42" t="n">
-        <v>289.4789774549949</v>
+        <v>287.0859399701539</v>
       </c>
       <c r="O42" t="n">
-        <v>17.01408173998805</v>
+        <v>16.94361059426691</v>
       </c>
       <c r="P42" t="n">
-        <v>405.2091557525648</v>
+        <v>405.0897053299687</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -35175,28 +35471,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4091018663775874</v>
+        <v>0.4076677415309523</v>
       </c>
       <c r="J43" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K43" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L43" t="n">
-        <v>0.0339519138051716</v>
+        <v>0.03440884594217675</v>
       </c>
       <c r="M43" t="n">
-        <v>13.42001068477686</v>
+        <v>13.30725459953696</v>
       </c>
       <c r="N43" t="n">
-        <v>297.6767798299564</v>
+        <v>294.8113818521098</v>
       </c>
       <c r="O43" t="n">
-        <v>17.25331214086027</v>
+        <v>17.17007227276897</v>
       </c>
       <c r="P43" t="n">
-        <v>406.6055126916719</v>
+        <v>406.6188263551301</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -35234,7 +35530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR213"/>
+  <dimension ref="A1:AR215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81927,6 +82223,450 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-34.468068106583004,172.66436802718744</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-34.46763279943086,172.6651199606593</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-34.4671459614406,172.6658044032917</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-34.4666376043628,172.66646066461706</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-34.46609863808322,172.6670734796065</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-34.46555328519365,172.6676687508157</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-34.46473659677325,172.66794651701554</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-34.464410686974745,172.668817191722</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-34.46406152369074,172.6696601959081</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-34.46353221436343,172.67028879066277</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-34.462710566234136,172.67056944100244</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-34.46190953156264,172.670793120031</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-34.46133211975297,172.67104152068495</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-34.46071106829882,172.67131847069916</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-34.460019695839826,172.67164108935177</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>-34.459378390081014,172.67212998067774</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>-34.45870737339106,172.67252023185037</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>-34.45804131150619,172.67292695538808</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>-34.45735549219701,172.67326809052318</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>-34.456671115160596,172.67361403412193</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>-34.4559905529493,172.67397266458303</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>-34.45530271297666,172.67430714733604</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>-34.45460630125729,172.67461318561115</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>-34.45389438517545,172.67486775897436</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>-34.453176701558185,172.6751032002078</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>-34.45245429807527,172.67532298845822</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>-34.45176248065732,172.67556772574258</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>-34.45107784345213,172.6757908868275</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>-34.450373999551275,172.67605356517478</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>-34.44966127884659,172.67631430456086</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>-34.448945771812376,172.6765578400314</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>-34.44822804828745,172.67678769794063</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>-34.44750536314114,172.67698689017647</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>-34.4467814457709,172.67717849595707</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>-34.44605051238247,172.67732672280323</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>-34.44530948988171,172.6774125537968</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>-34.4445937716795,172.6776550165309</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>-34.44383833768099,172.67765174365186</t>
+        </is>
+      </c>
+      <c r="AN214" t="inlineStr">
+        <is>
+          <t>-34.44309737850377,172.6776770915634</t>
+        </is>
+      </c>
+      <c r="AO214" t="inlineStr">
+        <is>
+          <t>-34.44236217219655,172.67768093520232</t>
+        </is>
+      </c>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>-34.44162402029304,172.6777410558224</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>-34.44089564842599,172.6779157756255</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-34.468072629691584,172.6643739516181</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-34.46763182146693,172.6651186797017</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-34.46714822297093,172.66580736550202</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-34.46663846007302,172.6664617854512</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-34.46609919182612,172.6670741960582</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-34.46554748126665,172.66766159267092</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-34.46473402787244,172.6679434594977</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-34.46441267786047,172.66881956130473</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-34.464059404373245,172.66965767344388</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-34.46354101270787,172.67029926268967</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-34.462741392532735,172.67060613098906</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-34.46191871460758,172.6708064155926</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-34.461335062745086,172.6710485083694</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-34.46071310204354,172.67132522403458</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>-34.46001920281361,172.67163945219176</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>-34.4593794685646,172.67213356194304</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>-34.458706849560144,172.67251849239076</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>-34.458040078972815,172.67292286256995</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>-34.457353520156026,172.673261542062</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>-34.45666578452097,172.67359633294208</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>-34.45598257244971,172.67394616416365</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>-34.45529627315412,172.67428576298443</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>-34.45460312758241,172.67460264699073</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>-34.45388286138787,172.67482949283442</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>-34.453160710044266,172.67505009869595</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>-34.45243568758178,172.67526119067418</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>-34.45175478888678,172.67553698224066</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>-34.451072855792894,172.67576334144107</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>-34.450370252836514,172.67603037892462</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>-34.449655287615535,172.67627722823107</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>-34.44894575454676,172.67655773318407</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>-34.448227374934156,172.6767835309282</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>-34.447489858825044,172.67689094285984</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>-34.4467803925919,172.67717197843095</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>-34.44605065050365,172.67732757755346</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>-34.44530952441195,172.67741276748248</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>-34.44459254586697,172.6776474307509</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>-34.443838959221466,172.67765558992792</t>
+        </is>
+      </c>
+      <c r="AN215" t="inlineStr">
+        <is>
+          <t>-34.44309827108332,172.67768353329964</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>-34.442362952278735,172.6776879476871</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>-34.4416249654305,172.677749908452</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>-34.44089141839646,172.67787615504892</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR215"/>
+  <dimension ref="A1:AR217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29648,7 +29648,7 @@
         <v>323.36</v>
       </c>
       <c r="L214" t="n">
-        <v>370.23</v>
+        <v>378.37</v>
       </c>
       <c r="M214" t="n">
         <v>419.46</v>
@@ -29786,7 +29786,7 @@
         <v>321.99</v>
       </c>
       <c r="L215" t="n">
-        <v>365.43</v>
+        <v>376.16</v>
       </c>
       <c r="M215" t="n">
         <v>417.87</v>
@@ -29855,16 +29855,16 @@
         <v>382.78</v>
       </c>
       <c r="AI215" t="n">
-        <v>372.43</v>
+        <v>380.76</v>
       </c>
       <c r="AJ215" t="n">
-        <v>373.82</v>
+        <v>382.63</v>
       </c>
       <c r="AK215" t="n">
         <v>381.8</v>
       </c>
       <c r="AL215" t="n">
-        <v>375.79</v>
+        <v>386.78</v>
       </c>
       <c r="AM215" t="n">
         <v>390.98</v>
@@ -29884,6 +29884,282 @@
       <c r="AR215" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="C216" t="n">
+        <v>347.21</v>
+      </c>
+      <c r="D216" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="E216" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="F216" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="G216" t="n">
+        <v>334.18</v>
+      </c>
+      <c r="H216" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="I216" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="J216" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="K216" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="L216" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="M216" t="n">
+        <v>414.83</v>
+      </c>
+      <c r="N216" t="n">
+        <v>438.46</v>
+      </c>
+      <c r="O216" t="n">
+        <v>439.92</v>
+      </c>
+      <c r="P216" t="n">
+        <v>432.29</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>411.61</v>
+      </c>
+      <c r="R216" t="n">
+        <v>404.78</v>
+      </c>
+      <c r="S216" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="T216" t="n">
+        <v>392.49</v>
+      </c>
+      <c r="U216" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="V216" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="W216" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="X216" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>401.28</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>410.76</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>412.49</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>408.47</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>398.81</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>386.37</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>381.69</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>386.01</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>390.97</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>395.72</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>409.89</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>420.34</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>422.81</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>423.83</v>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="C217" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="D217" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="E217" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="F217" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="G217" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="H217" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="I217" t="n">
+        <v>352.52</v>
+      </c>
+      <c r="J217" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="K217" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="L217" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="M217" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="N217" t="n">
+        <v>442.62</v>
+      </c>
+      <c r="O217" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="P217" t="n">
+        <v>435.61</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>410.23</v>
+      </c>
+      <c r="R217" t="n">
+        <v>404.99</v>
+      </c>
+      <c r="S217" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="T217" t="n">
+        <v>393.57</v>
+      </c>
+      <c r="U217" t="n">
+        <v>390.56</v>
+      </c>
+      <c r="V217" t="n">
+        <v>388</v>
+      </c>
+      <c r="W217" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="X217" t="n">
+        <v>385.99</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>393.59</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>403.42</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>412.41</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>414.08</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>409.49</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>394.82</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>389.86</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>388.58</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>394.23</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>398.82</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>412.73</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>423.36</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>423.62</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>425.23</v>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29898,7 +30174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B218"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32081,6 +32357,26 @@
       </c>
       <c r="B218" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -32249,28 +32545,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02333005100685901</v>
+        <v>0.01240362837996219</v>
       </c>
       <c r="J2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K2" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003523868178001432</v>
+        <v>0.0001012648449776332</v>
       </c>
       <c r="M2" t="n">
-        <v>7.13122599159618</v>
+        <v>7.120744077230234</v>
       </c>
       <c r="N2" t="n">
-        <v>96.61440845852528</v>
+        <v>96.09195083202037</v>
       </c>
       <c r="O2" t="n">
-        <v>9.829262864453533</v>
+        <v>9.80265019431074</v>
       </c>
       <c r="P2" t="n">
-        <v>376.5333056177416</v>
+        <v>376.6352108364366</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32327,28 +32623,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3943627974434177</v>
+        <v>0.3705424653177649</v>
       </c>
       <c r="J3" t="n">
+        <v>216</v>
+      </c>
+      <c r="K3" t="n">
         <v>214</v>
       </c>
-      <c r="K3" t="n">
-        <v>212</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05886413119306533</v>
+        <v>0.05276350570758548</v>
       </c>
       <c r="M3" t="n">
-        <v>9.508564083999088</v>
+        <v>9.528793539249508</v>
       </c>
       <c r="N3" t="n">
-        <v>156.3032663357583</v>
+        <v>156.6235513710273</v>
       </c>
       <c r="O3" t="n">
-        <v>12.50213047187392</v>
+        <v>12.51493313490037</v>
       </c>
       <c r="P3" t="n">
-        <v>351.874617031977</v>
+        <v>352.0962749049917</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32405,28 +32701,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06499507398553726</v>
+        <v>0.03796964664273887</v>
       </c>
       <c r="J4" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K4" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002096956413537798</v>
+        <v>0.0007182565646711714</v>
       </c>
       <c r="M4" t="n">
-        <v>9.239925694816018</v>
+        <v>9.274082804750787</v>
       </c>
       <c r="N4" t="n">
-        <v>126.8055752852435</v>
+        <v>127.8974473017761</v>
       </c>
       <c r="O4" t="n">
-        <v>11.26079816377345</v>
+        <v>11.30917535905143</v>
       </c>
       <c r="P4" t="n">
-        <v>351.4177951480759</v>
+        <v>351.6684942627087</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32483,28 +32779,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3405319195413817</v>
+        <v>-0.3672387212709285</v>
       </c>
       <c r="J5" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K5" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04421237182894144</v>
+        <v>0.05135308592829468</v>
       </c>
       <c r="M5" t="n">
-        <v>10.59029233033825</v>
+        <v>10.59372277932045</v>
       </c>
       <c r="N5" t="n">
-        <v>157.2235163248523</v>
+        <v>157.9566232290283</v>
       </c>
       <c r="O5" t="n">
-        <v>12.53888018623881</v>
+        <v>12.56807953623099</v>
       </c>
       <c r="P5" t="n">
-        <v>356.2434221071056</v>
+        <v>356.4923151259525</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32561,28 +32857,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6085911514296448</v>
+        <v>-0.6335323363686934</v>
       </c>
       <c r="J6" t="n">
+        <v>216</v>
+      </c>
+      <c r="K6" t="n">
         <v>214</v>
       </c>
-      <c r="K6" t="n">
-        <v>212</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.106409412891315</v>
+        <v>0.1153463902183073</v>
       </c>
       <c r="M6" t="n">
-        <v>11.68369687363698</v>
+        <v>11.66555672574585</v>
       </c>
       <c r="N6" t="n">
-        <v>194.1751617042243</v>
+        <v>194.2838965510843</v>
       </c>
       <c r="O6" t="n">
-        <v>13.93467479721806</v>
+        <v>13.93857584371819</v>
       </c>
       <c r="P6" t="n">
-        <v>362.2291099342718</v>
+        <v>362.4620770287306</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32639,28 +32935,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.565708479872278</v>
+        <v>-0.5902771140214429</v>
       </c>
       <c r="J7" t="n">
+        <v>216</v>
+      </c>
+      <c r="K7" t="n">
         <v>214</v>
       </c>
-      <c r="K7" t="n">
-        <v>212</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.08481634445782871</v>
+        <v>0.09262515522700876</v>
       </c>
       <c r="M7" t="n">
-        <v>12.26849565579967</v>
+        <v>12.25682112756203</v>
       </c>
       <c r="N7" t="n">
-        <v>215.5747802520949</v>
+        <v>215.4267661589029</v>
       </c>
       <c r="O7" t="n">
-        <v>14.68246506047588</v>
+        <v>14.6774236894253</v>
       </c>
       <c r="P7" t="n">
-        <v>364.4582999745065</v>
+        <v>364.6877870744409</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32717,28 +33013,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003340668205440934</v>
+        <v>0.001324179550436292</v>
       </c>
       <c r="J8" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K8" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L8" t="n">
-        <v>1.292972263700065e-07</v>
+        <v>2.07308487631952e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>5.450444954295268</v>
+        <v>5.405095727548546</v>
       </c>
       <c r="N8" t="n">
-        <v>54.06963403778859</v>
+        <v>53.5696848552063</v>
       </c>
       <c r="O8" t="n">
-        <v>7.353205698046845</v>
+        <v>7.319131427649479</v>
       </c>
       <c r="P8" t="n">
-        <v>388.0991594036655</v>
+        <v>388.0899553109704</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32799,28 +33095,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3402286806388532</v>
+        <v>-0.3456187501977913</v>
       </c>
       <c r="J9" t="n">
+        <v>216</v>
+      </c>
+      <c r="K9" t="n">
         <v>214</v>
       </c>
-      <c r="K9" t="n">
-        <v>212</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1119684505952826</v>
+        <v>0.1170614963655928</v>
       </c>
       <c r="M9" t="n">
-        <v>5.388242682437738</v>
+        <v>5.367003083685328</v>
       </c>
       <c r="N9" t="n">
-        <v>57.70420732722595</v>
+        <v>57.25762411585856</v>
       </c>
       <c r="O9" t="n">
-        <v>7.596328542607011</v>
+        <v>7.566876774195451</v>
       </c>
       <c r="P9" t="n">
-        <v>364.0590593595796</v>
+        <v>364.1090050671079</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32881,28 +33177,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.356201674046045</v>
+        <v>-0.3587099173056759</v>
       </c>
       <c r="J10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04156025389137774</v>
+        <v>0.04294341200244745</v>
       </c>
       <c r="M10" t="n">
-        <v>10.48254413440459</v>
+        <v>10.39804030995147</v>
       </c>
       <c r="N10" t="n">
-        <v>183.2516821264085</v>
+        <v>181.5504736485398</v>
       </c>
       <c r="O10" t="n">
-        <v>13.53704850129483</v>
+        <v>13.47406670788518</v>
       </c>
       <c r="P10" t="n">
-        <v>333.1986000677755</v>
+        <v>333.2220231644368</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32963,28 +33259,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1628317202449782</v>
+        <v>-0.1849956445259629</v>
       </c>
       <c r="J11" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001675642804577437</v>
+        <v>0.002202001026233469</v>
       </c>
       <c r="M11" t="n">
-        <v>24.06443792143229</v>
+        <v>23.95678451613943</v>
       </c>
       <c r="N11" t="n">
-        <v>1010.253493961542</v>
+        <v>1002.013769674273</v>
       </c>
       <c r="O11" t="n">
-        <v>31.78448511399141</v>
+        <v>31.65460108221668</v>
       </c>
       <c r="P11" t="n">
-        <v>343.0829708078476</v>
+        <v>343.2890345913922</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33045,28 +33341,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.809731458425924</v>
+        <v>0.7963104107404319</v>
       </c>
       <c r="J12" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K12" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04998478579115673</v>
+        <v>0.04942489739020273</v>
       </c>
       <c r="M12" t="n">
-        <v>21.05814818793743</v>
+        <v>20.92987548278527</v>
       </c>
       <c r="N12" t="n">
-        <v>794.2258047608185</v>
+        <v>785.6180247329175</v>
       </c>
       <c r="O12" t="n">
-        <v>28.18201207793401</v>
+        <v>28.02887840661694</v>
       </c>
       <c r="P12" t="n">
-        <v>372.6930296627304</v>
+        <v>372.8173656876205</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33127,28 +33423,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.558824135119241</v>
+        <v>1.533097217165328</v>
       </c>
       <c r="J13" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K13" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3048567105568303</v>
+        <v>0.3008697091281007</v>
       </c>
       <c r="M13" t="n">
-        <v>14.10609031848683</v>
+        <v>14.09751227688848</v>
       </c>
       <c r="N13" t="n">
-        <v>352.8873604818845</v>
+        <v>351.6297689083966</v>
       </c>
       <c r="O13" t="n">
-        <v>18.78529639057858</v>
+        <v>18.75179375175603</v>
       </c>
       <c r="P13" t="n">
-        <v>390.5985191771531</v>
+        <v>390.835632891014</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33209,28 +33505,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.646242946527087</v>
+        <v>1.633929501423476</v>
       </c>
       <c r="J14" t="n">
+        <v>216</v>
+      </c>
+      <c r="K14" t="n">
         <v>214</v>
       </c>
-      <c r="K14" t="n">
-        <v>212</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.402989013282321</v>
+        <v>0.4037680438123697</v>
       </c>
       <c r="M14" t="n">
-        <v>12.19114510086151</v>
+        <v>12.13534537451278</v>
       </c>
       <c r="N14" t="n">
-        <v>252.570549496519</v>
+        <v>250.7205454788302</v>
       </c>
       <c r="O14" t="n">
-        <v>15.89246832611344</v>
+        <v>15.83415755507157</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3115863527188</v>
+        <v>404.4258379828096</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33287,28 +33583,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.868910353613108</v>
+        <v>1.859635769093905</v>
       </c>
       <c r="J15" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K15" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4874073424262881</v>
+        <v>0.4896678458070549</v>
       </c>
       <c r="M15" t="n">
-        <v>11.56002284744896</v>
+        <v>11.49947586264513</v>
       </c>
       <c r="N15" t="n">
-        <v>230.1088172378417</v>
+        <v>228.2708465345835</v>
       </c>
       <c r="O15" t="n">
-        <v>15.16933806195385</v>
+        <v>15.10863483358385</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0501019339849</v>
+        <v>398.136301066766</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33365,28 +33661,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.864329235205987</v>
+        <v>1.841938670573422</v>
       </c>
       <c r="J16" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K16" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5058508657988827</v>
+        <v>0.5029799818601473</v>
       </c>
       <c r="M16" t="n">
-        <v>11.19123094735725</v>
+        <v>11.20397676541404</v>
       </c>
       <c r="N16" t="n">
-        <v>215.5144347852013</v>
+        <v>215.0760871945349</v>
       </c>
       <c r="O16" t="n">
-        <v>14.68040989840547</v>
+        <v>14.6654726209057</v>
       </c>
       <c r="P16" t="n">
-        <v>397.8646343595777</v>
+        <v>398.0721200366881</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33443,28 +33739,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.770520899238911</v>
+        <v>1.717062846721484</v>
       </c>
       <c r="J17" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K17" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4145977795847852</v>
+        <v>0.3969886338207548</v>
       </c>
       <c r="M17" t="n">
-        <v>13.82923540416726</v>
+        <v>13.97167620496639</v>
       </c>
       <c r="N17" t="n">
-        <v>282.2621988250788</v>
+        <v>288.62749128866</v>
       </c>
       <c r="O17" t="n">
-        <v>16.80066066632735</v>
+        <v>16.98904032865482</v>
       </c>
       <c r="P17" t="n">
-        <v>395.4942304073114</v>
+        <v>395.9884672921058</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33521,28 +33817,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.689347742050563</v>
+        <v>1.643841199738912</v>
       </c>
       <c r="J18" t="n">
+        <v>216</v>
+      </c>
+      <c r="K18" t="n">
         <v>214</v>
       </c>
-      <c r="K18" t="n">
-        <v>212</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.3612479570422574</v>
+        <v>0.348765006935751</v>
       </c>
       <c r="M18" t="n">
-        <v>14.26493291403233</v>
+        <v>14.36299101839025</v>
       </c>
       <c r="N18" t="n">
-        <v>317.5675812296464</v>
+        <v>321.0228927690465</v>
       </c>
       <c r="O18" t="n">
-        <v>17.82042595533694</v>
+        <v>17.91711173066258</v>
       </c>
       <c r="P18" t="n">
-        <v>386.9211282971442</v>
+        <v>387.3431827584646</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33599,28 +33895,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.297459048394598</v>
+        <v>1.257763036601828</v>
       </c>
       <c r="J19" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K19" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2642380226332829</v>
+        <v>0.2530021841803309</v>
       </c>
       <c r="M19" t="n">
-        <v>14.46318401686464</v>
+        <v>14.50967395055433</v>
       </c>
       <c r="N19" t="n">
-        <v>295.856830821217</v>
+        <v>297.979520826464</v>
       </c>
       <c r="O19" t="n">
-        <v>17.20048926110002</v>
+        <v>17.26208332810568</v>
       </c>
       <c r="P19" t="n">
-        <v>386.8384777885892</v>
+        <v>387.2079935819098</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33677,28 +33973,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.899657993248679</v>
+        <v>0.8667461859668778</v>
       </c>
       <c r="J20" t="n">
+        <v>216</v>
+      </c>
+      <c r="K20" t="n">
         <v>214</v>
       </c>
-      <c r="K20" t="n">
-        <v>212</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.1352212678219439</v>
+        <v>0.1278460360248599</v>
       </c>
       <c r="M20" t="n">
-        <v>15.44215033159031</v>
+        <v>15.44002073742159</v>
       </c>
       <c r="N20" t="n">
-        <v>323.1459761431012</v>
+        <v>323.4593846165854</v>
       </c>
       <c r="O20" t="n">
-        <v>17.97626146180293</v>
+        <v>17.98497663653154</v>
       </c>
       <c r="P20" t="n">
-        <v>388.4597027997139</v>
+        <v>388.7671283821198</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33755,28 +34051,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.340064064356739</v>
+        <v>0.3217201416472201</v>
       </c>
       <c r="J21" t="n">
+        <v>216</v>
+      </c>
+      <c r="K21" t="n">
         <v>214</v>
       </c>
-      <c r="K21" t="n">
-        <v>212</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.02496149367681044</v>
+        <v>0.02276917612584051</v>
       </c>
       <c r="M21" t="n">
-        <v>13.69836510549769</v>
+        <v>13.63581318749537</v>
       </c>
       <c r="N21" t="n">
-        <v>279.7320630423761</v>
+        <v>278.1396436749131</v>
       </c>
       <c r="O21" t="n">
-        <v>16.72519246652714</v>
+        <v>16.67751911031473</v>
       </c>
       <c r="P21" t="n">
-        <v>392.0494647652192</v>
+        <v>392.2218040540515</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33833,28 +34129,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03969689690862808</v>
+        <v>0.02718332951224336</v>
       </c>
       <c r="J22" t="n">
+        <v>216</v>
+      </c>
+      <c r="K22" t="n">
         <v>214</v>
       </c>
-      <c r="K22" t="n">
-        <v>212</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0003977798014465073</v>
+        <v>0.0001900297482486657</v>
       </c>
       <c r="M22" t="n">
-        <v>12.53888251014947</v>
+        <v>12.4738695200741</v>
       </c>
       <c r="N22" t="n">
-        <v>245.2263719021948</v>
+        <v>243.4208196197273</v>
       </c>
       <c r="O22" t="n">
-        <v>15.65970535809007</v>
+        <v>15.60194922500799</v>
       </c>
       <c r="P22" t="n">
-        <v>393.1254489043208</v>
+        <v>393.2430040132911</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33911,28 +34207,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1272352247677281</v>
+        <v>-0.1370351481266369</v>
       </c>
       <c r="J23" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K23" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005265248372495757</v>
+        <v>0.006216279946883119</v>
       </c>
       <c r="M23" t="n">
-        <v>10.98965165106628</v>
+        <v>10.93161350634638</v>
       </c>
       <c r="N23" t="n">
-        <v>190.9421468153198</v>
+        <v>189.4831290497427</v>
       </c>
       <c r="O23" t="n">
-        <v>13.81818174780314</v>
+        <v>13.76528710378911</v>
       </c>
       <c r="P23" t="n">
-        <v>393.583292742193</v>
+        <v>393.6746641621659</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33989,28 +34285,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2157772605549372</v>
+        <v>-0.2207659236443664</v>
       </c>
       <c r="J24" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K24" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01589481313029661</v>
+        <v>0.01695200693644938</v>
       </c>
       <c r="M24" t="n">
-        <v>10.94299868044795</v>
+        <v>10.86495224830108</v>
       </c>
       <c r="N24" t="n">
-        <v>179.9683334954165</v>
+        <v>178.3869022999546</v>
       </c>
       <c r="O24" t="n">
-        <v>13.41522767214245</v>
+        <v>13.35615597018673</v>
       </c>
       <c r="P24" t="n">
-        <v>393.6790692751603</v>
+        <v>393.7255789928912</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34067,28 +34363,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1352785704278995</v>
+        <v>-0.128647314413747</v>
       </c>
       <c r="J25" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K25" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L25" t="n">
-        <v>0.007312114898842426</v>
+        <v>0.006745566199959585</v>
       </c>
       <c r="M25" t="n">
-        <v>10.28112610655618</v>
+        <v>10.21476474792421</v>
       </c>
       <c r="N25" t="n">
-        <v>155.1052062145096</v>
+        <v>153.8115114598972</v>
       </c>
       <c r="O25" t="n">
-        <v>12.45412406452214</v>
+        <v>12.40207690106368</v>
       </c>
       <c r="P25" t="n">
-        <v>392.4214009777571</v>
+        <v>392.3595590026312</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34145,28 +34441,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.179079469521701</v>
+        <v>-0.159885837363656</v>
       </c>
       <c r="J26" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K26" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01304415325827357</v>
+        <v>0.01055636568714313</v>
       </c>
       <c r="M26" t="n">
-        <v>10.22636119762579</v>
+        <v>10.20174648439223</v>
       </c>
       <c r="N26" t="n">
-        <v>151.48585424996</v>
+        <v>151.2313786236326</v>
       </c>
       <c r="O26" t="n">
-        <v>12.30795897986177</v>
+        <v>12.29761678633843</v>
       </c>
       <c r="P26" t="n">
-        <v>395.8264527841856</v>
+        <v>395.6474683394094</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34223,28 +34519,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1167147806873338</v>
+        <v>0.1421346751333362</v>
       </c>
       <c r="J27" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K27" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005672532493470661</v>
+        <v>0.008445399689546274</v>
       </c>
       <c r="M27" t="n">
-        <v>9.969623452904283</v>
+        <v>9.987471383277187</v>
       </c>
       <c r="N27" t="n">
-        <v>149.4542763112129</v>
+        <v>150.0618834794127</v>
       </c>
       <c r="O27" t="n">
-        <v>12.22514933696979</v>
+        <v>12.24997483586855</v>
       </c>
       <c r="P27" t="n">
-        <v>393.6748987944358</v>
+        <v>393.4370961431143</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34301,28 +34597,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3594379509664843</v>
+        <v>0.3803866289776486</v>
       </c>
       <c r="J28" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K28" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04872355830812503</v>
+        <v>0.05484020977346515</v>
       </c>
       <c r="M28" t="n">
-        <v>10.05291548374827</v>
+        <v>10.05569346163885</v>
       </c>
       <c r="N28" t="n">
-        <v>158.2306981565412</v>
+        <v>158.1112287093149</v>
       </c>
       <c r="O28" t="n">
-        <v>12.57897842261212</v>
+        <v>12.57422875206726</v>
       </c>
       <c r="P28" t="n">
-        <v>391.5807955032782</v>
+        <v>391.3847636177511</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34379,28 +34675,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6023320452583092</v>
+        <v>0.6217888006881751</v>
       </c>
       <c r="J29" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K29" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1196788923237634</v>
+        <v>0.1279866229824972</v>
       </c>
       <c r="M29" t="n">
-        <v>10.53446919455799</v>
+        <v>10.53093067282472</v>
       </c>
       <c r="N29" t="n">
-        <v>168.1835907893879</v>
+        <v>167.778017704122</v>
       </c>
       <c r="O29" t="n">
-        <v>12.96856163147586</v>
+        <v>12.95291541330067</v>
       </c>
       <c r="P29" t="n">
-        <v>381.7316429332078</v>
+        <v>381.549994702804</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34457,28 +34753,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6387208717677884</v>
+        <v>0.6541172683973703</v>
       </c>
       <c r="J30" t="n">
+        <v>216</v>
+      </c>
+      <c r="K30" t="n">
         <v>214</v>
       </c>
-      <c r="K30" t="n">
-        <v>212</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.124600006760557</v>
+        <v>0.1317207850056417</v>
       </c>
       <c r="M30" t="n">
-        <v>10.88372314098166</v>
+        <v>10.85220862181184</v>
       </c>
       <c r="N30" t="n">
-        <v>178.715346479641</v>
+        <v>177.7774586371775</v>
       </c>
       <c r="O30" t="n">
-        <v>13.36844592612174</v>
+        <v>13.33332136555545</v>
       </c>
       <c r="P30" t="n">
-        <v>373.3779259414291</v>
+        <v>373.2337362954112</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34535,28 +34831,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5583432042325391</v>
+        <v>0.5763314078380726</v>
       </c>
       <c r="J31" t="n">
+        <v>216</v>
+      </c>
+      <c r="K31" t="n">
         <v>214</v>
       </c>
-      <c r="K31" t="n">
-        <v>212</v>
-      </c>
       <c r="L31" t="n">
-        <v>0.08370032457017906</v>
+        <v>0.08995612687844068</v>
       </c>
       <c r="M31" t="n">
-        <v>11.80014319058608</v>
+        <v>11.77867309178652</v>
       </c>
       <c r="N31" t="n">
-        <v>211.0564369157446</v>
+        <v>210.076778766158</v>
       </c>
       <c r="O31" t="n">
-        <v>14.52778155520465</v>
+        <v>14.4940256232062</v>
       </c>
       <c r="P31" t="n">
-        <v>368.98962029923</v>
+        <v>368.819947480048</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34613,28 +34909,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4357121293745171</v>
+        <v>0.4500551304122239</v>
       </c>
       <c r="J32" t="n">
+        <v>216</v>
+      </c>
+      <c r="K32" t="n">
         <v>214</v>
       </c>
-      <c r="K32" t="n">
-        <v>212</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.04358652745253588</v>
+        <v>0.04715616256016653</v>
       </c>
       <c r="M32" t="n">
-        <v>12.29614909415661</v>
+        <v>12.24266917820335</v>
       </c>
       <c r="N32" t="n">
-        <v>257.6193365225528</v>
+        <v>255.8683682258878</v>
       </c>
       <c r="O32" t="n">
-        <v>16.05052449369031</v>
+        <v>15.99588597814725</v>
       </c>
       <c r="P32" t="n">
-        <v>368.2952327960272</v>
+        <v>368.159932381277</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34691,28 +34987,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.346739558018231</v>
+        <v>0.3540649288051649</v>
       </c>
       <c r="J33" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K33" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04411508037968215</v>
+        <v>0.04676176404402699</v>
       </c>
       <c r="M33" t="n">
-        <v>10.04751027425045</v>
+        <v>9.99015488448298</v>
       </c>
       <c r="N33" t="n">
-        <v>161.4386213927959</v>
+        <v>160.0910804260856</v>
       </c>
       <c r="O33" t="n">
-        <v>12.70584988864562</v>
+        <v>12.6527103984121</v>
       </c>
       <c r="P33" t="n">
-        <v>370.0367032006201</v>
+        <v>369.9674738608687</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34769,28 +35065,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2862821891739934</v>
+        <v>0.3110185902816979</v>
       </c>
       <c r="J34" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K34" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02091074988449881</v>
+        <v>0.02488587033733014</v>
       </c>
       <c r="M34" t="n">
-        <v>12.26239292047158</v>
+        <v>12.25303920124428</v>
       </c>
       <c r="N34" t="n">
-        <v>239.3005584181491</v>
+        <v>238.9447322026597</v>
       </c>
       <c r="O34" t="n">
-        <v>15.46934253348051</v>
+        <v>15.45783724208079</v>
       </c>
       <c r="P34" t="n">
-        <v>365.8544467491568</v>
+        <v>365.6227083052539</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -34847,28 +35143,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.06027200841795783</v>
+        <v>-0.02550695889065689</v>
       </c>
       <c r="J35" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K35" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0008766928046854972</v>
+        <v>0.0001585821371736795</v>
       </c>
       <c r="M35" t="n">
-        <v>12.62098156438442</v>
+        <v>12.66461066315124</v>
       </c>
       <c r="N35" t="n">
-        <v>258.1697493416515</v>
+        <v>258.5927644821709</v>
       </c>
       <c r="O35" t="n">
-        <v>16.06766160154151</v>
+        <v>16.08081977021603</v>
       </c>
       <c r="P35" t="n">
-        <v>371.6702033825337</v>
+        <v>371.3446950548084</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -34925,28 +35221,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1820442737981032</v>
+        <v>0.2107755073942963</v>
       </c>
       <c r="J36" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K36" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L36" t="n">
-        <v>0.007179812339306868</v>
+        <v>0.009740208590925059</v>
       </c>
       <c r="M36" t="n">
-        <v>12.6314125710958</v>
+        <v>12.65189315609476</v>
       </c>
       <c r="N36" t="n">
-        <v>284.4292279471686</v>
+        <v>283.4134663721576</v>
       </c>
       <c r="O36" t="n">
-        <v>16.86502973454742</v>
+        <v>16.83488836827134</v>
       </c>
       <c r="P36" t="n">
-        <v>370.1363332062928</v>
+        <v>369.8668443488318</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35003,28 +35299,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2845361686280236</v>
+        <v>0.29011349377726</v>
       </c>
       <c r="J37" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K37" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02275117059771981</v>
+        <v>0.02409359465881644</v>
       </c>
       <c r="M37" t="n">
-        <v>11.05700001083959</v>
+        <v>10.98018540429705</v>
       </c>
       <c r="N37" t="n">
-        <v>219.1284674512313</v>
+        <v>217.1794234037784</v>
       </c>
       <c r="O37" t="n">
-        <v>14.80298846352422</v>
+        <v>14.73700863146176</v>
       </c>
       <c r="P37" t="n">
-        <v>376.8513573347651</v>
+        <v>376.7995684836482</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35081,28 +35377,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.03338591120272878</v>
+        <v>0.002871353079790285</v>
       </c>
       <c r="J38" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K38" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0002107612716953922</v>
+        <v>1.578637583765641e-06</v>
       </c>
       <c r="M38" t="n">
-        <v>13.4695808070411</v>
+        <v>13.54453792673085</v>
       </c>
       <c r="N38" t="n">
-        <v>329.5118576082284</v>
+        <v>329.017394942742</v>
       </c>
       <c r="O38" t="n">
-        <v>18.15246147518921</v>
+        <v>18.13883664799763</v>
       </c>
       <c r="P38" t="n">
-        <v>377.9529133722219</v>
+        <v>377.6127752706894</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -35159,28 +35455,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05405674787874182</v>
+        <v>0.06512646663183462</v>
       </c>
       <c r="J39" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K39" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0007668307334705027</v>
+        <v>0.001133699393174759</v>
       </c>
       <c r="M39" t="n">
-        <v>11.95461479084533</v>
+        <v>11.90721138399711</v>
       </c>
       <c r="N39" t="n">
-        <v>237.7534418472226</v>
+        <v>235.8863618755123</v>
       </c>
       <c r="O39" t="n">
-        <v>15.41925555424848</v>
+        <v>15.3585924444759</v>
       </c>
       <c r="P39" t="n">
-        <v>389.4784218464627</v>
+        <v>389.3745636776006</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -35237,28 +35533,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.002758031579091355</v>
+        <v>0.02322725522447002</v>
       </c>
       <c r="J40" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K40" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L40" t="n">
-        <v>1.975752289773425e-06</v>
+        <v>0.000142213900208632</v>
       </c>
       <c r="M40" t="n">
-        <v>12.00829937205672</v>
+        <v>11.99320056555193</v>
       </c>
       <c r="N40" t="n">
-        <v>242.0679112301641</v>
+        <v>241.0535708765294</v>
       </c>
       <c r="O40" t="n">
-        <v>15.55853178259967</v>
+        <v>15.52590000214253</v>
       </c>
       <c r="P40" t="n">
-        <v>399.4621815559846</v>
+        <v>399.2705354333689</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -35315,28 +35611,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09508815720771625</v>
+        <v>0.1229533869717024</v>
       </c>
       <c r="J41" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K41" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L41" t="n">
-        <v>0.002178684842472189</v>
+        <v>0.003677555068876792</v>
       </c>
       <c r="M41" t="n">
-        <v>12.88321579947571</v>
+        <v>12.87537477628239</v>
       </c>
       <c r="N41" t="n">
-        <v>260.3654373671948</v>
+        <v>260.2815127374761</v>
       </c>
       <c r="O41" t="n">
-        <v>16.13584324933763</v>
+        <v>16.13324247439045</v>
       </c>
       <c r="P41" t="n">
-        <v>403.3125740661388</v>
+        <v>403.0516856804244</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -35393,28 +35689,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3124164529831813</v>
+        <v>0.3299851870186087</v>
       </c>
       <c r="J42" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K42" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02058690938817775</v>
+        <v>0.02330571849354879</v>
       </c>
       <c r="M42" t="n">
-        <v>13.36814586469671</v>
+        <v>13.31070590706424</v>
       </c>
       <c r="N42" t="n">
-        <v>287.0859399701539</v>
+        <v>285.2110581631554</v>
       </c>
       <c r="O42" t="n">
-        <v>16.94361059426691</v>
+        <v>16.88819286256393</v>
       </c>
       <c r="P42" t="n">
-        <v>405.0897053299687</v>
+        <v>404.9226953836173</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -35471,28 +35767,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4076677415309523</v>
+        <v>0.4201121675753139</v>
       </c>
       <c r="J43" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K43" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L43" t="n">
-        <v>0.03440884594217675</v>
+        <v>0.03712803511069585</v>
       </c>
       <c r="M43" t="n">
-        <v>13.30725459953696</v>
+        <v>13.24300921786993</v>
       </c>
       <c r="N43" t="n">
-        <v>294.8113818521098</v>
+        <v>292.4477199633995</v>
       </c>
       <c r="O43" t="n">
-        <v>17.17007227276897</v>
+        <v>17.10110288734032</v>
       </c>
       <c r="P43" t="n">
-        <v>406.6188263551301</v>
+        <v>406.5027600434875</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -35530,7 +35826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR215"/>
+  <dimension ref="A1:AR217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82281,7 +82577,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>-34.462710566234136,172.67056944100244</t>
+          <t>-34.462658289944244,172.67050722096175</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -82503,7 +82799,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>-34.462741392532735,172.67060613098906</t>
+          <t>-34.46267248289587,172.67052411361868</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -82618,12 +82914,12 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>-34.4467803925919,172.67717197843095</t>
+          <t>-34.44676601062096,172.6770829768204</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>-34.44605065050365,172.67732757755346</t>
+          <t>-34.446035439873,172.6772334481991</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -82633,7 +82929,7 @@
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>-34.44459254586697,172.6776474307509</t>
+          <t>-34.44457357161023,172.67753001145215</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -82664,6 +82960,450 @@
       <c r="AR215" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-34.46803711716916,172.66432743684862</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-34.46763090462574,172.66511747880392</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-34.46715127909288,172.6658113684892</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-34.46663919353891,172.66646274616616</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-34.46609814586729,172.66707284276058</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-34.46554186659774,172.66765466794487</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-34.464674557797395,172.6678726780125</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-34.46439366811081,172.66879693561606</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-34.464059404373245,172.66965767344388</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-34.463515966323556,172.67026945181595</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-34.462668308498564,172.6705191451896</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-34.46193627212346,172.67083183604558</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-34.46132586589343,172.67102667185713</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-34.46069917396618,172.67127897392587</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-34.46002619762085,172.67166267940115</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>-34.459393427214344,172.67217991375625</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>-34.45871797325838,172.67255543033156</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>-34.458044331212385,172.67293698279306</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>-34.45736282572131,172.67329244261592</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>-34.45667317962727,172.67362088949275</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>-34.455990214009276,172.6739715390825</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>-34.455301480475015,172.6743030546369</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>-34.45460248052237,172.67460049834006</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>-34.4538820294562,172.67482673030602</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>-34.45315655039815,172.6750362861673</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>-34.45243078845663,172.6752449227191</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>-34.45175152965966,172.67552395533477</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>-34.4510733949996,172.67576631932053</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>-34.45037146145466,172.67603785835993</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>-34.449653319312404,172.676265047536</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>-34.448938313057035,172.6765116819805</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>-34.44821907023199,172.6767321377805</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>-34.44748307350494,172.6768489525645</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>-34.446760002287434,172.67704579488426</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>-34.44602960422025,172.67719733501673</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>-34.44530272194627,172.67737067140504</t>
+        </is>
+      </c>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>-34.44456633753732,172.67748524469093</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>-34.44383077559544,172.67760494729816</t>
+        </is>
+      </c>
+      <c r="AN216" t="inlineStr">
+        <is>
+          <t>-34.44308970230574,172.67762169263733</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>-34.442356423578595,172.67762925858793</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>-34.441621277085645,172.67771536160592</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>-34.4408851597734,172.67781753387644</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-34.468027398592824,172.66431470734028</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-34.46761745762033,172.66509986564012</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-34.46714082715527,172.6657976782743</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-34.466631308780215,172.66645241848104</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-34.46608522519825,172.6670561255575</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-34.46552861850099,172.6676383287073</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-34.464674557797395,172.6678726780125</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-34.46438621834289,172.6687880687949</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-34.464059404373245,172.66965767344388</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-34.463515966323556,172.67026945181595</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-34.462668308498564,172.6705191451896</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-34.4619139209428,172.67079947514185</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-34.461308861926334,172.67098629858486</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-34.46068675577628,172.67123773766943</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>-34.460015967328594,172.6716287083297</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-34.45939767951475,172.67219403417928</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>-34.458717326173755,172.6725532815868</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>-34.458040787679536,172.67292521594035</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>-34.45735949790415,172.6732813920859</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>-34.45667225523925,172.6736178199237</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>-34.455983620083195,172.67394964298288</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>-34.455294393588005,172.67427952161927</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>-34.4545967494175,172.6745814674356</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>-34.4538767913666,172.67480933660988</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>-34.453149956585555,172.67501439075437</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>-34.45242570445654,172.6752280408809</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>-34.45174738392073,172.67550738511198</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>-34.45107143074627,172.67575547133129</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>-34.45037009744272,172.67602941728293</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>-34.449651040223046,172.676250943574</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>-34.448932287336895,172.67647439226488</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>-34.44821323448244,172.6766960236829</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>-34.447479395959036,172.67682619446836</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>-34.4467534932467,172.67700551445955</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>-34.446025167045214,172.6771698761803</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>-34.44529635109601,172.67733124640483</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>-34.4445607091065,172.677450414233</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>-34.44382542342364,172.67757182659636</t>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>-34.44308547741086,172.67759120175998</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>-34.44235279917776,172.6775966775112</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>-34.4416203434718,172.677706616936</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>-34.44088354612755,172.67780241976342</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR217"/>
+  <dimension ref="A1:AR218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30062,7 +30062,7 @@
         <v>325.89</v>
       </c>
       <c r="L217" t="n">
-        <v>376.81</v>
+        <v>384.04</v>
       </c>
       <c r="M217" t="n">
         <v>418.7</v>
@@ -30077,7 +30077,7 @@
         <v>435.61</v>
       </c>
       <c r="Q217" t="n">
-        <v>410.23</v>
+        <v>415.09</v>
       </c>
       <c r="R217" t="n">
         <v>404.99</v>
@@ -30160,6 +30160,144 @@
       <c r="AR217" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="C218" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="D218" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="E218" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="F218" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="G218" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="H218" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="I218" t="n">
+        <v>357.72</v>
+      </c>
+      <c r="J218" t="n">
+        <v>332.49</v>
+      </c>
+      <c r="K218" t="n">
+        <v>333.03</v>
+      </c>
+      <c r="L218" t="n">
+        <v>400.85</v>
+      </c>
+      <c r="M218" t="n">
+        <v>427.11</v>
+      </c>
+      <c r="N218" t="n">
+        <v>449.95</v>
+      </c>
+      <c r="O218" t="n">
+        <v>452.75</v>
+      </c>
+      <c r="P218" t="n">
+        <v>445</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>421.79</v>
+      </c>
+      <c r="R218" t="n">
+        <v>410.42</v>
+      </c>
+      <c r="S218" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="T218" t="n">
+        <v>394.31</v>
+      </c>
+      <c r="U218" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="V218" t="n">
+        <v>392.43</v>
+      </c>
+      <c r="W218" t="n">
+        <v>394.69</v>
+      </c>
+      <c r="X218" t="n">
+        <v>394.34</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>399.47</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>407.3</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>413.73</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>415.61</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>412.62</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>403.54</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>399.59</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>396.66</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>400.46</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>400.62</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>399.73</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>401.36</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>408.86</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>407.67</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>418.98</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>428.38</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>425.34</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>427.47</v>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30174,7 +30312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32377,6 +32515,16 @@
       </c>
       <c r="B220" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -32545,28 +32693,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01240362837996219</v>
+        <v>0.01123218110025788</v>
       </c>
       <c r="J2" t="n">
+        <v>217</v>
+      </c>
+      <c r="K2" t="n">
         <v>216</v>
       </c>
-      <c r="K2" t="n">
-        <v>215</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001012648449776332</v>
+        <v>8.386963165163408e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.120744077230234</v>
+        <v>7.0937859935382</v>
       </c>
       <c r="N2" t="n">
-        <v>96.09195083202037</v>
+        <v>95.65575574865814</v>
       </c>
       <c r="O2" t="n">
-        <v>9.80265019431074</v>
+        <v>9.780376053539973</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6352108364366</v>
+        <v>376.646202699722</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32623,28 +32771,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3705424653177649</v>
+        <v>0.3627952909501387</v>
       </c>
       <c r="J3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05276350570758548</v>
+        <v>0.05105575342673785</v>
       </c>
       <c r="M3" t="n">
-        <v>9.528793539249508</v>
+        <v>9.520101229473736</v>
       </c>
       <c r="N3" t="n">
-        <v>156.6235513710273</v>
+        <v>156.2765646434165</v>
       </c>
       <c r="O3" t="n">
-        <v>12.51493313490037</v>
+        <v>12.50106254057696</v>
       </c>
       <c r="P3" t="n">
-        <v>352.0962749049917</v>
+        <v>352.1688050580262</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32701,28 +32849,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03796964664273887</v>
+        <v>0.02843617793599914</v>
       </c>
       <c r="J4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007182565646711714</v>
+        <v>0.0004052116193971056</v>
       </c>
       <c r="M4" t="n">
-        <v>9.274082804750787</v>
+        <v>9.274611962187059</v>
       </c>
       <c r="N4" t="n">
-        <v>127.8974473017761</v>
+        <v>127.8770282192461</v>
       </c>
       <c r="O4" t="n">
-        <v>11.30917535905143</v>
+        <v>11.30827255681636</v>
       </c>
       <c r="P4" t="n">
-        <v>351.6684942627087</v>
+        <v>351.7574705355198</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32779,28 +32927,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3672387212709285</v>
+        <v>-0.3752940002046037</v>
       </c>
       <c r="J5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05135308592829468</v>
+        <v>0.05388806047202643</v>
       </c>
       <c r="M5" t="n">
-        <v>10.59372277932045</v>
+        <v>10.57468963806563</v>
       </c>
       <c r="N5" t="n">
-        <v>157.9566232290283</v>
+        <v>157.6274944007986</v>
       </c>
       <c r="O5" t="n">
-        <v>12.56807953623099</v>
+        <v>12.55497886899053</v>
       </c>
       <c r="P5" t="n">
-        <v>356.4923151259525</v>
+        <v>356.5678407582403</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32857,28 +33005,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6335323363686934</v>
+        <v>-0.6391831572935459</v>
       </c>
       <c r="J6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K6" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1153463902183073</v>
+        <v>0.1181091929441267</v>
       </c>
       <c r="M6" t="n">
-        <v>11.66555672574585</v>
+        <v>11.63156264085106</v>
       </c>
       <c r="N6" t="n">
-        <v>194.2838965510843</v>
+        <v>193.5804135832661</v>
       </c>
       <c r="O6" t="n">
-        <v>13.93857584371819</v>
+        <v>13.9133178495737</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4620770287306</v>
+        <v>362.5151775407423</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32935,28 +33083,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5902771140214429</v>
+        <v>-0.5967463012370346</v>
       </c>
       <c r="J7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K7" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09262515522700876</v>
+        <v>0.09523348118899921</v>
       </c>
       <c r="M7" t="n">
-        <v>12.25682112756203</v>
+        <v>12.22693956959074</v>
       </c>
       <c r="N7" t="n">
-        <v>215.4267661589029</v>
+        <v>214.6871186467572</v>
       </c>
       <c r="O7" t="n">
-        <v>14.6774236894253</v>
+        <v>14.65220524858825</v>
       </c>
       <c r="P7" t="n">
-        <v>364.6877870744409</v>
+        <v>364.7485777379597</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33013,28 +33161,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001324179550436292</v>
+        <v>0.00881478002950805</v>
       </c>
       <c r="J8" t="n">
+        <v>217</v>
+      </c>
+      <c r="K8" t="n">
         <v>216</v>
       </c>
-      <c r="K8" t="n">
-        <v>215</v>
-      </c>
       <c r="L8" t="n">
-        <v>2.07308487631952e-06</v>
+        <v>9.217599354349737e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>5.405095727548546</v>
+        <v>5.421600791285116</v>
       </c>
       <c r="N8" t="n">
-        <v>53.5696848552063</v>
+        <v>53.67455333849325</v>
       </c>
       <c r="O8" t="n">
-        <v>7.319131427649479</v>
+        <v>7.326291922827894</v>
       </c>
       <c r="P8" t="n">
-        <v>388.0899553109704</v>
+        <v>388.0199058031639</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33095,28 +33243,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3456187501977913</v>
+        <v>-0.34324799781286</v>
       </c>
       <c r="J9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1170614963655928</v>
+        <v>0.116621320319461</v>
       </c>
       <c r="M9" t="n">
-        <v>5.367003083685328</v>
+        <v>5.354782240192691</v>
       </c>
       <c r="N9" t="n">
-        <v>57.25762411585856</v>
+        <v>57.02661921091772</v>
       </c>
       <c r="O9" t="n">
-        <v>7.566876774195451</v>
+        <v>7.551597129807556</v>
       </c>
       <c r="P9" t="n">
-        <v>364.1090050671079</v>
+        <v>364.0869029002005</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33177,28 +33325,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3587099173056759</v>
+        <v>-0.3512121951603955</v>
       </c>
       <c r="J10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04294341200244745</v>
+        <v>0.04156098229534722</v>
       </c>
       <c r="M10" t="n">
-        <v>10.39804030995147</v>
+        <v>10.38924239135296</v>
       </c>
       <c r="N10" t="n">
-        <v>181.5504736485398</v>
+        <v>181.0566347955681</v>
       </c>
       <c r="O10" t="n">
-        <v>13.47406670788518</v>
+        <v>13.45572869805155</v>
       </c>
       <c r="P10" t="n">
-        <v>333.2220231644368</v>
+        <v>333.1515834377192</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33259,28 +33407,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1849956445259629</v>
+        <v>-0.1895724881619605</v>
       </c>
       <c r="J11" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002202001026233469</v>
+        <v>0.002334753075508234</v>
       </c>
       <c r="M11" t="n">
-        <v>23.95678451613943</v>
+        <v>23.86668805414561</v>
       </c>
       <c r="N11" t="n">
-        <v>1002.013769674273</v>
+        <v>997.3094300904046</v>
       </c>
       <c r="O11" t="n">
-        <v>31.65460108221668</v>
+        <v>31.58020630221412</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2890345913922</v>
+        <v>343.3318563903088</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33341,28 +33489,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7963104107404319</v>
+        <v>0.8082871659982394</v>
       </c>
       <c r="J12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K12" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04942489739020273</v>
+        <v>0.05137580100235173</v>
       </c>
       <c r="M12" t="n">
-        <v>20.92987548278527</v>
+        <v>20.83114619429201</v>
       </c>
       <c r="N12" t="n">
-        <v>785.6180247329175</v>
+        <v>781.2104789279717</v>
       </c>
       <c r="O12" t="n">
-        <v>28.02887840661694</v>
+        <v>27.95014273537743</v>
       </c>
       <c r="P12" t="n">
-        <v>372.8173656876205</v>
+        <v>372.7064885176218</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33423,28 +33571,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.533097217165328</v>
+        <v>1.529369077272421</v>
       </c>
       <c r="J13" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3008697091281007</v>
+        <v>0.3019196017111185</v>
       </c>
       <c r="M13" t="n">
-        <v>14.09751227688848</v>
+        <v>14.04864922229239</v>
       </c>
       <c r="N13" t="n">
-        <v>351.6297689083966</v>
+        <v>350.0518261256276</v>
       </c>
       <c r="O13" t="n">
-        <v>18.75179375175603</v>
+        <v>18.7096719940684</v>
       </c>
       <c r="P13" t="n">
-        <v>390.835632891014</v>
+        <v>390.8702076801701</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33505,28 +33653,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.633929501423476</v>
+        <v>1.635823027202633</v>
       </c>
       <c r="J14" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K14" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4037680438123697</v>
+        <v>0.4067287221235125</v>
       </c>
       <c r="M14" t="n">
-        <v>12.13534537451278</v>
+        <v>12.09035754983893</v>
       </c>
       <c r="N14" t="n">
-        <v>250.7205454788302</v>
+        <v>249.5770818683803</v>
       </c>
       <c r="O14" t="n">
-        <v>15.83415755507157</v>
+        <v>15.79800879441394</v>
       </c>
       <c r="P14" t="n">
-        <v>404.4258379828096</v>
+        <v>404.408159872087</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33583,28 +33731,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.859635769093905</v>
+        <v>1.864174354080882</v>
       </c>
       <c r="J15" t="n">
+        <v>217</v>
+      </c>
+      <c r="K15" t="n">
         <v>216</v>
       </c>
-      <c r="K15" t="n">
-        <v>215</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.4896678458070549</v>
+        <v>0.4932617175898892</v>
       </c>
       <c r="M15" t="n">
-        <v>11.49947586264513</v>
+        <v>11.47218374327915</v>
       </c>
       <c r="N15" t="n">
-        <v>228.2708465345835</v>
+        <v>227.3435848912326</v>
       </c>
       <c r="O15" t="n">
-        <v>15.10863483358385</v>
+        <v>15.07791712708465</v>
       </c>
       <c r="P15" t="n">
-        <v>398.136301066766</v>
+        <v>398.0938577879709</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33661,28 +33809,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.841938670573422</v>
+        <v>1.840332086398188</v>
       </c>
       <c r="J16" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K16" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5029799818601473</v>
+        <v>0.5050236882057297</v>
       </c>
       <c r="M16" t="n">
-        <v>11.20397676541404</v>
+        <v>11.15952856578245</v>
       </c>
       <c r="N16" t="n">
-        <v>215.0760871945349</v>
+        <v>214.0781438219486</v>
       </c>
       <c r="O16" t="n">
-        <v>14.6654726209057</v>
+        <v>14.63140949539547</v>
       </c>
       <c r="P16" t="n">
-        <v>398.0721200366881</v>
+        <v>398.0871005554893</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33739,28 +33887,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.717062846721484</v>
+        <v>1.7044008807236</v>
       </c>
       <c r="J17" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K17" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3969886338207548</v>
+        <v>0.3954172519018448</v>
       </c>
       <c r="M17" t="n">
-        <v>13.97167620496639</v>
+        <v>13.97277824070414</v>
       </c>
       <c r="N17" t="n">
-        <v>288.62749128866</v>
+        <v>287.7636977631004</v>
       </c>
       <c r="O17" t="n">
-        <v>16.98904032865482</v>
+        <v>16.96359919837475</v>
       </c>
       <c r="P17" t="n">
-        <v>395.9884672921058</v>
+        <v>396.1064744655734</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33817,28 +33965,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.643841199738912</v>
+        <v>1.62639807523587</v>
       </c>
       <c r="J18" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K18" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L18" t="n">
-        <v>0.348765006935751</v>
+        <v>0.3448519127108987</v>
       </c>
       <c r="M18" t="n">
-        <v>14.36299101839025</v>
+        <v>14.38426382592369</v>
       </c>
       <c r="N18" t="n">
-        <v>321.0228927690465</v>
+        <v>321.4537559993651</v>
       </c>
       <c r="O18" t="n">
-        <v>17.91711173066258</v>
+        <v>17.92913149038082</v>
       </c>
       <c r="P18" t="n">
-        <v>387.3431827584646</v>
+        <v>387.5059370027353</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33895,28 +34043,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.257763036601828</v>
+        <v>1.242138719431478</v>
       </c>
       <c r="J19" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K19" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2530021841803309</v>
+        <v>0.2492017181145261</v>
       </c>
       <c r="M19" t="n">
-        <v>14.50967395055433</v>
+        <v>14.51628497498594</v>
       </c>
       <c r="N19" t="n">
-        <v>297.979520826464</v>
+        <v>298.1288117153403</v>
       </c>
       <c r="O19" t="n">
-        <v>17.26208332810568</v>
+        <v>17.26640702970193</v>
       </c>
       <c r="P19" t="n">
-        <v>387.2079935819098</v>
+        <v>387.3543275834605</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33973,28 +34121,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8667461859668778</v>
+        <v>0.8518440732018758</v>
       </c>
       <c r="J20" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K20" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1278460360248599</v>
+        <v>0.1246551539990017</v>
       </c>
       <c r="M20" t="n">
-        <v>15.44002073742159</v>
+        <v>15.43171624304048</v>
       </c>
       <c r="N20" t="n">
-        <v>323.4593846165854</v>
+        <v>323.3469778252085</v>
       </c>
       <c r="O20" t="n">
-        <v>17.98497663653154</v>
+        <v>17.98185134587672</v>
       </c>
       <c r="P20" t="n">
-        <v>388.7671283821198</v>
+        <v>388.9071628706307</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34051,28 +34199,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3217201416472201</v>
+        <v>0.3145198820219052</v>
       </c>
       <c r="J21" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K21" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02276917612584051</v>
+        <v>0.02197511135491348</v>
       </c>
       <c r="M21" t="n">
-        <v>13.63581318749537</v>
+        <v>13.59760342946677</v>
       </c>
       <c r="N21" t="n">
-        <v>278.1396436749131</v>
+        <v>277.1668949085052</v>
       </c>
       <c r="O21" t="n">
-        <v>16.67751911031473</v>
+        <v>16.64833009369124</v>
       </c>
       <c r="P21" t="n">
-        <v>392.2218040540515</v>
+        <v>392.2898510838036</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34129,28 +34277,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02718332951224336</v>
+        <v>0.02586268516693774</v>
       </c>
       <c r="J22" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K22" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001900297482486657</v>
+        <v>0.0001737583555262434</v>
       </c>
       <c r="M22" t="n">
-        <v>12.4738695200741</v>
+        <v>12.42126622538426</v>
       </c>
       <c r="N22" t="n">
-        <v>243.4208196197273</v>
+        <v>242.2994261277849</v>
       </c>
       <c r="O22" t="n">
-        <v>15.60194922500799</v>
+        <v>15.56597013127627</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2430040132911</v>
+        <v>393.2554849417205</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34207,28 +34355,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1370351481266369</v>
+        <v>-0.1330904085591028</v>
       </c>
       <c r="J23" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K23" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L23" t="n">
-        <v>0.006216279946883119</v>
+        <v>0.005921339261902969</v>
       </c>
       <c r="M23" t="n">
-        <v>10.93161350634638</v>
+        <v>10.90610631619415</v>
       </c>
       <c r="N23" t="n">
-        <v>189.4831290497427</v>
+        <v>188.7078854554793</v>
       </c>
       <c r="O23" t="n">
-        <v>13.76528710378911</v>
+        <v>13.73709887332399</v>
       </c>
       <c r="P23" t="n">
-        <v>393.6746641621659</v>
+        <v>393.6376611376473</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34285,28 +34433,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2207659236443664</v>
+        <v>-0.2152708092926467</v>
       </c>
       <c r="J24" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K24" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01695200693644938</v>
+        <v>0.01627489309026864</v>
       </c>
       <c r="M24" t="n">
-        <v>10.86495224830108</v>
+        <v>10.84842800289417</v>
       </c>
       <c r="N24" t="n">
-        <v>178.3869022999546</v>
+        <v>177.7549172605974</v>
       </c>
       <c r="O24" t="n">
-        <v>13.35615597018673</v>
+        <v>13.33247603637814</v>
       </c>
       <c r="P24" t="n">
-        <v>393.7255789928912</v>
+        <v>393.6740329154866</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34363,28 +34511,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.128647314413747</v>
+        <v>-0.1197082419332253</v>
       </c>
       <c r="J25" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K25" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L25" t="n">
-        <v>0.006745566199959585</v>
+        <v>0.005885359591615291</v>
       </c>
       <c r="M25" t="n">
-        <v>10.21476474792421</v>
+        <v>10.20640088329921</v>
       </c>
       <c r="N25" t="n">
-        <v>153.8115114598972</v>
+        <v>153.6056877494879</v>
       </c>
       <c r="O25" t="n">
-        <v>12.40207690106368</v>
+        <v>12.39377616989624</v>
       </c>
       <c r="P25" t="n">
-        <v>392.3595590026312</v>
+        <v>392.2757074041904</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34441,28 +34589,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.159885837363656</v>
+        <v>-0.1463880137744317</v>
       </c>
       <c r="J26" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K26" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01055636568714313</v>
+        <v>0.00888583899956974</v>
       </c>
       <c r="M26" t="n">
-        <v>10.20174648439223</v>
+        <v>10.20355660464944</v>
       </c>
       <c r="N26" t="n">
-        <v>151.2313786236326</v>
+        <v>151.6812862674045</v>
       </c>
       <c r="O26" t="n">
-        <v>12.29761678633843</v>
+        <v>12.31589567459081</v>
       </c>
       <c r="P26" t="n">
-        <v>395.6474683394094</v>
+        <v>395.5208540753575</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34519,28 +34667,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1421346751333362</v>
+        <v>0.156238339323221</v>
       </c>
       <c r="J27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K27" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008445399689546274</v>
+        <v>0.01020303468669459</v>
       </c>
       <c r="M27" t="n">
-        <v>9.987471383277187</v>
+        <v>10.00341477988675</v>
       </c>
       <c r="N27" t="n">
-        <v>150.0618834794127</v>
+        <v>150.6184719297512</v>
       </c>
       <c r="O27" t="n">
-        <v>12.24997483586855</v>
+        <v>12.27267175189458</v>
       </c>
       <c r="P27" t="n">
-        <v>393.4370961431143</v>
+        <v>393.30436314094</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34597,28 +34745,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3803866289776486</v>
+        <v>0.3924624166544241</v>
       </c>
       <c r="J28" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K28" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L28" t="n">
-        <v>0.05484020977346515</v>
+        <v>0.05839770933263688</v>
       </c>
       <c r="M28" t="n">
-        <v>10.05569346163885</v>
+        <v>10.06411818335939</v>
       </c>
       <c r="N28" t="n">
-        <v>158.1112287093149</v>
+        <v>158.2950102379588</v>
       </c>
       <c r="O28" t="n">
-        <v>12.57422875206726</v>
+        <v>12.58153449456619</v>
       </c>
       <c r="P28" t="n">
-        <v>391.3847636177511</v>
+        <v>391.2710782545428</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34675,28 +34823,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6217888006881751</v>
+        <v>0.6342344850967062</v>
       </c>
       <c r="J29" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K29" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1279866229824972</v>
+        <v>0.1329443059430125</v>
       </c>
       <c r="M29" t="n">
-        <v>10.53093067282472</v>
+        <v>10.54292700267545</v>
       </c>
       <c r="N29" t="n">
-        <v>167.778017704122</v>
+        <v>167.9758138705933</v>
       </c>
       <c r="O29" t="n">
-        <v>12.95291541330067</v>
+        <v>12.96054836303593</v>
       </c>
       <c r="P29" t="n">
-        <v>381.549994702804</v>
+        <v>381.4330919580573</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34753,28 +34901,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6541172683973703</v>
+        <v>0.6651942715033231</v>
       </c>
       <c r="J30" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K30" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1317207850056417</v>
+        <v>0.1362771059196055</v>
       </c>
       <c r="M30" t="n">
-        <v>10.85220862181184</v>
+        <v>10.85139488674521</v>
       </c>
       <c r="N30" t="n">
-        <v>177.7774586371775</v>
+        <v>177.7218370175324</v>
       </c>
       <c r="O30" t="n">
-        <v>13.33332136555545</v>
+        <v>13.33123538977286</v>
       </c>
       <c r="P30" t="n">
-        <v>373.2337362954112</v>
+        <v>373.1293788663848</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34831,28 +34979,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5763314078380726</v>
+        <v>0.590400396187284</v>
       </c>
       <c r="J31" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K31" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08995612687844068</v>
+        <v>0.09433870800428823</v>
       </c>
       <c r="M31" t="n">
-        <v>11.77867309178652</v>
+        <v>11.79223131441533</v>
       </c>
       <c r="N31" t="n">
-        <v>210.076778766158</v>
+        <v>210.3326380401324</v>
       </c>
       <c r="O31" t="n">
-        <v>14.4940256232062</v>
+        <v>14.50284930764063</v>
       </c>
       <c r="P31" t="n">
-        <v>368.819947480048</v>
+        <v>368.6864576289664</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34909,28 +35057,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4500551304122239</v>
+        <v>0.4667854634625083</v>
       </c>
       <c r="J32" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K32" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04715616256016653</v>
+        <v>0.05070140586500538</v>
       </c>
       <c r="M32" t="n">
-        <v>12.24266917820335</v>
+        <v>12.25621722000539</v>
       </c>
       <c r="N32" t="n">
-        <v>255.8683682258878</v>
+        <v>256.421825626877</v>
       </c>
       <c r="O32" t="n">
-        <v>15.99588597814725</v>
+        <v>16.01317662510712</v>
       </c>
       <c r="P32" t="n">
-        <v>368.159932381277</v>
+        <v>368.0011910693937</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34987,28 +35135,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3540649288051649</v>
+        <v>0.3690938008764204</v>
       </c>
       <c r="J33" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K33" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L33" t="n">
-        <v>0.04676176404402699</v>
+        <v>0.05067674492040486</v>
       </c>
       <c r="M33" t="n">
-        <v>9.99015488448298</v>
+        <v>10.02075031589995</v>
       </c>
       <c r="N33" t="n">
-        <v>160.0910804260856</v>
+        <v>160.7313050252033</v>
       </c>
       <c r="O33" t="n">
-        <v>12.6527103984121</v>
+        <v>12.67798505383262</v>
       </c>
       <c r="P33" t="n">
-        <v>369.9674738608687</v>
+        <v>369.8246204106717</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35065,28 +35213,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3110185902816979</v>
+        <v>0.333815042656912</v>
       </c>
       <c r="J34" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K34" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02488587033733014</v>
+        <v>0.02846173815501118</v>
       </c>
       <c r="M34" t="n">
-        <v>12.25303920124428</v>
+        <v>12.29528252710455</v>
       </c>
       <c r="N34" t="n">
-        <v>238.9447322026597</v>
+        <v>241.0844343983694</v>
       </c>
       <c r="O34" t="n">
-        <v>15.45783724208079</v>
+        <v>15.52689390697217</v>
       </c>
       <c r="P34" t="n">
-        <v>365.6227083052539</v>
+        <v>365.4078707442445</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35143,28 +35291,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.02550695889065689</v>
+        <v>0.0001657761329022268</v>
       </c>
       <c r="J35" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K35" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0001585821371736795</v>
+        <v>6.660511697731408e-09</v>
       </c>
       <c r="M35" t="n">
-        <v>12.66461066315124</v>
+        <v>12.72334971152468</v>
       </c>
       <c r="N35" t="n">
-        <v>258.5927644821709</v>
+        <v>261.5141932291779</v>
       </c>
       <c r="O35" t="n">
-        <v>16.08081977021603</v>
+        <v>16.17140047210438</v>
       </c>
       <c r="P35" t="n">
-        <v>371.3446950548084</v>
+        <v>371.1027509274449</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35221,28 +35369,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2107755073942963</v>
+        <v>0.2315149193391493</v>
       </c>
       <c r="J36" t="n">
+        <v>217</v>
+      </c>
+      <c r="K36" t="n">
         <v>216</v>
       </c>
-      <c r="K36" t="n">
-        <v>215</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.009740208590925059</v>
+        <v>0.01173414990797406</v>
       </c>
       <c r="M36" t="n">
-        <v>12.65189315609476</v>
+        <v>12.70787206374357</v>
       </c>
       <c r="N36" t="n">
-        <v>283.4134663721576</v>
+        <v>284.7901989617305</v>
       </c>
       <c r="O36" t="n">
-        <v>16.83488836827134</v>
+        <v>16.87572810167699</v>
       </c>
       <c r="P36" t="n">
-        <v>369.8668443488318</v>
+        <v>369.6710261781213</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35299,28 +35447,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.29011349377726</v>
+        <v>0.3046234543259591</v>
       </c>
       <c r="J37" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K37" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02409359465881644</v>
+        <v>0.02660299410071765</v>
       </c>
       <c r="M37" t="n">
-        <v>10.98018540429705</v>
+        <v>11.00025444995958</v>
       </c>
       <c r="N37" t="n">
-        <v>217.1794234037784</v>
+        <v>217.4776226675026</v>
       </c>
       <c r="O37" t="n">
-        <v>14.73700863146176</v>
+        <v>14.74712252161426</v>
       </c>
       <c r="P37" t="n">
-        <v>376.7995684836482</v>
+        <v>376.6640605476764</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35377,28 +35525,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.002871353079790285</v>
+        <v>0.02966472973151407</v>
       </c>
       <c r="J38" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K38" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L38" t="n">
-        <v>1.578637583765641e-06</v>
+        <v>0.0001678685955656123</v>
       </c>
       <c r="M38" t="n">
-        <v>13.54453792673085</v>
+        <v>13.64285403130041</v>
       </c>
       <c r="N38" t="n">
-        <v>329.017394942742</v>
+        <v>331.9670974142439</v>
       </c>
       <c r="O38" t="n">
-        <v>18.13883664799763</v>
+        <v>18.21996425392333</v>
       </c>
       <c r="P38" t="n">
-        <v>377.6127752706894</v>
+        <v>377.359735567032</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -35455,28 +35603,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.06512646663183462</v>
+        <v>0.07946325628572996</v>
       </c>
       <c r="J39" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K39" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L39" t="n">
-        <v>0.001133699393174759</v>
+        <v>0.00169475151154852</v>
       </c>
       <c r="M39" t="n">
-        <v>11.90721138399711</v>
+        <v>11.9364846497463</v>
       </c>
       <c r="N39" t="n">
-        <v>235.8863618755123</v>
+        <v>236.049850940901</v>
       </c>
       <c r="O39" t="n">
-        <v>15.3585924444759</v>
+        <v>15.36391391999125</v>
       </c>
       <c r="P39" t="n">
-        <v>389.3745636776006</v>
+        <v>389.239258851187</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -35533,28 +35681,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02322725522447002</v>
+        <v>0.03975181256883376</v>
       </c>
       <c r="J40" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K40" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L40" t="n">
-        <v>0.000142213900208632</v>
+        <v>0.000417659856441488</v>
       </c>
       <c r="M40" t="n">
-        <v>11.99320056555193</v>
+        <v>12.01660776546759</v>
       </c>
       <c r="N40" t="n">
-        <v>241.0535708765294</v>
+        <v>241.6197072481555</v>
       </c>
       <c r="O40" t="n">
-        <v>15.52590000214253</v>
+        <v>15.54412130833247</v>
       </c>
       <c r="P40" t="n">
-        <v>399.2705354333689</v>
+        <v>399.1148837353156</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -35611,28 +35759,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1229533869717024</v>
+        <v>0.1420440447697041</v>
       </c>
       <c r="J41" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K41" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L41" t="n">
-        <v>0.003677555068876792</v>
+        <v>0.004908406989497904</v>
       </c>
       <c r="M41" t="n">
-        <v>12.87537477628239</v>
+        <v>12.89184366109418</v>
       </c>
       <c r="N41" t="n">
-        <v>260.2815127374761</v>
+        <v>261.3311587966351</v>
       </c>
       <c r="O41" t="n">
-        <v>16.13324247439045</v>
+        <v>16.1657402798831</v>
       </c>
       <c r="P41" t="n">
-        <v>403.0516856804244</v>
+        <v>402.8718628118724</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -35689,28 +35837,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3299851870186087</v>
+        <v>0.340307241925158</v>
       </c>
       <c r="J42" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K42" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02330571849354879</v>
+        <v>0.02494234773890414</v>
       </c>
       <c r="M42" t="n">
-        <v>13.31070590706424</v>
+        <v>13.28989767876199</v>
       </c>
       <c r="N42" t="n">
-        <v>285.2110581631554</v>
+        <v>284.4773967078829</v>
       </c>
       <c r="O42" t="n">
-        <v>16.88819286256393</v>
+        <v>16.8664577403758</v>
       </c>
       <c r="P42" t="n">
-        <v>404.9226953836173</v>
+        <v>404.8239822218752</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -35767,28 +35915,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4201121675753139</v>
+        <v>0.4286235719160422</v>
       </c>
       <c r="J43" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K43" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L43" t="n">
-        <v>0.03712803511069585</v>
+        <v>0.03890700536364367</v>
       </c>
       <c r="M43" t="n">
-        <v>13.24300921786993</v>
+        <v>13.22461907258515</v>
       </c>
       <c r="N43" t="n">
-        <v>292.4477199633995</v>
+        <v>291.4997034714013</v>
       </c>
       <c r="O43" t="n">
-        <v>17.10110288734032</v>
+        <v>17.07336239501175</v>
       </c>
       <c r="P43" t="n">
-        <v>406.5027600434875</v>
+        <v>406.4228902690542</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -35826,7 +35974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR217"/>
+  <dimension ref="A1:AR218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83243,7 +83391,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>-34.462668308498564,172.6705191451896</t>
+          <t>-34.46262187634277,172.67046388100383</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -83268,7 +83416,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>-34.45939767951475,172.67219403417928</t>
+          <t>-34.459382704014786,172.6721443057394</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -83404,6 +83552,228 @@
       <c r="AR217" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>-34.46800264372257,172.6642822831342</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>-34.46759679812526,172.66507280542672</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-34.467120717867495,172.66577133863066</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-34.466600869936144,172.66641254883118</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-34.46604609401525,172.66700549634533</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-34.465495813680626,172.66759786966512</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-34.4646217026099,172.6678097697141</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-34.464352822823656,172.66874832099532</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-34.46399421927936,172.66958008862142</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-34.463470112155015,172.6702148750318</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-34.46251391987843,172.6703353900975</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-34.46186534896775,172.67072915086015</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>-34.461278900577,172.6709151601427</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-34.46065963908516,172.6711476932813</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>-34.45998703280654,172.67153262754331</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>-34.459362058745135,172.67207575010065</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>-34.45870059440084,172.67249772119845</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>-34.458029263486594,172.67288694809594</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>-34.45735721773257,172.67327382042697</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>-34.45666664728363,172.67359919787276</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>-34.455969970027525,172.67390431602135</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>-34.4552664773717,172.6741868220322</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>-34.454571021034,172.6744960330312</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>-34.45385867372,172.6747491749014</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>-34.45313800143875,172.67497469253792</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>-34.45242163725481,172.67521453541184</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>-34.451743394622696,172.67549144018216</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>-34.45106540317856,172.6757221828969</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>-34.450363294640326,172.67598731875134</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>-34.44964123321395,172.67619025380705</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>-34.448915487776425,172.67637042984867</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>-34.448193223650925,172.67657218869473</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>-34.447459333404055,172.67670204000785</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>-34.446731721531506,172.6768707834299</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>-34.44600591619507,172.67705074546504</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>-34.44527575365322,172.67720378296335</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>-34.44453545010643,172.67729410459836</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>-34.44381014378714,172.6774772723584</t>
+        </is>
+      </c>
+      <c r="AN218" t="inlineStr">
+        <is>
+          <t>-34.443076179640116,172.67752410036834</t>
+        </is>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>-34.44234677449231,172.67754251956882</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>-34.441618360981096,172.67768804800798</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>-34.44088096429031,172.67777823718384</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR218"/>
+  <dimension ref="A1:AR219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30301,6 +30301,144 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="C219" t="n">
+        <v>355.04</v>
+      </c>
+      <c r="D219" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="E219" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="F219" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="G219" t="n">
+        <v>341.95</v>
+      </c>
+      <c r="H219" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="I219" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="J219" t="n">
+        <v>335.21</v>
+      </c>
+      <c r="K219" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="L219" t="n">
+        <v>402.92</v>
+      </c>
+      <c r="M219" t="n">
+        <v>430.23</v>
+      </c>
+      <c r="N219" t="n">
+        <v>450.8</v>
+      </c>
+      <c r="O219" t="n">
+        <v>452.88</v>
+      </c>
+      <c r="P219" t="n">
+        <v>444.66</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>424.33</v>
+      </c>
+      <c r="R219" t="n">
+        <v>412.29</v>
+      </c>
+      <c r="S219" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="T219" t="n">
+        <v>394.56</v>
+      </c>
+      <c r="U219" t="n">
+        <v>393.98</v>
+      </c>
+      <c r="V219" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="W219" t="n">
+        <v>395.69</v>
+      </c>
+      <c r="X219" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>400.19</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>408.41</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>416.11</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>419.27</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>417.08</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>407.71</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>404.67</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>404.78</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>402.81</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>400.46</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>404.41</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>399.73</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>401.36</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>408.86</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>412.79</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>424.12</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>433.18</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>425.34</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>427.47</v>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30312,7 +30450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B221"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32525,6 +32663,16 @@
       </c>
       <c r="B221" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>-0.25</v>
       </c>
     </row>
   </sheetData>
@@ -32693,28 +32841,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01123218110025788</v>
+        <v>0.01199810195406654</v>
       </c>
       <c r="J2" t="n">
+        <v>218</v>
+      </c>
+      <c r="K2" t="n">
         <v>217</v>
       </c>
-      <c r="K2" t="n">
-        <v>216</v>
-      </c>
       <c r="L2" t="n">
-        <v>8.386963165163408e-05</v>
+        <v>9.664054540559075e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0937859935382</v>
+        <v>7.065486173331119</v>
       </c>
       <c r="N2" t="n">
-        <v>95.65575574865814</v>
+        <v>95.21873206200277</v>
       </c>
       <c r="O2" t="n">
-        <v>9.780376053539973</v>
+        <v>9.758008611494599</v>
       </c>
       <c r="P2" t="n">
-        <v>376.646202699722</v>
+        <v>376.6390081314042</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32771,28 +32919,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3627952909501387</v>
+        <v>0.3571301901382167</v>
       </c>
       <c r="J3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05105575342673785</v>
+        <v>0.04995436774004369</v>
       </c>
       <c r="M3" t="n">
-        <v>9.520101229473736</v>
+        <v>9.501952175680684</v>
       </c>
       <c r="N3" t="n">
-        <v>156.2765646434165</v>
+        <v>155.7613343635039</v>
       </c>
       <c r="O3" t="n">
-        <v>12.50106254057696</v>
+        <v>12.48043806777246</v>
       </c>
       <c r="P3" t="n">
-        <v>352.1688050580262</v>
+        <v>352.2219007043581</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32849,28 +32997,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02843617793599914</v>
+        <v>0.0210818011721513</v>
       </c>
       <c r="J4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004052116193971056</v>
+        <v>0.0002243534098335109</v>
       </c>
       <c r="M4" t="n">
-        <v>9.274611962187059</v>
+        <v>9.265087397296298</v>
       </c>
       <c r="N4" t="n">
-        <v>127.8770282192461</v>
+        <v>127.6330063405233</v>
       </c>
       <c r="O4" t="n">
-        <v>11.30827255681636</v>
+        <v>11.29747787519512</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7574705355198</v>
+        <v>351.8261847858598</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32927,28 +33075,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3752940002046037</v>
+        <v>-0.3815286967969012</v>
       </c>
       <c r="J5" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05388806047202643</v>
+        <v>0.05603113698662709</v>
       </c>
       <c r="M5" t="n">
-        <v>10.57468963806563</v>
+        <v>10.54892129718702</v>
       </c>
       <c r="N5" t="n">
-        <v>157.6274944007986</v>
+        <v>157.144524513603</v>
       </c>
       <c r="O5" t="n">
-        <v>12.55497886899053</v>
+        <v>12.53572991546974</v>
       </c>
       <c r="P5" t="n">
-        <v>356.5678407582403</v>
+        <v>356.6263606748145</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33005,28 +33153,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6391831572935459</v>
+        <v>-0.6444007744186723</v>
       </c>
       <c r="J6" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K6" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1181091929441267</v>
+        <v>0.1207670867460744</v>
       </c>
       <c r="M6" t="n">
-        <v>11.63156264085106</v>
+        <v>11.59660262386332</v>
       </c>
       <c r="N6" t="n">
-        <v>193.5804135832661</v>
+        <v>192.8584616351978</v>
       </c>
       <c r="O6" t="n">
-        <v>13.9133178495737</v>
+        <v>13.88734897794384</v>
       </c>
       <c r="P6" t="n">
-        <v>362.5151775407423</v>
+        <v>362.564260442203</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33083,28 +33231,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5967463012370346</v>
+        <v>-0.6026324847237997</v>
       </c>
       <c r="J7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09523348118899921</v>
+        <v>0.09771858279065204</v>
       </c>
       <c r="M7" t="n">
-        <v>12.22693956959074</v>
+        <v>12.19485299652374</v>
       </c>
       <c r="N7" t="n">
-        <v>214.6871186467572</v>
+        <v>213.9149679839845</v>
       </c>
       <c r="O7" t="n">
-        <v>14.65220524858825</v>
+        <v>14.62583221509069</v>
       </c>
       <c r="P7" t="n">
-        <v>364.7485777379597</v>
+        <v>364.8039499427674</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33161,28 +33309,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00881478002950805</v>
+        <v>0.01610286896098015</v>
       </c>
       <c r="J8" t="n">
+        <v>218</v>
+      </c>
+      <c r="K8" t="n">
         <v>217</v>
       </c>
-      <c r="K8" t="n">
-        <v>216</v>
-      </c>
       <c r="L8" t="n">
-        <v>9.217599354349737e-05</v>
+        <v>0.0003086393732684156</v>
       </c>
       <c r="M8" t="n">
-        <v>5.421600791285116</v>
+        <v>5.437483715800369</v>
       </c>
       <c r="N8" t="n">
-        <v>53.67455333849325</v>
+        <v>53.76831373067269</v>
       </c>
       <c r="O8" t="n">
-        <v>7.326291922827894</v>
+        <v>7.332688029002235</v>
       </c>
       <c r="P8" t="n">
-        <v>388.0199058031639</v>
+        <v>387.951676182669</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33243,28 +33391,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.34324799781286</v>
+        <v>-0.3384083936898392</v>
       </c>
       <c r="J9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.116621320319461</v>
+        <v>0.1144670967649392</v>
       </c>
       <c r="M9" t="n">
-        <v>5.354782240192691</v>
+        <v>5.356140892534343</v>
       </c>
       <c r="N9" t="n">
-        <v>57.02661921091772</v>
+        <v>56.91287530194795</v>
       </c>
       <c r="O9" t="n">
-        <v>7.551597129807556</v>
+        <v>7.544062254644241</v>
       </c>
       <c r="P9" t="n">
-        <v>364.0869029002005</v>
+        <v>364.0417348978049</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33325,28 +33473,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3512121951603955</v>
+        <v>-0.3416135709631805</v>
       </c>
       <c r="J10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04156098229534722</v>
+        <v>0.03965922777761066</v>
       </c>
       <c r="M10" t="n">
-        <v>10.38924239135296</v>
+        <v>10.39152414843627</v>
       </c>
       <c r="N10" t="n">
-        <v>181.0566347955681</v>
+        <v>180.8077993750829</v>
       </c>
       <c r="O10" t="n">
-        <v>13.45572869805155</v>
+        <v>13.44647906981909</v>
       </c>
       <c r="P10" t="n">
-        <v>333.1515834377192</v>
+        <v>333.0613075227155</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33407,28 +33555,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1895724881619605</v>
+        <v>-0.1867920229866635</v>
       </c>
       <c r="J11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002334753075508234</v>
+        <v>0.002289023058927309</v>
       </c>
       <c r="M11" t="n">
-        <v>23.86668805414561</v>
+        <v>23.767671738565</v>
       </c>
       <c r="N11" t="n">
-        <v>997.3094300904046</v>
+        <v>992.5660336409114</v>
       </c>
       <c r="O11" t="n">
-        <v>31.58020630221412</v>
+        <v>31.50501600762824</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3318563903088</v>
+        <v>343.3058119821005</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33489,28 +33637,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8082871659982394</v>
+        <v>0.8156528317767103</v>
       </c>
       <c r="J12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05137580100235173</v>
+        <v>0.05273480818953025</v>
       </c>
       <c r="M12" t="n">
-        <v>20.83114619429201</v>
+        <v>20.77485756952037</v>
       </c>
       <c r="N12" t="n">
-        <v>781.2104789279717</v>
+        <v>777.8993134698978</v>
       </c>
       <c r="O12" t="n">
-        <v>27.95014273537743</v>
+        <v>27.89084641006611</v>
       </c>
       <c r="P12" t="n">
-        <v>372.7064885176218</v>
+        <v>372.6380259543417</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33571,28 +33719,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.529369077272421</v>
+        <v>1.528351244398177</v>
       </c>
       <c r="J13" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K13" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3019196017111185</v>
+        <v>0.3037352106922035</v>
       </c>
       <c r="M13" t="n">
-        <v>14.04864922229239</v>
+        <v>13.98725018950798</v>
       </c>
       <c r="N13" t="n">
-        <v>350.0518261256276</v>
+        <v>348.4073789132215</v>
       </c>
       <c r="O13" t="n">
-        <v>18.7096719940684</v>
+        <v>18.66567381353326</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8702076801701</v>
+        <v>390.8796576027826</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33653,28 +33801,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.635823027202633</v>
+        <v>1.638348106222508</v>
       </c>
       <c r="J14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K14" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4067287221235125</v>
+        <v>0.4098264128954734</v>
       </c>
       <c r="M14" t="n">
-        <v>12.09035754983893</v>
+        <v>12.04956078490557</v>
       </c>
       <c r="N14" t="n">
-        <v>249.5770818683803</v>
+        <v>248.4628128362321</v>
       </c>
       <c r="O14" t="n">
-        <v>15.79800879441394</v>
+        <v>15.76270322109225</v>
       </c>
       <c r="P14" t="n">
-        <v>404.408159872087</v>
+        <v>404.3845597535705</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33731,28 +33879,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.864174354080882</v>
+        <v>1.868667726407731</v>
       </c>
       <c r="J15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K15" t="n">
         <v>217</v>
       </c>
-      <c r="K15" t="n">
-        <v>216</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.4932617175898892</v>
+        <v>0.4968017355036007</v>
       </c>
       <c r="M15" t="n">
-        <v>11.47218374327915</v>
+        <v>11.4448832579658</v>
       </c>
       <c r="N15" t="n">
-        <v>227.3435848912326</v>
+        <v>226.4255798230919</v>
       </c>
       <c r="O15" t="n">
-        <v>15.07791712708465</v>
+        <v>15.04744429539754</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0938577879709</v>
+        <v>398.0517917413728</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33809,28 +33957,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.840332086398188</v>
+        <v>1.838448152764495</v>
       </c>
       <c r="J16" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K16" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5050236882057297</v>
+        <v>0.5069448312199327</v>
       </c>
       <c r="M16" t="n">
-        <v>11.15952856578245</v>
+        <v>11.11692328686995</v>
       </c>
       <c r="N16" t="n">
-        <v>214.0781438219486</v>
+        <v>213.0963411140524</v>
       </c>
       <c r="O16" t="n">
-        <v>14.63140949539547</v>
+        <v>14.59781973837369</v>
       </c>
       <c r="P16" t="n">
-        <v>398.0871005554893</v>
+        <v>398.1046868274383</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33887,28 +34035,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7044008807236</v>
+        <v>1.690137050242263</v>
       </c>
       <c r="J17" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K17" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3954172519018448</v>
+        <v>0.3926366340249466</v>
       </c>
       <c r="M17" t="n">
-        <v>13.97277824070414</v>
+        <v>13.98243409068629</v>
       </c>
       <c r="N17" t="n">
-        <v>287.7636977631004</v>
+        <v>287.7471133450061</v>
       </c>
       <c r="O17" t="n">
-        <v>16.96359919837475</v>
+        <v>16.96311036764797</v>
       </c>
       <c r="P17" t="n">
-        <v>396.1064744655734</v>
+        <v>396.2393156189839</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33965,28 +34113,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.62639807523587</v>
+        <v>1.61096615009078</v>
       </c>
       <c r="J18" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K18" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3448519127108987</v>
+        <v>0.3417066079238814</v>
       </c>
       <c r="M18" t="n">
-        <v>14.38426382592369</v>
+        <v>14.39645599613045</v>
       </c>
       <c r="N18" t="n">
-        <v>321.4537559993651</v>
+        <v>321.5032434897207</v>
       </c>
       <c r="O18" t="n">
-        <v>17.92913149038082</v>
+        <v>17.93051152337046</v>
       </c>
       <c r="P18" t="n">
-        <v>387.5059370027353</v>
+        <v>387.6500830373378</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34043,28 +34191,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.242138719431478</v>
+        <v>1.226695948479219</v>
       </c>
       <c r="J19" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K19" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2492017181145261</v>
+        <v>0.2454100081442359</v>
       </c>
       <c r="M19" t="n">
-        <v>14.51628497498594</v>
+        <v>14.52576094260844</v>
       </c>
       <c r="N19" t="n">
-        <v>298.1288117153403</v>
+        <v>298.280068855602</v>
       </c>
       <c r="O19" t="n">
-        <v>17.26640702970193</v>
+        <v>17.27078657315879</v>
       </c>
       <c r="P19" t="n">
-        <v>387.3543275834605</v>
+        <v>387.4991217608773</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34121,28 +34269,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8518440732018758</v>
+        <v>0.8375371207111391</v>
       </c>
       <c r="J20" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K20" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1246551539990017</v>
+        <v>0.1216295853635624</v>
       </c>
       <c r="M20" t="n">
-        <v>15.43171624304048</v>
+        <v>15.42135050811997</v>
       </c>
       <c r="N20" t="n">
-        <v>323.3469778252085</v>
+        <v>323.1601835653717</v>
       </c>
       <c r="O20" t="n">
-        <v>17.98185134587672</v>
+        <v>17.97665662923369</v>
       </c>
       <c r="P20" t="n">
-        <v>388.9071628706307</v>
+        <v>389.0417505037331</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34199,28 +34347,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3145198820219052</v>
+        <v>0.3088652141276979</v>
       </c>
       <c r="J21" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K21" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02197511135491348</v>
+        <v>0.02140110106786963</v>
       </c>
       <c r="M21" t="n">
-        <v>13.59760342946677</v>
+        <v>13.55430836865579</v>
       </c>
       <c r="N21" t="n">
-        <v>277.1668949085052</v>
+        <v>276.085846212921</v>
       </c>
       <c r="O21" t="n">
-        <v>16.64833009369124</v>
+        <v>16.61583119235751</v>
       </c>
       <c r="P21" t="n">
-        <v>392.2898510838036</v>
+        <v>392.3433486681122</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34277,28 +34425,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02586268516693774</v>
+        <v>0.02637541439506084</v>
       </c>
       <c r="J22" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K22" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001737583555262434</v>
+        <v>0.0001825226481944053</v>
       </c>
       <c r="M22" t="n">
-        <v>12.42126622538426</v>
+        <v>12.36717964852316</v>
       </c>
       <c r="N22" t="n">
-        <v>242.2994261277849</v>
+        <v>241.17933139007</v>
       </c>
       <c r="O22" t="n">
-        <v>15.56597013127627</v>
+        <v>15.52994949734448</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2554849417205</v>
+        <v>393.2506341218983</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34355,28 +34503,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1330904085591028</v>
+        <v>-0.1284070936334741</v>
       </c>
       <c r="J23" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K23" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005921339261902969</v>
+        <v>0.005564476012029806</v>
       </c>
       <c r="M23" t="n">
-        <v>10.90610631619415</v>
+        <v>10.88541701780565</v>
       </c>
       <c r="N23" t="n">
-        <v>188.7078854554793</v>
+        <v>187.983215607633</v>
       </c>
       <c r="O23" t="n">
-        <v>13.73709887332399</v>
+        <v>13.71069712332794</v>
       </c>
       <c r="P23" t="n">
-        <v>393.6376611376473</v>
+        <v>393.5936825285485</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34433,28 +34581,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2152708092926467</v>
+        <v>-0.2087551257603363</v>
       </c>
       <c r="J24" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K24" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01627489309026864</v>
+        <v>0.01544573562918783</v>
       </c>
       <c r="M24" t="n">
-        <v>10.84842800289417</v>
+        <v>10.83819011383638</v>
       </c>
       <c r="N24" t="n">
-        <v>177.7549172605974</v>
+        <v>177.2123735541473</v>
       </c>
       <c r="O24" t="n">
-        <v>13.33247603637814</v>
+        <v>13.31211378985874</v>
       </c>
       <c r="P24" t="n">
-        <v>393.6740329154866</v>
+        <v>393.6128474723488</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34511,28 +34659,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1197082419332253</v>
+        <v>-0.110404909991725</v>
       </c>
       <c r="J25" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K25" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L25" t="n">
-        <v>0.005885359591615291</v>
+        <v>0.005041765880378524</v>
       </c>
       <c r="M25" t="n">
-        <v>10.20640088329921</v>
+        <v>10.20149710783781</v>
       </c>
       <c r="N25" t="n">
-        <v>153.6056877494879</v>
+        <v>153.4573300785714</v>
       </c>
       <c r="O25" t="n">
-        <v>12.39377616989624</v>
+        <v>12.38778955579128</v>
       </c>
       <c r="P25" t="n">
-        <v>392.2757074041904</v>
+        <v>392.1883445842074</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34589,28 +34737,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1463880137744317</v>
+        <v>-0.1323205983138897</v>
       </c>
       <c r="J26" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K26" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L26" t="n">
-        <v>0.00888583899956974</v>
+        <v>0.007282676409002042</v>
       </c>
       <c r="M26" t="n">
-        <v>10.20355660464944</v>
+        <v>10.20728445228365</v>
       </c>
       <c r="N26" t="n">
-        <v>151.6812862674045</v>
+        <v>152.2573214911579</v>
       </c>
       <c r="O26" t="n">
-        <v>12.31589567459081</v>
+        <v>12.33925935748001</v>
       </c>
       <c r="P26" t="n">
-        <v>395.5208540753575</v>
+        <v>395.3887541898291</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34667,28 +34815,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.156238339323221</v>
+        <v>0.1719642885183945</v>
       </c>
       <c r="J27" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K27" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01020303468669459</v>
+        <v>0.01232473327402517</v>
       </c>
       <c r="M27" t="n">
-        <v>10.00341477988675</v>
+        <v>10.02655366822959</v>
       </c>
       <c r="N27" t="n">
-        <v>150.6184719297512</v>
+        <v>151.5145705233757</v>
       </c>
       <c r="O27" t="n">
-        <v>12.27267175189458</v>
+        <v>12.30912549791315</v>
       </c>
       <c r="P27" t="n">
-        <v>393.30436314094</v>
+        <v>393.156200340773</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34745,28 +34893,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3924624166544241</v>
+        <v>0.4072854975071306</v>
       </c>
       <c r="J28" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K28" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L28" t="n">
-        <v>0.05839770933263688</v>
+        <v>0.06265968790479615</v>
       </c>
       <c r="M28" t="n">
-        <v>10.06411818335939</v>
+        <v>10.08492554333032</v>
       </c>
       <c r="N28" t="n">
-        <v>158.2950102379588</v>
+        <v>158.9799662522375</v>
       </c>
       <c r="O28" t="n">
-        <v>12.58153449456619</v>
+        <v>12.60872579812241</v>
       </c>
       <c r="P28" t="n">
-        <v>391.2710782545428</v>
+        <v>391.1313751565401</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34823,28 +34971,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6342344850967062</v>
+        <v>0.6500944715485469</v>
       </c>
       <c r="J29" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K29" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1329443059430125</v>
+        <v>0.1387495280462275</v>
       </c>
       <c r="M29" t="n">
-        <v>10.54292700267545</v>
+        <v>10.57148961991686</v>
       </c>
       <c r="N29" t="n">
-        <v>167.9758138705933</v>
+        <v>168.8272683511159</v>
       </c>
       <c r="O29" t="n">
-        <v>12.96054836303593</v>
+        <v>12.99335477662008</v>
       </c>
       <c r="P29" t="n">
-        <v>381.4330919580573</v>
+        <v>381.2839530134322</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34901,28 +35049,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6651942715033231</v>
+        <v>0.6794720989277885</v>
       </c>
       <c r="J30" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K30" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1362771059196055</v>
+        <v>0.1416589607269098</v>
       </c>
       <c r="M30" t="n">
-        <v>10.85139488674521</v>
+        <v>10.86602547266896</v>
       </c>
       <c r="N30" t="n">
-        <v>177.7218370175324</v>
+        <v>178.2073655061551</v>
       </c>
       <c r="O30" t="n">
-        <v>13.33123538977286</v>
+        <v>13.34943315299025</v>
       </c>
       <c r="P30" t="n">
-        <v>373.1293788663848</v>
+        <v>372.9947200551161</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34979,28 +35127,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.590400396187284</v>
+        <v>0.6076104127725557</v>
       </c>
       <c r="J31" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K31" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L31" t="n">
-        <v>0.09433870800428823</v>
+        <v>0.09944739866102981</v>
       </c>
       <c r="M31" t="n">
-        <v>11.79223131441533</v>
+        <v>11.8246654854681</v>
       </c>
       <c r="N31" t="n">
-        <v>210.3326380401324</v>
+        <v>211.242631800286</v>
       </c>
       <c r="O31" t="n">
-        <v>14.50284930764063</v>
+        <v>14.53418837776248</v>
       </c>
       <c r="P31" t="n">
-        <v>368.6864576289664</v>
+        <v>368.522988975232</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35057,28 +35205,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4667854634625083</v>
+        <v>0.4874492738420979</v>
       </c>
       <c r="J32" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K32" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05070140586500538</v>
+        <v>0.05500087059653824</v>
       </c>
       <c r="M32" t="n">
-        <v>12.25621722000539</v>
+        <v>12.28953088633203</v>
       </c>
       <c r="N32" t="n">
-        <v>256.421825626877</v>
+        <v>257.9503943502866</v>
       </c>
       <c r="O32" t="n">
-        <v>16.01317662510712</v>
+        <v>16.06083417355047</v>
       </c>
       <c r="P32" t="n">
-        <v>368.0011910693937</v>
+        <v>367.8049166935358</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35135,28 +35283,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3690938008764204</v>
+        <v>0.3889740736210244</v>
       </c>
       <c r="J33" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K33" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05067674492040486</v>
+        <v>0.05567678462090508</v>
       </c>
       <c r="M33" t="n">
-        <v>10.02075031589995</v>
+        <v>10.07683826367407</v>
       </c>
       <c r="N33" t="n">
-        <v>160.7313050252033</v>
+        <v>162.4730779811962</v>
       </c>
       <c r="O33" t="n">
-        <v>12.67798505383262</v>
+        <v>12.74649277178614</v>
       </c>
       <c r="P33" t="n">
-        <v>369.8246204106717</v>
+        <v>369.6354475094538</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35213,28 +35361,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.333815042656912</v>
+        <v>0.3559883402794113</v>
       </c>
       <c r="J34" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K34" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02846173815501118</v>
+        <v>0.03214537591745026</v>
       </c>
       <c r="M34" t="n">
-        <v>12.29528252710455</v>
+        <v>12.33552079495203</v>
       </c>
       <c r="N34" t="n">
-        <v>241.0844343983694</v>
+        <v>243.1088289392082</v>
       </c>
       <c r="O34" t="n">
-        <v>15.52689390697217</v>
+        <v>15.59194756722867</v>
       </c>
       <c r="P34" t="n">
-        <v>365.4078707442445</v>
+        <v>365.1986786334005</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35291,28 +35439,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0001657761329022268</v>
+        <v>0.02835617328806328</v>
       </c>
       <c r="J35" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K35" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L35" t="n">
-        <v>6.660511697731408e-09</v>
+        <v>0.0001930086127701625</v>
       </c>
       <c r="M35" t="n">
-        <v>12.72334971152468</v>
+        <v>12.79305927195939</v>
       </c>
       <c r="N35" t="n">
-        <v>261.5141932291779</v>
+        <v>265.382503640561</v>
       </c>
       <c r="O35" t="n">
-        <v>16.17140047210438</v>
+        <v>16.29056486560736</v>
       </c>
       <c r="P35" t="n">
-        <v>371.1027509274449</v>
+        <v>370.8367909973155</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35369,28 +35517,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2315149193391493</v>
+        <v>0.2516913607317711</v>
       </c>
       <c r="J36" t="n">
+        <v>218</v>
+      </c>
+      <c r="K36" t="n">
         <v>217</v>
       </c>
-      <c r="K36" t="n">
-        <v>216</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.01173414990797406</v>
+        <v>0.01384940518317812</v>
       </c>
       <c r="M36" t="n">
-        <v>12.70787206374357</v>
+        <v>12.76636461504648</v>
       </c>
       <c r="N36" t="n">
-        <v>284.7901989617305</v>
+        <v>286.076150214861</v>
       </c>
       <c r="O36" t="n">
-        <v>16.87572810167699</v>
+        <v>16.9137858037419</v>
       </c>
       <c r="P36" t="n">
-        <v>369.6710261781213</v>
+        <v>369.4803181429501</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35447,28 +35595,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3046234543259591</v>
+        <v>0.3187314761493974</v>
       </c>
       <c r="J37" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K37" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02660299410071765</v>
+        <v>0.02916690328310745</v>
       </c>
       <c r="M37" t="n">
-        <v>11.00025444995958</v>
+        <v>11.02146720237916</v>
       </c>
       <c r="N37" t="n">
-        <v>217.4776226675026</v>
+        <v>217.733647178661</v>
       </c>
       <c r="O37" t="n">
-        <v>14.74712252161426</v>
+        <v>14.75580045875726</v>
       </c>
       <c r="P37" t="n">
-        <v>376.6640605476764</v>
+        <v>376.5321614730959</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35525,28 +35673,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.02966472973151407</v>
+        <v>0.05573132878006377</v>
       </c>
       <c r="J38" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K38" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0001678685955656123</v>
+        <v>0.0005903854204935</v>
       </c>
       <c r="M38" t="n">
-        <v>13.64285403130041</v>
+        <v>13.73829195499862</v>
       </c>
       <c r="N38" t="n">
-        <v>331.9670974142439</v>
+        <v>334.7595946299004</v>
       </c>
       <c r="O38" t="n">
-        <v>18.21996425392333</v>
+        <v>18.29643666482357</v>
       </c>
       <c r="P38" t="n">
-        <v>377.359735567032</v>
+        <v>377.1132912483686</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -35603,28 +35751,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07946325628572996</v>
+        <v>0.09778205571086374</v>
       </c>
       <c r="J39" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K39" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" t="n">
-        <v>0.00169475151154852</v>
+        <v>0.002566316183489237</v>
       </c>
       <c r="M39" t="n">
-        <v>11.9364846497463</v>
+        <v>11.99174915594343</v>
       </c>
       <c r="N39" t="n">
-        <v>236.049850940901</v>
+        <v>237.0730794649028</v>
       </c>
       <c r="O39" t="n">
-        <v>15.36391391999125</v>
+        <v>15.39717764607861</v>
       </c>
       <c r="P39" t="n">
-        <v>389.239258851187</v>
+        <v>389.0661841764745</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -35681,28 +35829,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.03975181256883376</v>
+        <v>0.06021279995368049</v>
       </c>
       <c r="J40" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K40" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L40" t="n">
-        <v>0.000417659856441488</v>
+        <v>0.000956603808644263</v>
       </c>
       <c r="M40" t="n">
-        <v>12.01660776546759</v>
+        <v>12.05932503790843</v>
       </c>
       <c r="N40" t="n">
-        <v>241.6197072481555</v>
+        <v>243.1614990995212</v>
       </c>
       <c r="O40" t="n">
-        <v>15.54412130833247</v>
+        <v>15.59363649375992</v>
       </c>
       <c r="P40" t="n">
-        <v>399.1148837353156</v>
+        <v>398.9219390468585</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -35759,28 +35907,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1420440447697041</v>
+        <v>0.1647123329377525</v>
       </c>
       <c r="J41" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K41" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" t="n">
-        <v>0.004908406989497904</v>
+        <v>0.006571316717096432</v>
       </c>
       <c r="M41" t="n">
-        <v>12.89184366109418</v>
+        <v>12.92541367420346</v>
       </c>
       <c r="N41" t="n">
-        <v>261.3311587966351</v>
+        <v>263.3913156522252</v>
       </c>
       <c r="O41" t="n">
-        <v>16.1657402798831</v>
+        <v>16.22933503419734</v>
       </c>
       <c r="P41" t="n">
-        <v>402.8718628118724</v>
+        <v>402.6581035383743</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -35837,28 +35985,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.340307241925158</v>
+        <v>0.3503367475712391</v>
       </c>
       <c r="J42" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K42" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02494234773890414</v>
+        <v>0.02659746934407059</v>
       </c>
       <c r="M42" t="n">
-        <v>13.28989767876199</v>
+        <v>13.26827390674628</v>
       </c>
       <c r="N42" t="n">
-        <v>284.4773967078829</v>
+        <v>283.7308573727195</v>
       </c>
       <c r="O42" t="n">
-        <v>16.8664577403758</v>
+        <v>16.8443123152214</v>
       </c>
       <c r="P42" t="n">
-        <v>404.8239822218752</v>
+        <v>404.7279617571401</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -35915,28 +36063,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4286235719160422</v>
+        <v>0.4368937444072186</v>
       </c>
       <c r="J43" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K43" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L43" t="n">
-        <v>0.03890700536364367</v>
+        <v>0.04068944305469357</v>
       </c>
       <c r="M43" t="n">
-        <v>13.22461907258515</v>
+        <v>13.20536966940118</v>
       </c>
       <c r="N43" t="n">
-        <v>291.4997034714013</v>
+        <v>290.5465752024853</v>
       </c>
       <c r="O43" t="n">
-        <v>17.07336239501175</v>
+        <v>17.04542681197761</v>
       </c>
       <c r="P43" t="n">
-        <v>406.4228902690542</v>
+        <v>406.345197340972</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -35974,7 +36122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR218"/>
+  <dimension ref="A1:AR219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83777,6 +83925,228 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-34.467988768766844,172.66426410957524</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>-34.46758304549946,172.66505479197846</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-34.46710678194436,172.66575308502487</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-34.466589256719125,172.6663973375266</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-34.466044125150134,172.66700294896484</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-34.46549284862889,172.6675942127917</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-34.4646217026099,172.6678097697141</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-34.464333556172065,172.6687253895869</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-34.463976750950266,172.66955929743824</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-34.46341507427627,172.670149367682</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-34.462500626003475,172.6703195676233</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>-34.46184732939004,172.67070306149222</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-34.461275426202306,172.67090691080418</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-34.46065923849717,172.67114636308054</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-34.459988080490234,172.67153610650564</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>-34.45935423202094,172.67204976035993</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>-34.4586948322559,172.67247858714722</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>-34.45803006463409,172.67288960842703</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>-34.45735644740422,172.67327126243418</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>-34.45666171721042,172.67358282684108</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>-34.45596346852785,172.6738827268869</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>-34.45526339610731,172.6741765902935</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>-34.454566738099714,172.6744818110217</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>-34.45385645523063,172.67474180816336</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>-34.45313458127841,172.67496333557602</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>-34.452414303963074,172.67519018464517</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>-34.45173385158758,172.6754532974151</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>-34.451056814360385,172.6756747495451</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>-34.45035609470428,172.67594276269875</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>-34.44963403333075,172.67614569812466</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>-34.44890652682373,172.67631497612086</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>-34.448182605255504,172.67650647817752</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>-34.447459333404055,172.67670204000785</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>-34.44672517790218,172.6768302893437</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>-34.44600591619507,172.67705074546504</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>-34.44527575365322,172.67720378296335</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>-34.44453545010643,172.67729410459836</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>-34.44380130400933,172.6774225698096</t>
+        </is>
+      </c>
+      <c r="AN219" t="inlineStr">
+        <is>
+          <t>-34.44306853312591,172.6774689161952</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>-34.44234101381449,172.67749073508955</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>-34.441618360981096,172.67768804800798</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>-34.44088096429031,172.67777823718384</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR219"/>
+  <dimension ref="A1:AR220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30404,19 +30404,19 @@
         <v>402.81</v>
       </c>
       <c r="AH219" t="n">
-        <v>400.46</v>
+        <v>405.06</v>
       </c>
       <c r="AI219" t="n">
         <v>404.41</v>
       </c>
       <c r="AJ219" t="n">
-        <v>399.73</v>
+        <v>404.86</v>
       </c>
       <c r="AK219" t="n">
-        <v>401.36</v>
+        <v>406.9</v>
       </c>
       <c r="AL219" t="n">
-        <v>408.86</v>
+        <v>413.05</v>
       </c>
       <c r="AM219" t="n">
         <v>412.79</v>
@@ -30428,12 +30428,150 @@
         <v>433.18</v>
       </c>
       <c r="AP219" t="n">
-        <v>425.34</v>
+        <v>433.19</v>
       </c>
       <c r="AQ219" t="n">
-        <v>427.47</v>
+        <v>435</v>
       </c>
       <c r="AR219" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="C220" t="n">
+        <v>356.31</v>
+      </c>
+      <c r="D220" t="n">
+        <v>345.4</v>
+      </c>
+      <c r="E220" t="n">
+        <v>340.84</v>
+      </c>
+      <c r="F220" t="n">
+        <v>339.79</v>
+      </c>
+      <c r="G220" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="H220" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="I220" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="J220" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="K220" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="L220" t="n">
+        <v>402.92</v>
+      </c>
+      <c r="M220" t="n">
+        <v>433.87</v>
+      </c>
+      <c r="N220" t="n">
+        <v>452.61</v>
+      </c>
+      <c r="O220" t="n">
+        <v>454.07</v>
+      </c>
+      <c r="P220" t="n">
+        <v>446.14</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>422.59</v>
+      </c>
+      <c r="R220" t="n">
+        <v>413.19</v>
+      </c>
+      <c r="S220" t="n">
+        <v>402.38</v>
+      </c>
+      <c r="T220" t="n">
+        <v>395.24</v>
+      </c>
+      <c r="U220" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="V220" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="W220" t="n">
+        <v>394.56</v>
+      </c>
+      <c r="X220" t="n">
+        <v>395.83</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>401.37</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>409.6</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>417.89</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>421.21</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>418.81</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>412.87</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>408.23</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>410.11</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>409.31</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>409.96</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>413.68</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>420.81</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>420.24</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>431.34</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>438.3</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>437.98</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>440.5</v>
+      </c>
+      <c r="AR220" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30450,7 +30588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32673,6 +32811,16 @@
       </c>
       <c r="B222" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>-0.51</v>
       </c>
     </row>
   </sheetData>
@@ -32841,28 +32989,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01199810195406654</v>
+        <v>0.01379427950629366</v>
       </c>
       <c r="J2" t="n">
+        <v>219</v>
+      </c>
+      <c r="K2" t="n">
         <v>218</v>
       </c>
-      <c r="K2" t="n">
-        <v>217</v>
-      </c>
       <c r="L2" t="n">
-        <v>9.664054540559075e-05</v>
+        <v>0.0001289689679667694</v>
       </c>
       <c r="M2" t="n">
-        <v>7.065486173331119</v>
+        <v>7.043242047992839</v>
       </c>
       <c r="N2" t="n">
-        <v>95.21873206200277</v>
+        <v>94.8029660967693</v>
       </c>
       <c r="O2" t="n">
-        <v>9.758008611494599</v>
+        <v>9.736681472492016</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6390081314042</v>
+        <v>376.6220622676236</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32919,28 +33067,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3571301901382167</v>
+        <v>0.3526189905339779</v>
       </c>
       <c r="J3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04995436774004369</v>
+        <v>0.04917813498783952</v>
       </c>
       <c r="M3" t="n">
-        <v>9.501952175680684</v>
+        <v>9.478675799941595</v>
       </c>
       <c r="N3" t="n">
-        <v>155.7613343635039</v>
+        <v>155.1768409116526</v>
       </c>
       <c r="O3" t="n">
-        <v>12.48043806777246</v>
+        <v>12.4569996753493</v>
       </c>
       <c r="P3" t="n">
-        <v>352.2219007043581</v>
+        <v>352.264367729229</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32997,28 +33145,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0210818011721513</v>
+        <v>0.01524966224808513</v>
       </c>
       <c r="J4" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K4" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002243534098335109</v>
+        <v>0.000118358559761722</v>
       </c>
       <c r="M4" t="n">
-        <v>9.265087397296298</v>
+        <v>9.248507297739502</v>
       </c>
       <c r="N4" t="n">
-        <v>127.6330063405233</v>
+        <v>127.2647794073128</v>
       </c>
       <c r="O4" t="n">
-        <v>11.29747787519512</v>
+        <v>11.28116923937022</v>
       </c>
       <c r="P4" t="n">
-        <v>351.8261847858598</v>
+        <v>351.880917141332</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33075,28 +33223,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3815286967969012</v>
+        <v>-0.3862467191610472</v>
       </c>
       <c r="J5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K5" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05603113698662709</v>
+        <v>0.05783078761423466</v>
       </c>
       <c r="M5" t="n">
-        <v>10.54892129718702</v>
+        <v>10.51754693748892</v>
       </c>
       <c r="N5" t="n">
-        <v>157.144524513603</v>
+        <v>156.5616259095684</v>
       </c>
       <c r="O5" t="n">
-        <v>12.53572991546974</v>
+        <v>12.51245882748744</v>
       </c>
       <c r="P5" t="n">
-        <v>356.6263606748145</v>
+        <v>356.6708393020002</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33153,28 +33301,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6444007744186723</v>
+        <v>-0.6491186698991898</v>
       </c>
       <c r="J6" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K6" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1207670867460744</v>
+        <v>0.1233080815435879</v>
       </c>
       <c r="M6" t="n">
-        <v>11.59660262386332</v>
+        <v>11.5602439448666</v>
       </c>
       <c r="N6" t="n">
-        <v>192.8584616351978</v>
+        <v>192.1135360810632</v>
       </c>
       <c r="O6" t="n">
-        <v>13.88734897794384</v>
+        <v>13.86050273550939</v>
       </c>
       <c r="P6" t="n">
-        <v>362.564260442203</v>
+        <v>362.6088357556423</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33231,28 +33379,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6026324847237997</v>
+        <v>-0.6076057237401656</v>
       </c>
       <c r="J7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09771858279065204</v>
+        <v>0.09999575163497665</v>
       </c>
       <c r="M7" t="n">
-        <v>12.19485299652374</v>
+        <v>12.15911325140284</v>
       </c>
       <c r="N7" t="n">
-        <v>213.9149679839845</v>
+        <v>213.0889972158353</v>
       </c>
       <c r="O7" t="n">
-        <v>14.62583221509069</v>
+        <v>14.59756819527949</v>
       </c>
       <c r="P7" t="n">
-        <v>364.8039499427674</v>
+        <v>364.8509377764061</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33309,28 +33457,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01610286896098015</v>
+        <v>0.02323445236749181</v>
       </c>
       <c r="J8" t="n">
+        <v>219</v>
+      </c>
+      <c r="K8" t="n">
         <v>218</v>
       </c>
-      <c r="K8" t="n">
-        <v>217</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0003086393732684156</v>
+        <v>0.0006447425664635187</v>
       </c>
       <c r="M8" t="n">
-        <v>5.437483715800369</v>
+        <v>5.452067154956974</v>
       </c>
       <c r="N8" t="n">
-        <v>53.76831373067269</v>
+        <v>53.85139497143246</v>
       </c>
       <c r="O8" t="n">
-        <v>7.332688029002235</v>
+        <v>7.338350970853905</v>
       </c>
       <c r="P8" t="n">
-        <v>387.951676182669</v>
+        <v>387.8846208544758</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33391,28 +33539,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3384083936898392</v>
+        <v>-0.3331130699832879</v>
       </c>
       <c r="J9" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1144670967649392</v>
+        <v>0.1119748499175032</v>
       </c>
       <c r="M9" t="n">
-        <v>5.356140892534343</v>
+        <v>5.359745318639439</v>
       </c>
       <c r="N9" t="n">
-        <v>56.91287530194795</v>
+        <v>56.83224082515893</v>
       </c>
       <c r="O9" t="n">
-        <v>7.544062254644241</v>
+        <v>7.538716125784212</v>
       </c>
       <c r="P9" t="n">
-        <v>364.0417348978049</v>
+        <v>363.9920976216271</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33473,28 +33621,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3416135709631805</v>
+        <v>-0.3316069852082126</v>
       </c>
       <c r="J10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03965922777761066</v>
+        <v>0.03768109137878561</v>
       </c>
       <c r="M10" t="n">
-        <v>10.39152414843627</v>
+        <v>10.39580305127685</v>
       </c>
       <c r="N10" t="n">
-        <v>180.8077993750829</v>
+        <v>180.6215789314737</v>
       </c>
       <c r="O10" t="n">
-        <v>13.44647906981909</v>
+        <v>13.43955278018855</v>
       </c>
       <c r="P10" t="n">
-        <v>333.0613075227155</v>
+        <v>332.9667814152327</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33555,28 +33703,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1867920229866635</v>
+        <v>-0.1810595651831793</v>
       </c>
       <c r="J11" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002289023058927309</v>
+        <v>0.002171495600345574</v>
       </c>
       <c r="M11" t="n">
-        <v>23.767671738565</v>
+        <v>23.68596013035511</v>
       </c>
       <c r="N11" t="n">
-        <v>992.5660336409114</v>
+        <v>988.0372216465204</v>
       </c>
       <c r="O11" t="n">
-        <v>31.50501600762824</v>
+        <v>31.43305937459032</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3058119821005</v>
+        <v>343.2518689808821</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33637,28 +33785,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8156528317767103</v>
+        <v>0.822801834989809</v>
       </c>
       <c r="J12" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05273480818953025</v>
+        <v>0.05409134510672475</v>
       </c>
       <c r="M12" t="n">
-        <v>20.77485756952037</v>
+        <v>20.71757515946306</v>
       </c>
       <c r="N12" t="n">
-        <v>777.8993134698978</v>
+        <v>774.6032587743371</v>
       </c>
       <c r="O12" t="n">
-        <v>27.89084641006611</v>
+        <v>27.83169521919815</v>
       </c>
       <c r="P12" t="n">
-        <v>372.6380259543417</v>
+        <v>372.5712782965227</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33719,28 +33867,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.528351244398177</v>
+        <v>1.5302923552476</v>
       </c>
       <c r="J13" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3037352106922035</v>
+        <v>0.3063584425354694</v>
       </c>
       <c r="M13" t="n">
-        <v>13.98725018950798</v>
+        <v>13.93381559658519</v>
       </c>
       <c r="N13" t="n">
-        <v>348.4073789132215</v>
+        <v>346.7964163164395</v>
       </c>
       <c r="O13" t="n">
-        <v>18.66567381353326</v>
+        <v>18.62247073608761</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8796576027826</v>
+        <v>390.8615548438289</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33801,28 +33949,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.638348106222508</v>
+        <v>1.642204909933318</v>
       </c>
       <c r="J14" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K14" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4098264128954734</v>
+        <v>0.4132586112599123</v>
       </c>
       <c r="M14" t="n">
-        <v>12.04956078490557</v>
+        <v>12.01703202772874</v>
       </c>
       <c r="N14" t="n">
-        <v>248.4628128362321</v>
+        <v>247.414806568423</v>
       </c>
       <c r="O14" t="n">
-        <v>15.76270322109225</v>
+        <v>15.72942486451501</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3845597535705</v>
+        <v>404.3483546539396</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33879,28 +34027,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.868667726407731</v>
+        <v>1.873924172794476</v>
       </c>
       <c r="J15" t="n">
+        <v>219</v>
+      </c>
+      <c r="K15" t="n">
         <v>218</v>
       </c>
-      <c r="K15" t="n">
-        <v>217</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.4968017355036007</v>
+        <v>0.5004770921453283</v>
       </c>
       <c r="M15" t="n">
-        <v>11.4448832579658</v>
+        <v>11.4219249803009</v>
       </c>
       <c r="N15" t="n">
-        <v>226.4255798230919</v>
+        <v>225.5660587005901</v>
       </c>
       <c r="O15" t="n">
-        <v>15.04744429539754</v>
+        <v>15.01885677075955</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0517917413728</v>
+        <v>398.0023675507686</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33957,28 +34105,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.838448152764495</v>
+        <v>1.837710252039679</v>
       </c>
       <c r="J16" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K16" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5069448312199327</v>
+        <v>0.5091898568880514</v>
       </c>
       <c r="M16" t="n">
-        <v>11.11692328686995</v>
+        <v>11.0687624538907</v>
       </c>
       <c r="N16" t="n">
-        <v>213.0963411140524</v>
+        <v>212.1041654327321</v>
       </c>
       <c r="O16" t="n">
-        <v>14.59781973837369</v>
+        <v>14.56379639492162</v>
       </c>
       <c r="P16" t="n">
-        <v>398.1046868274383</v>
+        <v>398.1116059328301</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34035,28 +34183,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.690137050242263</v>
+        <v>1.674596722116738</v>
       </c>
       <c r="J17" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K17" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3926366340249466</v>
+        <v>0.3892374746097345</v>
       </c>
       <c r="M17" t="n">
-        <v>13.98243409068629</v>
+        <v>13.99812772537186</v>
       </c>
       <c r="N17" t="n">
-        <v>287.7471133450061</v>
+        <v>288.0025641770137</v>
       </c>
       <c r="O17" t="n">
-        <v>16.96311036764797</v>
+        <v>16.97063829609876</v>
       </c>
       <c r="P17" t="n">
-        <v>396.2393156189839</v>
+        <v>396.3846994958816</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34113,28 +34261,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.61096615009078</v>
+        <v>1.596501627892762</v>
       </c>
       <c r="J18" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K18" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3417066079238814</v>
+        <v>0.3389176593561224</v>
       </c>
       <c r="M18" t="n">
-        <v>14.39645599613045</v>
+        <v>14.40301809510892</v>
       </c>
       <c r="N18" t="n">
-        <v>321.5032434897207</v>
+        <v>321.3854628360696</v>
       </c>
       <c r="O18" t="n">
-        <v>17.93051152337046</v>
+        <v>17.92722685849849</v>
       </c>
       <c r="P18" t="n">
-        <v>387.6500830373378</v>
+        <v>387.785786075796</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34191,28 +34339,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.226695948479219</v>
+        <v>1.211812936882152</v>
       </c>
       <c r="J19" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K19" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2454100081442359</v>
+        <v>0.2418212229550649</v>
       </c>
       <c r="M19" t="n">
-        <v>14.52576094260844</v>
+        <v>14.53182931974137</v>
       </c>
       <c r="N19" t="n">
-        <v>298.280068855602</v>
+        <v>298.3402535494919</v>
       </c>
       <c r="O19" t="n">
-        <v>17.27078657315879</v>
+        <v>17.27252886955155</v>
       </c>
       <c r="P19" t="n">
-        <v>387.4991217608773</v>
+        <v>387.6392894537584</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34269,28 +34417,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8375371207111391</v>
+        <v>0.8240469211954923</v>
       </c>
       <c r="J20" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K20" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1216295853635624</v>
+        <v>0.118852960012969</v>
       </c>
       <c r="M20" t="n">
-        <v>15.42135050811997</v>
+        <v>15.40831293987833</v>
       </c>
       <c r="N20" t="n">
-        <v>323.1601835653717</v>
+        <v>322.8468618548657</v>
       </c>
       <c r="O20" t="n">
-        <v>17.97665662923369</v>
+        <v>17.96793983334944</v>
       </c>
       <c r="P20" t="n">
-        <v>389.0417505037331</v>
+        <v>389.1692077300011</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34347,28 +34495,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3088652141276979</v>
+        <v>0.3037452664754938</v>
       </c>
       <c r="J21" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K21" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02140110106786963</v>
+        <v>0.02090176259637266</v>
       </c>
       <c r="M21" t="n">
-        <v>13.55430836865579</v>
+        <v>13.50937342644555</v>
       </c>
       <c r="N21" t="n">
-        <v>276.085846212921</v>
+        <v>274.9808524478826</v>
       </c>
       <c r="O21" t="n">
-        <v>16.61583119235751</v>
+        <v>16.58254662130888</v>
       </c>
       <c r="P21" t="n">
-        <v>392.3433486681122</v>
+        <v>392.3919962770424</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34425,28 +34573,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02637541439506084</v>
+        <v>0.02678769996207939</v>
       </c>
       <c r="J22" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K22" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001825226481944053</v>
+        <v>0.0001901482162423029</v>
       </c>
       <c r="M22" t="n">
-        <v>12.36717964852316</v>
+        <v>12.31290620984809</v>
       </c>
       <c r="N22" t="n">
-        <v>241.17933139007</v>
+        <v>240.0689906716855</v>
       </c>
       <c r="O22" t="n">
-        <v>15.52994949734448</v>
+        <v>15.49415988918681</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2506341218983</v>
+        <v>393.2467167562543</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34503,28 +34651,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1284070936334741</v>
+        <v>-0.1247517073389631</v>
       </c>
       <c r="J23" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K23" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005564476012029806</v>
+        <v>0.005303036102387249</v>
       </c>
       <c r="M23" t="n">
-        <v>10.88541701780565</v>
+        <v>10.85834734846034</v>
       </c>
       <c r="N23" t="n">
-        <v>187.983215607633</v>
+        <v>187.211525637098</v>
       </c>
       <c r="O23" t="n">
-        <v>13.71069712332794</v>
+        <v>13.68252628855863</v>
       </c>
       <c r="P23" t="n">
-        <v>393.5936825285485</v>
+        <v>393.5592076373145</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34581,28 +34729,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2087551257603363</v>
+        <v>-0.202276826198121</v>
       </c>
       <c r="J24" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K24" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01544573562918783</v>
+        <v>0.01463479610515683</v>
       </c>
       <c r="M24" t="n">
-        <v>10.83819011383638</v>
+        <v>10.8275546465937</v>
       </c>
       <c r="N24" t="n">
-        <v>177.2123735541473</v>
+        <v>176.6754414684104</v>
       </c>
       <c r="O24" t="n">
-        <v>13.31211378985874</v>
+        <v>13.29193144236045</v>
       </c>
       <c r="P24" t="n">
-        <v>393.6128474723488</v>
+        <v>393.5517489577747</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34659,28 +34807,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.110404909991725</v>
+        <v>-0.1003128797074534</v>
       </c>
       <c r="J25" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K25" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L25" t="n">
-        <v>0.005041765880378524</v>
+        <v>0.004188797560956581</v>
       </c>
       <c r="M25" t="n">
-        <v>10.20149710783781</v>
+        <v>10.20166450076367</v>
       </c>
       <c r="N25" t="n">
-        <v>153.4573300785714</v>
+        <v>153.4173261620025</v>
       </c>
       <c r="O25" t="n">
-        <v>12.38778955579128</v>
+        <v>12.3861747994287</v>
       </c>
       <c r="P25" t="n">
-        <v>392.1883445842074</v>
+        <v>392.0931640428503</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34737,28 +34885,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1323205983138897</v>
+        <v>-0.1175502481912824</v>
       </c>
       <c r="J26" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K26" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L26" t="n">
-        <v>0.007282676409002042</v>
+        <v>0.005759500188482036</v>
       </c>
       <c r="M26" t="n">
-        <v>10.20728445228365</v>
+        <v>10.21300235866754</v>
       </c>
       <c r="N26" t="n">
-        <v>152.2573214911579</v>
+        <v>152.9773493791197</v>
       </c>
       <c r="O26" t="n">
-        <v>12.33925935748001</v>
+        <v>12.36840124588137</v>
       </c>
       <c r="P26" t="n">
-        <v>395.3887541898291</v>
+        <v>395.249451207069</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34815,28 +34963,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1719642885183945</v>
+        <v>0.1888315821839885</v>
       </c>
       <c r="J27" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K27" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01232473327402517</v>
+        <v>0.01478841890743532</v>
       </c>
       <c r="M27" t="n">
-        <v>10.02655366822959</v>
+        <v>10.05432034999506</v>
       </c>
       <c r="N27" t="n">
-        <v>151.5145705233757</v>
+        <v>152.6670223320605</v>
       </c>
       <c r="O27" t="n">
-        <v>12.30912549791315</v>
+        <v>12.35584972116692</v>
       </c>
       <c r="P27" t="n">
-        <v>393.156200340773</v>
+        <v>392.9965853786542</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34893,28 +35041,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4072854975071306</v>
+        <v>0.423385259384964</v>
       </c>
       <c r="J28" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K28" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06265968790479615</v>
+        <v>0.06731647872840008</v>
       </c>
       <c r="M28" t="n">
-        <v>10.08492554333032</v>
+        <v>10.11076113073814</v>
       </c>
       <c r="N28" t="n">
-        <v>158.9799662522375</v>
+        <v>159.9366867093522</v>
       </c>
       <c r="O28" t="n">
-        <v>12.60872579812241</v>
+        <v>12.6466077154845</v>
       </c>
       <c r="P28" t="n">
-        <v>391.1313751565401</v>
+        <v>390.978968005863</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34971,28 +35119,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6500944715485469</v>
+        <v>0.6670167599536967</v>
       </c>
       <c r="J29" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K29" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1387495280462275</v>
+        <v>0.1448361985078762</v>
       </c>
       <c r="M29" t="n">
-        <v>10.57148961991686</v>
+        <v>10.60430574501257</v>
       </c>
       <c r="N29" t="n">
-        <v>168.8272683511159</v>
+        <v>169.9227359693983</v>
       </c>
       <c r="O29" t="n">
-        <v>12.99335477662008</v>
+        <v>13.03544153335046</v>
       </c>
       <c r="P29" t="n">
-        <v>381.2839530134322</v>
+        <v>381.1241146211763</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35049,28 +35197,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6794720989277885</v>
+        <v>0.6977231152014436</v>
       </c>
       <c r="J30" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K30" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1416589607269098</v>
+        <v>0.1479437381108445</v>
       </c>
       <c r="M30" t="n">
-        <v>10.86602547266896</v>
+        <v>10.89841824551641</v>
       </c>
       <c r="N30" t="n">
-        <v>178.2073655061551</v>
+        <v>179.5439023951218</v>
       </c>
       <c r="O30" t="n">
-        <v>13.34943315299025</v>
+        <v>13.39939932963869</v>
       </c>
       <c r="P30" t="n">
-        <v>372.9947200551161</v>
+        <v>372.8218377926288</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35127,28 +35275,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6076104127725557</v>
+        <v>0.6316362523120087</v>
       </c>
       <c r="J31" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K31" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L31" t="n">
-        <v>0.09944739866102981</v>
+        <v>0.10588854319987</v>
       </c>
       <c r="M31" t="n">
-        <v>11.8246654854681</v>
+        <v>11.89119393945357</v>
       </c>
       <c r="N31" t="n">
-        <v>211.242631800286</v>
+        <v>213.9746542807502</v>
       </c>
       <c r="O31" t="n">
-        <v>14.53418837776248</v>
+        <v>14.62787251382614</v>
       </c>
       <c r="P31" t="n">
-        <v>368.522988975232</v>
+        <v>368.2937927189369</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35205,28 +35353,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4874492738420979</v>
+        <v>0.5136712366173428</v>
       </c>
       <c r="J32" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K32" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L32" t="n">
-        <v>0.05500087059653824</v>
+        <v>0.06029940603717621</v>
       </c>
       <c r="M32" t="n">
-        <v>12.28953088633203</v>
+        <v>12.34755731971548</v>
       </c>
       <c r="N32" t="n">
-        <v>257.9503943502866</v>
+        <v>261.1755473013039</v>
       </c>
       <c r="O32" t="n">
-        <v>16.06083417355047</v>
+        <v>16.16092656072986</v>
       </c>
       <c r="P32" t="n">
-        <v>367.8049166935358</v>
+        <v>367.5547703587563</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35283,28 +35431,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3889740736210244</v>
+        <v>0.4130190018312261</v>
       </c>
       <c r="J33" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K33" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L33" t="n">
-        <v>0.05567678462090508</v>
+        <v>0.06159516461158843</v>
       </c>
       <c r="M33" t="n">
-        <v>10.07683826367407</v>
+        <v>10.15396105621306</v>
       </c>
       <c r="N33" t="n">
-        <v>162.4730779811962</v>
+        <v>165.4020178593759</v>
       </c>
       <c r="O33" t="n">
-        <v>12.74649277178614</v>
+        <v>12.86087158241524</v>
       </c>
       <c r="P33" t="n">
-        <v>369.6354475094538</v>
+        <v>369.4056455524168</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35361,28 +35509,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3559883402794113</v>
+        <v>0.3896135577518814</v>
       </c>
       <c r="J34" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K34" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L34" t="n">
-        <v>0.03214537591745026</v>
+        <v>0.03759488058791249</v>
       </c>
       <c r="M34" t="n">
-        <v>12.33552079495203</v>
+        <v>12.4287550807326</v>
       </c>
       <c r="N34" t="n">
-        <v>243.1088289392082</v>
+        <v>248.8887262903929</v>
       </c>
       <c r="O34" t="n">
-        <v>15.59194756722867</v>
+        <v>15.77620760165107</v>
       </c>
       <c r="P34" t="n">
-        <v>365.1986786334005</v>
+        <v>364.8802190711381</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35439,28 +35587,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02835617328806328</v>
+        <v>0.06005995131308317</v>
       </c>
       <c r="J35" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K35" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0001930086127701625</v>
+        <v>0.0008529162200950902</v>
       </c>
       <c r="M35" t="n">
-        <v>12.79305927195939</v>
+        <v>12.89114564882066</v>
       </c>
       <c r="N35" t="n">
-        <v>265.382503640561</v>
+        <v>270.6455504756088</v>
       </c>
       <c r="O35" t="n">
-        <v>16.29056486560736</v>
+        <v>16.45130847305493</v>
       </c>
       <c r="P35" t="n">
-        <v>370.8367909973155</v>
+        <v>370.5363778610038</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35517,28 +35665,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2516913607317711</v>
+        <v>0.2842536447141882</v>
       </c>
       <c r="J36" t="n">
+        <v>219</v>
+      </c>
+      <c r="K36" t="n">
         <v>218</v>
       </c>
-      <c r="K36" t="n">
-        <v>217</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.01384940518317812</v>
+        <v>0.01738693472002084</v>
       </c>
       <c r="M36" t="n">
-        <v>12.76636461504648</v>
+        <v>12.90229707767209</v>
       </c>
       <c r="N36" t="n">
-        <v>286.076150214861</v>
+        <v>291.1282757944304</v>
       </c>
       <c r="O36" t="n">
-        <v>16.9137858037419</v>
+        <v>17.06248152510151</v>
       </c>
       <c r="P36" t="n">
-        <v>369.4803181429501</v>
+        <v>369.1713836745828</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35595,28 +35743,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3187314761493974</v>
+        <v>0.3475347554766827</v>
       </c>
       <c r="J37" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K37" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02916690328310745</v>
+        <v>0.03409767812659525</v>
       </c>
       <c r="M37" t="n">
-        <v>11.02146720237916</v>
+        <v>11.13765623277438</v>
       </c>
       <c r="N37" t="n">
-        <v>217.733647178661</v>
+        <v>221.4674668932188</v>
       </c>
       <c r="O37" t="n">
-        <v>14.75580045875726</v>
+        <v>14.8817830549037</v>
       </c>
       <c r="P37" t="n">
-        <v>376.5321614730959</v>
+        <v>376.2618783330814</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35673,28 +35821,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.05573132878006377</v>
+        <v>0.09481860070887557</v>
       </c>
       <c r="J38" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K38" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0005903854204935</v>
+        <v>0.001676666850112141</v>
       </c>
       <c r="M38" t="n">
-        <v>13.73829195499862</v>
+        <v>13.91142772902197</v>
       </c>
       <c r="N38" t="n">
-        <v>334.7595946299004</v>
+        <v>342.6094107688524</v>
       </c>
       <c r="O38" t="n">
-        <v>18.29643666482357</v>
+        <v>18.50971125568555</v>
       </c>
       <c r="P38" t="n">
-        <v>377.1132912483686</v>
+        <v>376.7422732533578</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -35751,28 +35899,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09778205571086374</v>
+        <v>0.1220230756870962</v>
       </c>
       <c r="J39" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K39" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L39" t="n">
-        <v>0.002566316183489237</v>
+        <v>0.003967158000719229</v>
       </c>
       <c r="M39" t="n">
-        <v>11.99174915594343</v>
+        <v>12.08140126073647</v>
       </c>
       <c r="N39" t="n">
-        <v>237.0730794649028</v>
+        <v>239.7373421973031</v>
       </c>
       <c r="O39" t="n">
-        <v>15.39717764607861</v>
+        <v>15.48345382003974</v>
       </c>
       <c r="P39" t="n">
-        <v>389.0661841764745</v>
+        <v>388.8361497916237</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -35829,28 +35977,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.06021279995368049</v>
+        <v>0.08634995742592656</v>
       </c>
       <c r="J40" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K40" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L40" t="n">
-        <v>0.000956603808644263</v>
+        <v>0.001949202563599206</v>
       </c>
       <c r="M40" t="n">
-        <v>12.05932503790843</v>
+        <v>12.13266545526904</v>
       </c>
       <c r="N40" t="n">
-        <v>243.1614990995212</v>
+        <v>246.4441518812314</v>
       </c>
       <c r="O40" t="n">
-        <v>15.59363649375992</v>
+        <v>15.69853980092516</v>
       </c>
       <c r="P40" t="n">
-        <v>398.9219390468585</v>
+        <v>398.6743689509287</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -35907,28 +36055,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1647123329377525</v>
+        <v>0.1912263626019931</v>
       </c>
       <c r="J41" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K41" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L41" t="n">
-        <v>0.006571316717096432</v>
+        <v>0.008772696409745429</v>
       </c>
       <c r="M41" t="n">
-        <v>12.92541367420346</v>
+        <v>12.97713273385777</v>
       </c>
       <c r="N41" t="n">
-        <v>263.3913156522252</v>
+        <v>266.7069135396284</v>
       </c>
       <c r="O41" t="n">
-        <v>16.22933503419734</v>
+        <v>16.33116387584267</v>
       </c>
       <c r="P41" t="n">
-        <v>402.6581035383743</v>
+        <v>402.406963724321</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -35985,28 +36133,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3503367475712391</v>
+        <v>0.377837398817891</v>
       </c>
       <c r="J42" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K42" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02659746934407059</v>
+        <v>0.03070048387630231</v>
       </c>
       <c r="M42" t="n">
-        <v>13.26827390674628</v>
+        <v>13.32766838276987</v>
       </c>
       <c r="N42" t="n">
-        <v>283.7308573727195</v>
+        <v>286.1983532533857</v>
       </c>
       <c r="O42" t="n">
-        <v>16.8443123152214</v>
+        <v>16.91739794570624</v>
       </c>
       <c r="P42" t="n">
-        <v>404.7279617571401</v>
+        <v>404.4638065128369</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -36063,28 +36211,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4368937444072186</v>
+        <v>0.4623433629936926</v>
       </c>
       <c r="J43" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K43" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04068944305469357</v>
+        <v>0.04528334186900196</v>
       </c>
       <c r="M43" t="n">
-        <v>13.20536966940118</v>
+        <v>13.27835670977441</v>
       </c>
       <c r="N43" t="n">
-        <v>290.5465752024853</v>
+        <v>292.4699726842384</v>
       </c>
       <c r="O43" t="n">
-        <v>17.04542681197761</v>
+        <v>17.10175349735337</v>
       </c>
       <c r="P43" t="n">
-        <v>406.345197340972</v>
+        <v>406.1053116472337</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -36122,7 +36270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR219"/>
+  <dimension ref="A1:AR220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84093,7 +84241,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>-34.447459333404055,172.67670204000785</t>
+          <t>-34.4474513912219,172.67665289109866</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
@@ -84103,17 +84251,17 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>-34.44600591619507,172.67705074546504</t>
+          <t>-34.44599705903857,172.6769959346703</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>-34.44527575365322,172.67720378296335</t>
+          <t>-34.44526618865985,172.67714459208258</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>-34.44453545010643,172.67729410459836</t>
+          <t>-34.44452821594732,172.67724933787852</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -84133,15 +84281,237 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>-34.441618360981096,172.67768804800798</t>
+          <t>-34.441609312949964,172.67760330029546</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>-34.44088096429031,172.67777823718384</t>
+          <t>-34.44087228513276,172.67769694486284</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-34.46798112837157,172.6642541021114</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>-34.46757528290507,172.66504462439025</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>-34.46709675785763,172.665739955242</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>-34.46657941604428,172.66638444795078</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-34.46604160254163,172.66699968513376</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-34.46548729704238,172.66758736588048</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-34.4646217026099,172.6678097697141</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-34.4643294459525,172.66872049755446</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-34.46397225542382,172.6695539467675</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-34.46339214716822,172.67012207934812</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-34.462500626003475,172.6703195676233</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-34.46182630654237,172.6706726239105</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-34.46126802782611,172.67088934456788</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-34.46065557157578,172.67113418662814</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-34.45998351998405,172.67152096278784</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>-34.459359593635746,172.67206756435502</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>-34.45869205903,172.67246937824655</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>-34.45802886291283,172.6728856179304</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>-34.45735435211086,172.67326430469404</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>-34.45666014574912,172.67357760857513</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>-34.455963776655885,172.67388375006854</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>-34.45526687793599,172.67418815215828</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>-34.45456642997488,172.6744807878556</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>-34.45385281937209,172.67472973489913</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>-34.45313091461886,172.6749511600954</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>-34.45240881939719,172.67517197273008</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>-34.451728793252684,172.6754330796678</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>-34.45105348281835,172.67565635051218</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>-34.45034718540845,172.67588762860132</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>-34.449619219131606,172.6760540224285</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>-34.44889414720037,172.67623836665544</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>-34.448173247225775,172.67644856745926</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>-34.447442672064426,172.67659893415492</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>-34.44671671778111,172.67677793552147</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>-34.445988253653994,172.6769414444182</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>-34.44525448272654,172.67707215272006</t>
+        </is>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>-34.44451481803429,172.677166428652</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>-34.443788441398375,172.6773429733484</t>
+        </is>
+      </c>
+      <c r="AN220" t="inlineStr">
+        <is>
+          <t>-34.44305779226048,172.67739140070086</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>-34.44233486906736,172.67743549831968</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>-34.44160379189324,172.6775515880062</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>-34.440865945740555,172.67763756801241</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0005/nzd0005.xlsx
+++ b/data/nzd0005/nzd0005.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR220"/>
+  <dimension ref="A1:AR221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30577,6 +30577,144 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>378.42</v>
+      </c>
+      <c r="C221" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="D221" t="n">
+        <v>345.83</v>
+      </c>
+      <c r="E221" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="F221" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="G221" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="H221" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="I221" t="n">
+        <v>360.52</v>
+      </c>
+      <c r="J221" t="n">
+        <v>346.66</v>
+      </c>
+      <c r="K221" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="L221" t="n">
+        <v>409.28</v>
+      </c>
+      <c r="M221" t="n">
+        <v>436.14</v>
+      </c>
+      <c r="N221" t="n">
+        <v>454.63</v>
+      </c>
+      <c r="O221" t="n">
+        <v>454.57</v>
+      </c>
+      <c r="P221" t="n">
+        <v>444.73</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>425.44</v>
+      </c>
+      <c r="R221" t="n">
+        <v>413.63</v>
+      </c>
+      <c r="S221" t="n">
+        <v>403.83</v>
+      </c>
+      <c r="T221" t="n">
+        <v>396.9</v>
+      </c>
+      <c r="U221" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="V221" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="W221" t="n">
+        <v>393.44</v>
+      </c>
+      <c r="X221" t="n">
+        <v>394.56</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>400.74</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>410.66</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>419.52</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>420.99</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>414.68</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>416.21</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>413.4</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>410.11</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>411.48</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>410.59</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>411.6</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>412.31</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>421.78</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>423.84</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>433.78</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>440.22</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>440.58</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>443.66</v>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30588,7 +30726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B223"/>
+  <dimension ref="A1:B224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32821,6 +32959,16 @@
       </c>
       <c r="B223" t="n">
         <v>-0.51</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -32989,28 +33137,28 @@
         <v>0.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01379427950629366</v>
+        <v>0.01497362074698534</v>
       </c>
       <c r="J2" t="n">
+        <v>220</v>
+      </c>
+      <c r="K2" t="n">
         <v>219</v>
       </c>
-      <c r="K2" t="n">
-        <v>218</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0001289689679667694</v>
+        <v>0.0001534384798419497</v>
       </c>
       <c r="M2" t="n">
-        <v>7.043242047992839</v>
+        <v>7.017671812032852</v>
       </c>
       <c r="N2" t="n">
-        <v>94.8029660967693</v>
+        <v>94.37922046723541</v>
       </c>
       <c r="O2" t="n">
-        <v>9.736681472492016</v>
+        <v>9.714896832557482</v>
       </c>
       <c r="P2" t="n">
-        <v>376.6220622676236</v>
+        <v>376.6108875064484</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33067,28 +33215,28 @@
         <v>0.0727</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3526189905339779</v>
+        <v>0.3477059331796206</v>
       </c>
       <c r="J3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04917813498783952</v>
+        <v>0.04828221238275499</v>
       </c>
       <c r="M3" t="n">
-        <v>9.478675799941595</v>
+        <v>9.457251372135058</v>
       </c>
       <c r="N3" t="n">
-        <v>155.1768409116526</v>
+        <v>154.6245933910103</v>
       </c>
       <c r="O3" t="n">
-        <v>12.4569996753493</v>
+        <v>12.43481376583543</v>
       </c>
       <c r="P3" t="n">
-        <v>352.264367729229</v>
+        <v>352.3108204049788</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33145,28 +33293,28 @@
         <v>0.0868</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01524966224808513</v>
+        <v>0.009896643812288605</v>
       </c>
       <c r="J4" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000118358559761722</v>
+        <v>5.026836888488706e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>9.248507297739502</v>
+        <v>9.229728668999295</v>
       </c>
       <c r="N4" t="n">
-        <v>127.2647794073128</v>
+        <v>126.8676524069112</v>
       </c>
       <c r="O4" t="n">
-        <v>11.28116923937022</v>
+        <v>11.26355416406878</v>
       </c>
       <c r="P4" t="n">
-        <v>351.880917141332</v>
+        <v>351.931374096586</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33223,28 +33371,28 @@
         <v>0.0726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3862467191610472</v>
+        <v>-0.3914036927583726</v>
       </c>
       <c r="J5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05783078761423466</v>
+        <v>0.05978066823896122</v>
       </c>
       <c r="M5" t="n">
-        <v>10.51754693748892</v>
+        <v>10.48788904255292</v>
       </c>
       <c r="N5" t="n">
-        <v>156.5616259095684</v>
+        <v>156.0145532530195</v>
       </c>
       <c r="O5" t="n">
-        <v>12.51245882748744</v>
+        <v>12.49057857959428</v>
       </c>
       <c r="P5" t="n">
-        <v>356.6708393020002</v>
+        <v>356.7196685538046</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33301,28 +33449,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6491186698991898</v>
+        <v>-0.6540984711621339</v>
       </c>
       <c r="J6" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K6" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1233080815435879</v>
+        <v>0.1259563352725316</v>
       </c>
       <c r="M6" t="n">
-        <v>11.5602439448666</v>
+        <v>11.52499056740261</v>
       </c>
       <c r="N6" t="n">
-        <v>192.1135360810632</v>
+        <v>191.3940239910445</v>
       </c>
       <c r="O6" t="n">
-        <v>13.86050273550939</v>
+        <v>13.83452290435216</v>
       </c>
       <c r="P6" t="n">
-        <v>362.6088357556423</v>
+        <v>362.6560895929334</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33379,28 +33527,28 @@
         <v>0.0851</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6076057237401656</v>
+        <v>-0.6125748214568986</v>
       </c>
       <c r="J7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K7" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09999575163497665</v>
+        <v>0.1023018997803784</v>
       </c>
       <c r="M7" t="n">
-        <v>12.15911325140284</v>
+        <v>12.12352195866669</v>
       </c>
       <c r="N7" t="n">
-        <v>213.0889972158353</v>
+        <v>212.2725728645727</v>
       </c>
       <c r="O7" t="n">
-        <v>14.59756819527949</v>
+        <v>14.56957696244379</v>
       </c>
       <c r="P7" t="n">
-        <v>364.8509377764061</v>
+        <v>364.8980900466657</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33457,28 +33605,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02323445236749181</v>
+        <v>0.03021307446824983</v>
       </c>
       <c r="J8" t="n">
+        <v>220</v>
+      </c>
+      <c r="K8" t="n">
         <v>219</v>
       </c>
-      <c r="K8" t="n">
-        <v>218</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0006447425664635187</v>
+        <v>0.001093991174308306</v>
       </c>
       <c r="M8" t="n">
-        <v>5.452067154956974</v>
+        <v>5.465803848116241</v>
       </c>
       <c r="N8" t="n">
-        <v>53.85139497143246</v>
+        <v>53.92421674260643</v>
       </c>
       <c r="O8" t="n">
-        <v>7.338350970853905</v>
+        <v>7.343311020418952</v>
       </c>
       <c r="P8" t="n">
-        <v>387.8846208544758</v>
+        <v>387.8187192429155</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -33539,28 +33687,28 @@
         <v>0.0851</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3331130699832879</v>
+        <v>-0.3286035648324015</v>
       </c>
       <c r="J9" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1119748499175032</v>
+        <v>0.1100279909096235</v>
       </c>
       <c r="M9" t="n">
-        <v>5.359745318639439</v>
+        <v>5.358969720373913</v>
       </c>
       <c r="N9" t="n">
-        <v>56.83224082515893</v>
+        <v>56.70453290937822</v>
       </c>
       <c r="O9" t="n">
-        <v>7.538716125784212</v>
+        <v>7.530241225178528</v>
       </c>
       <c r="P9" t="n">
-        <v>363.9920976216271</v>
+        <v>363.9496425287188</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -33621,28 +33769,28 @@
         <v>0.0429</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3316069852082126</v>
+        <v>-0.3128420023782161</v>
       </c>
       <c r="J10" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03768109137878561</v>
+        <v>0.03358047615284177</v>
       </c>
       <c r="M10" t="n">
-        <v>10.39580305127685</v>
+        <v>10.44705657871112</v>
       </c>
       <c r="N10" t="n">
-        <v>180.6215789314737</v>
+        <v>182.0993935130764</v>
       </c>
       <c r="O10" t="n">
-        <v>13.43955278018855</v>
+        <v>13.49442082910847</v>
       </c>
       <c r="P10" t="n">
-        <v>332.9667814152327</v>
+        <v>332.7887454844284</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33703,28 +33851,28 @@
         <v>0.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1810595651831793</v>
+        <v>-0.1661626868224519</v>
       </c>
       <c r="J11" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K11" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002171495600345574</v>
+        <v>0.001844478726529597</v>
       </c>
       <c r="M11" t="n">
-        <v>23.68596013035511</v>
+        <v>23.65528264613734</v>
       </c>
       <c r="N11" t="n">
-        <v>988.0372216465204</v>
+        <v>984.833579718515</v>
       </c>
       <c r="O11" t="n">
-        <v>31.43305937459032</v>
+        <v>31.38205824541333</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2518689808821</v>
+        <v>343.1110451223719</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33785,28 +33933,28 @@
         <v>0.0293</v>
       </c>
       <c r="I12" t="n">
-        <v>0.822801834989809</v>
+        <v>0.8350010490880814</v>
       </c>
       <c r="J12" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05409134510672475</v>
+        <v>0.05606461394672735</v>
       </c>
       <c r="M12" t="n">
-        <v>20.71757515946306</v>
+        <v>20.68829088805732</v>
       </c>
       <c r="N12" t="n">
-        <v>774.6032587743371</v>
+        <v>771.9967820017559</v>
       </c>
       <c r="O12" t="n">
-        <v>27.83169521919815</v>
+        <v>27.78483006969371</v>
       </c>
       <c r="P12" t="n">
-        <v>372.5712782965227</v>
+        <v>372.4568687832936</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -33867,28 +34015,28 @@
         <v>0.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5302923552476</v>
+        <v>1.533975834776636</v>
       </c>
       <c r="J13" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3063584425354694</v>
+        <v>0.3094294942849</v>
       </c>
       <c r="M13" t="n">
-        <v>13.93381559658519</v>
+        <v>13.89163936345362</v>
       </c>
       <c r="N13" t="n">
-        <v>346.7964163164395</v>
+        <v>345.2658605773706</v>
       </c>
       <c r="O13" t="n">
-        <v>18.62247073608761</v>
+        <v>18.5813309689422</v>
       </c>
       <c r="P13" t="n">
-        <v>390.8615548438289</v>
+        <v>390.8270495253126</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -33949,28 +34097,28 @@
         <v>0.0384</v>
       </c>
       <c r="I14" t="n">
-        <v>1.642204909933318</v>
+        <v>1.647539086062999</v>
       </c>
       <c r="J14" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4132586112599123</v>
+        <v>0.4170333654276198</v>
       </c>
       <c r="M14" t="n">
-        <v>12.01703202772874</v>
+        <v>11.99416292212842</v>
       </c>
       <c r="N14" t="n">
-        <v>247.414806568423</v>
+        <v>246.4671402750303</v>
       </c>
       <c r="O14" t="n">
-        <v>15.72942486451501</v>
+        <v>15.69927196640119</v>
       </c>
       <c r="P14" t="n">
-        <v>404.3483546539396</v>
+        <v>404.2980621339884</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34027,28 +34175,28 @@
         <v>0.0372</v>
       </c>
       <c r="I15" t="n">
-        <v>1.873924172794476</v>
+        <v>1.87934485622426</v>
       </c>
       <c r="J15" t="n">
+        <v>220</v>
+      </c>
+      <c r="K15" t="n">
         <v>219</v>
       </c>
-      <c r="K15" t="n">
-        <v>218</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5004770921453283</v>
+        <v>0.5041665714159076</v>
       </c>
       <c r="M15" t="n">
-        <v>11.4219249803009</v>
+        <v>11.40065974269756</v>
       </c>
       <c r="N15" t="n">
-        <v>225.5660587005901</v>
+        <v>224.7283752744294</v>
       </c>
       <c r="O15" t="n">
-        <v>15.01885677075955</v>
+        <v>14.99094310823803</v>
       </c>
       <c r="P15" t="n">
-        <v>398.0023675507686</v>
+        <v>397.9511781084083</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34105,28 +34253,28 @@
         <v>0.0318</v>
       </c>
       <c r="I16" t="n">
-        <v>1.837710252039679</v>
+        <v>1.835684729022596</v>
       </c>
       <c r="J16" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K16" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5091898568880514</v>
+        <v>0.511045756776199</v>
       </c>
       <c r="M16" t="n">
-        <v>11.0687624538907</v>
+        <v>11.02755134708261</v>
       </c>
       <c r="N16" t="n">
-        <v>212.1041654327321</v>
+        <v>211.1450243401531</v>
       </c>
       <c r="O16" t="n">
-        <v>14.56379639492162</v>
+        <v>14.53083013252006</v>
       </c>
       <c r="P16" t="n">
-        <v>398.1116059328301</v>
+        <v>398.130683514203</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34183,28 +34331,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>1.674596722116738</v>
+        <v>1.661627728524536</v>
       </c>
       <c r="J17" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K17" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3892374746097345</v>
+        <v>0.38692699868281</v>
       </c>
       <c r="M17" t="n">
-        <v>13.99812772537186</v>
+        <v>13.9997790811199</v>
       </c>
       <c r="N17" t="n">
-        <v>288.0025641770137</v>
+        <v>287.7859052851384</v>
       </c>
       <c r="O17" t="n">
-        <v>16.97063829609876</v>
+        <v>16.96425374972735</v>
       </c>
       <c r="P17" t="n">
-        <v>396.3846994958816</v>
+        <v>396.5065737817148</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34261,28 +34409,28 @@
         <v>0.0441</v>
       </c>
       <c r="I18" t="n">
-        <v>1.596501627892762</v>
+        <v>1.582592968326489</v>
       </c>
       <c r="J18" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K18" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3389176593561224</v>
+        <v>0.3363136984253772</v>
       </c>
       <c r="M18" t="n">
-        <v>14.40301809510892</v>
+        <v>14.40615567110096</v>
       </c>
       <c r="N18" t="n">
-        <v>321.3854628360696</v>
+        <v>321.1841296573115</v>
       </c>
       <c r="O18" t="n">
-        <v>17.92722685849849</v>
+        <v>17.92161068814161</v>
       </c>
       <c r="P18" t="n">
-        <v>387.785786075796</v>
+        <v>387.9168443688189</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34339,28 +34487,28 @@
         <v>0.0561</v>
       </c>
       <c r="I19" t="n">
-        <v>1.211812936882152</v>
+        <v>1.198369368086939</v>
       </c>
       <c r="J19" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K19" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2418212229550649</v>
+        <v>0.2387992895659353</v>
       </c>
       <c r="M19" t="n">
-        <v>14.53182931974137</v>
+        <v>14.53150882509322</v>
       </c>
       <c r="N19" t="n">
-        <v>298.3402535494919</v>
+        <v>298.1500227374738</v>
       </c>
       <c r="O19" t="n">
-        <v>17.27252886955155</v>
+        <v>17.2670212468009</v>
       </c>
       <c r="P19" t="n">
-        <v>387.6392894537584</v>
+        <v>387.766461987236</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34417,28 +34565,28 @@
         <v>0.0674</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8240469211954923</v>
+        <v>0.8121680944300852</v>
       </c>
       <c r="J20" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K20" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L20" t="n">
-        <v>0.118852960012969</v>
+        <v>0.1165615607046537</v>
       </c>
       <c r="M20" t="n">
-        <v>15.40831293987833</v>
+        <v>15.38802663125267</v>
       </c>
       <c r="N20" t="n">
-        <v>322.8468618548657</v>
+        <v>322.2862516040649</v>
       </c>
       <c r="O20" t="n">
-        <v>17.96793983334944</v>
+        <v>17.95233276218065</v>
       </c>
       <c r="P20" t="n">
-        <v>389.1692077300011</v>
+        <v>389.2819271172903</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34495,28 +34643,28 @@
         <v>0.0735</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3037452664754938</v>
+        <v>0.2990921714247327</v>
       </c>
       <c r="J21" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K21" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02090176259637266</v>
+        <v>0.02046617229619163</v>
       </c>
       <c r="M21" t="n">
-        <v>13.50937342644555</v>
+        <v>13.4630892589155</v>
       </c>
       <c r="N21" t="n">
-        <v>274.9808524478826</v>
+        <v>273.8589557465797</v>
       </c>
       <c r="O21" t="n">
-        <v>16.58254662130888</v>
+        <v>16.54868441135366</v>
       </c>
       <c r="P21" t="n">
-        <v>392.3919962770424</v>
+        <v>392.4363978068597</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34573,28 +34721,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02678769996207939</v>
+        <v>0.0268447202390091</v>
       </c>
       <c r="J22" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K22" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001901482162423029</v>
+        <v>0.0001928540216676877</v>
       </c>
       <c r="M22" t="n">
-        <v>12.31290620984809</v>
+        <v>12.25679663528176</v>
       </c>
       <c r="N22" t="n">
-        <v>240.0689906716855</v>
+        <v>238.967777715333</v>
       </c>
       <c r="O22" t="n">
-        <v>15.49415988918681</v>
+        <v>15.45858265544849</v>
       </c>
       <c r="P22" t="n">
-        <v>393.2467167562543</v>
+        <v>393.2461726479783</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34651,28 +34799,28 @@
         <v>0.0708</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1247517073389631</v>
+        <v>-0.1220939392348891</v>
       </c>
       <c r="J23" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K23" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005303036102387249</v>
+        <v>0.005129122758040561</v>
       </c>
       <c r="M23" t="n">
-        <v>10.85834734846034</v>
+        <v>10.82525905231281</v>
       </c>
       <c r="N23" t="n">
-        <v>187.211525637098</v>
+        <v>186.4068156090927</v>
       </c>
       <c r="O23" t="n">
-        <v>13.68252628855863</v>
+        <v>13.65308813452446</v>
       </c>
       <c r="P23" t="n">
-        <v>393.5592076373145</v>
+        <v>393.5340332388104</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34729,28 +34877,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.202276826198121</v>
+        <v>-0.1969792913127624</v>
       </c>
       <c r="J24" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K24" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01463479610515683</v>
+        <v>0.01400918338632462</v>
       </c>
       <c r="M24" t="n">
-        <v>10.8275546465937</v>
+        <v>10.80975047882329</v>
       </c>
       <c r="N24" t="n">
-        <v>176.6754414684104</v>
+        <v>176.0561261479494</v>
       </c>
       <c r="O24" t="n">
-        <v>13.29193144236045</v>
+        <v>13.26861432659603</v>
       </c>
       <c r="P24" t="n">
-        <v>393.5517489577747</v>
+        <v>393.5015706694247</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34807,28 +34955,28 @@
         <v>0.0713</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1003128797074534</v>
+        <v>-0.09094541822202108</v>
       </c>
       <c r="J25" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K25" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004188797560956581</v>
+        <v>0.003466385681592521</v>
       </c>
       <c r="M25" t="n">
-        <v>10.20166450076367</v>
+        <v>10.19960290812118</v>
       </c>
       <c r="N25" t="n">
-        <v>153.4173261620025</v>
+        <v>153.2945342126251</v>
       </c>
       <c r="O25" t="n">
-        <v>12.3861747994287</v>
+        <v>12.38121699238912</v>
       </c>
       <c r="P25" t="n">
-        <v>392.0931640428503</v>
+        <v>392.0044353806148</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34885,28 +35033,28 @@
         <v>0.0665</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1175502481912824</v>
+        <v>-0.1022048577955626</v>
       </c>
       <c r="J26" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K26" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005759500188482036</v>
+        <v>0.004358852205709085</v>
       </c>
       <c r="M26" t="n">
-        <v>10.21300235866754</v>
+        <v>10.2201902694319</v>
       </c>
       <c r="N26" t="n">
-        <v>152.9773493791197</v>
+        <v>153.8238654029004</v>
       </c>
       <c r="O26" t="n">
-        <v>12.36840124588137</v>
+        <v>12.40257495050525</v>
       </c>
       <c r="P26" t="n">
-        <v>395.249451207069</v>
+        <v>395.1040995594096</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34963,28 +35111,28 @@
         <v>0.0655</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1888315821839885</v>
+        <v>0.2066827143274876</v>
       </c>
       <c r="J27" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K27" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01478841890743532</v>
+        <v>0.01759696753714901</v>
       </c>
       <c r="M27" t="n">
-        <v>10.05432034999506</v>
+        <v>10.08575849277227</v>
       </c>
       <c r="N27" t="n">
-        <v>152.6670223320605</v>
+        <v>154.0591697841938</v>
       </c>
       <c r="O27" t="n">
-        <v>12.35584972116692</v>
+        <v>12.4120574355823</v>
       </c>
       <c r="P27" t="n">
-        <v>392.9965853786542</v>
+        <v>392.8269211099523</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35041,28 +35189,28 @@
         <v>0.0641</v>
       </c>
       <c r="I28" t="n">
-        <v>0.423385259384964</v>
+        <v>0.4412707517295714</v>
       </c>
       <c r="J28" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K28" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06731647872840008</v>
+        <v>0.07247098735904889</v>
       </c>
       <c r="M28" t="n">
-        <v>10.11076113073814</v>
+        <v>10.14373247985055</v>
       </c>
       <c r="N28" t="n">
-        <v>159.9366867093522</v>
+        <v>161.3087642263166</v>
       </c>
       <c r="O28" t="n">
-        <v>12.6466077154845</v>
+        <v>12.70073872758261</v>
       </c>
       <c r="P28" t="n">
-        <v>390.978968005863</v>
+        <v>390.8089106252262</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35119,28 +35267,28 @@
         <v>0.0631</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6670167599536967</v>
+        <v>0.6853425618472728</v>
       </c>
       <c r="J29" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K29" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1448361985078762</v>
+        <v>0.15124884039411</v>
       </c>
       <c r="M29" t="n">
-        <v>10.60430574501257</v>
+        <v>10.64286738588459</v>
       </c>
       <c r="N29" t="n">
-        <v>169.9227359693983</v>
+        <v>171.3625971970521</v>
       </c>
       <c r="O29" t="n">
-        <v>13.03544153335046</v>
+        <v>13.09055373913007</v>
       </c>
       <c r="P29" t="n">
-        <v>381.1241146211763</v>
+        <v>380.9502508985254</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -35197,28 +35345,28 @@
         <v>0.0589</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6977231152014436</v>
+        <v>0.7170388280698429</v>
       </c>
       <c r="J30" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K30" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1479437381108445</v>
+        <v>0.1544699277086897</v>
       </c>
       <c r="M30" t="n">
-        <v>10.89841824551641</v>
+        <v>10.93638284770643</v>
       </c>
       <c r="N30" t="n">
-        <v>179.5439023951218</v>
+        <v>181.1596341106647</v>
       </c>
       <c r="O30" t="n">
-        <v>13.39939932963869</v>
+        <v>13.45955549454233</v>
       </c>
       <c r="P30" t="n">
-        <v>372.8218377926288</v>
+        <v>372.6380758382869</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -35275,28 +35423,28 @@
         <v>0.0567</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6316362523120087</v>
+        <v>0.6575771859750759</v>
       </c>
       <c r="J31" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K31" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L31" t="n">
-        <v>0.10588854319987</v>
+        <v>0.1127051745116104</v>
       </c>
       <c r="M31" t="n">
-        <v>11.89119393945357</v>
+        <v>11.97033085075254</v>
       </c>
       <c r="N31" t="n">
-        <v>213.9746542807502</v>
+        <v>217.3528722876224</v>
       </c>
       <c r="O31" t="n">
-        <v>14.62787251382614</v>
+        <v>14.74289226331192</v>
       </c>
       <c r="P31" t="n">
-        <v>368.2937927189369</v>
+        <v>368.0452614193824</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -35353,28 +35501,28 @@
         <v>0.0509</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5136712366173428</v>
+        <v>0.5405120742042876</v>
       </c>
       <c r="J32" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K32" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06029940603717621</v>
+        <v>0.06584373937026711</v>
       </c>
       <c r="M32" t="n">
-        <v>12.34755731971548</v>
+        <v>12.41004415669298</v>
       </c>
       <c r="N32" t="n">
-        <v>261.1755473013039</v>
+        <v>264.6449781302233</v>
       </c>
       <c r="O32" t="n">
-        <v>16.16092656072986</v>
+        <v>16.26791253142896</v>
       </c>
       <c r="P32" t="n">
-        <v>367.5547703587563</v>
+        <v>367.2976173844934</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -35431,28 +35579,28 @@
         <v>0.044</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4130190018312261</v>
+        <v>0.4381033681469493</v>
       </c>
       <c r="J33" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K33" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L33" t="n">
-        <v>0.06159516461158843</v>
+        <v>0.06785373893862789</v>
       </c>
       <c r="M33" t="n">
-        <v>10.15396105621306</v>
+        <v>10.2397041363676</v>
       </c>
       <c r="N33" t="n">
-        <v>165.4020178593759</v>
+        <v>168.6847495776759</v>
       </c>
       <c r="O33" t="n">
-        <v>12.86087158241524</v>
+        <v>12.98786932401446</v>
       </c>
       <c r="P33" t="n">
-        <v>369.4056455524168</v>
+        <v>369.1648669910242</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -35509,28 +35657,28 @@
         <v>0.0439</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3896135577518814</v>
+        <v>0.4198313154915324</v>
       </c>
       <c r="J34" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K34" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L34" t="n">
-        <v>0.03759488058791249</v>
+        <v>0.04281582410088969</v>
       </c>
       <c r="M34" t="n">
-        <v>12.4287550807326</v>
+        <v>12.50889477073242</v>
       </c>
       <c r="N34" t="n">
-        <v>248.8887262903929</v>
+        <v>253.6943937892955</v>
       </c>
       <c r="O34" t="n">
-        <v>15.77620760165107</v>
+        <v>15.92778684529949</v>
       </c>
       <c r="P34" t="n">
-        <v>364.8802190711381</v>
+        <v>364.5926422897869</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -35587,28 +35735,28 @@
         <v>0.0424</v>
       </c>
       <c r="I35" t="n">
-        <v>0.06005995131308317</v>
+        <v>0.09215813854687852</v>
       </c>
       <c r="J35" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K35" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0008529162200950902</v>
+        <v>0.001976461671561514</v>
       </c>
       <c r="M35" t="n">
-        <v>12.89114564882066</v>
+        <v>13.00503225903479</v>
       </c>
       <c r="N35" t="n">
-        <v>270.6455504756088</v>
+        <v>276.114862144826</v>
       </c>
       <c r="O35" t="n">
-        <v>16.45130847305493</v>
+        <v>16.6167043105673</v>
       </c>
       <c r="P35" t="n">
-        <v>370.5363778610038</v>
+        <v>370.2309053818267</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -35665,28 +35813,28 @@
         <v>0.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2842536447141882</v>
+        <v>0.3132404117322332</v>
       </c>
       <c r="J36" t="n">
+        <v>220</v>
+      </c>
+      <c r="K36" t="n">
         <v>219</v>
       </c>
-      <c r="K36" t="n">
-        <v>218</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.01738693472002084</v>
+        <v>0.02085353395521961</v>
       </c>
       <c r="M36" t="n">
-        <v>12.90229707767209</v>
+        <v>13.01723015062972</v>
       </c>
       <c r="N36" t="n">
-        <v>291.1282757944304</v>
+        <v>295.2624834238729</v>
       </c>
       <c r="O36" t="n">
-        <v>17.06248152510151</v>
+        <v>17.18320352623087</v>
       </c>
       <c r="P36" t="n">
-        <v>369.1713836745828</v>
+        <v>368.8950288431378</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -35743,28 +35891,28 @@
         <v>0.0331</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3475347554766827</v>
+        <v>0.3699459289473063</v>
       </c>
       <c r="J37" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K37" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03409767812659525</v>
+        <v>0.03828196025256325</v>
       </c>
       <c r="M37" t="n">
-        <v>11.13765623277438</v>
+        <v>11.22189651468404</v>
       </c>
       <c r="N37" t="n">
-        <v>221.4674668932188</v>
+        <v>223.7225103198151</v>
       </c>
       <c r="O37" t="n">
-        <v>14.8817830549037</v>
+        <v>14.95735639475823</v>
       </c>
       <c r="P37" t="n">
-        <v>376.2618783330814</v>
+        <v>376.0505011919406</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -35821,28 +35969,28 @@
         <v>0.036</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09481860070887557</v>
+        <v>0.1303974647358767</v>
       </c>
       <c r="J38" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K38" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L38" t="n">
-        <v>0.001676666850112141</v>
+        <v>0.003122210207859299</v>
       </c>
       <c r="M38" t="n">
-        <v>13.91142772902197</v>
+        <v>14.06001337005468</v>
       </c>
       <c r="N38" t="n">
-        <v>342.6094107688524</v>
+        <v>349.2682580650205</v>
       </c>
       <c r="O38" t="n">
-        <v>18.50971125568555</v>
+        <v>18.6887200756237</v>
       </c>
       <c r="P38" t="n">
-        <v>376.7422732533578</v>
+        <v>376.4029511172237</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -35899,28 +36047,28 @@
         <v>0.0363</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1220230756870962</v>
+        <v>0.1487706107557658</v>
       </c>
       <c r="J39" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K39" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L39" t="n">
-        <v>0.003967158000719229</v>
+        <v>0.005830973760246883</v>
       </c>
       <c r="M39" t="n">
-        <v>12.08140126073647</v>
+        <v>12.19114846668357</v>
       </c>
       <c r="N39" t="n">
-        <v>239.7373421973031</v>
+        <v>243.2595678615833</v>
       </c>
       <c r="O39" t="n">
-        <v>15.48345382003974</v>
+        <v>15.59678068902629</v>
       </c>
       <c r="P39" t="n">
-        <v>388.8361497916237</v>
+        <v>388.5812192854329</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -35977,28 +36125,28 @@
         <v>0.0359</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08634995742592656</v>
+        <v>0.1139755282963341</v>
       </c>
       <c r="J40" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K40" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="n">
-        <v>0.001949202563599206</v>
+        <v>0.003356260633727404</v>
       </c>
       <c r="M40" t="n">
-        <v>12.13266545526904</v>
+        <v>12.21545575849201</v>
       </c>
       <c r="N40" t="n">
-        <v>246.4441518812314</v>
+        <v>250.2829826052414</v>
       </c>
       <c r="O40" t="n">
-        <v>15.69853980092516</v>
+        <v>15.82033446565658</v>
       </c>
       <c r="P40" t="n">
-        <v>398.6743689509287</v>
+        <v>398.4115388052502</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
@@ -36055,28 +36203,28 @@
         <v>0.0393</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1912263626019931</v>
+        <v>0.2187750235348583</v>
       </c>
       <c r="J41" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K41" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L41" t="n">
-        <v>0.008772696409745429</v>
+        <v>0.01135318945127983</v>
       </c>
       <c r="M41" t="n">
-        <v>12.97713273385777</v>
+        <v>13.03873618013773</v>
       </c>
       <c r="N41" t="n">
-        <v>266.7069135396284</v>
+        <v>270.4223565809783</v>
       </c>
       <c r="O41" t="n">
-        <v>16.33116387584267</v>
+        <v>16.44452360456144</v>
       </c>
       <c r="P41" t="n">
-        <v>402.406963724321</v>
+        <v>402.1448653010812</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
@@ -36133,28 +36281,28 @@
         <v>0.0397</v>
       </c>
       <c r="I42" t="n">
-        <v>0.377837398817891</v>
+        <v>0.4002399976706835</v>
       </c>
       <c r="J42" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K42" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L42" t="n">
-        <v>0.03070048387630231</v>
+        <v>0.03428174712253029</v>
       </c>
       <c r="M42" t="n">
-        <v>13.32766838276987</v>
+        <v>13.36290336768795</v>
       </c>
       <c r="N42" t="n">
-        <v>286.1983532533857</v>
+        <v>288.021827746686</v>
       </c>
       <c r="O42" t="n">
-        <v>16.91739794570624</v>
+        <v>16.97120584244638</v>
       </c>
       <c r="P42" t="n">
-        <v>404.4638065128369</v>
+        <v>404.2474417431487</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -36211,28 +36359,28 @@
         <v>0.0312</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4623433629936926</v>
+        <v>0.4835859682554057</v>
       </c>
       <c r="J43" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K43" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04528334186900196</v>
+        <v>0.04931670647579589</v>
       </c>
       <c r="M43" t="n">
-        <v>13.27835670977441</v>
+        <v>13.3333720643036</v>
       </c>
       <c r="N43" t="n">
-        <v>292.4699726842384</v>
+        <v>294.0531803381017</v>
       </c>
       <c r="O43" t="n">
-        <v>17.10175349735337</v>
+        <v>17.14797889951179</v>
       </c>
       <c r="P43" t="n">
-        <v>406.1053116472337</v>
+        <v>405.903957626785</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -36270,7 +36418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR220"/>
+  <dimension ref="A1:AR221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84517,6 +84665,228 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-34.46798534586986,172.6642596262312</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>-34.46757876690424,172.66504918779574</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>-34.46709412959075,172.6657365126775</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-34.46658357235432,172.66638989199484</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-34.466044617366414,172.66700358580994</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-34.46548836950798,172.66758868857917</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-34.4646217026099,172.6678097697141</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-34.46433484061565,172.66872691834712</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-34.46390321695263,172.6694717758247</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-34.46332066849818,172.67003700405002</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-34.462459781041495,172.67027095367592</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-34.46181319613628,172.6706536422395</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-34.46125977107181,172.6708697402637</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-34.460654030852155,172.67112907047198</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-34.45998786479065,172.6715353902487</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>-34.45935081167912,172.6720384026401</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>-34.45869070323042,172.67246487611752</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>-34.458024394973705,172.67287078146967</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>-34.457349237128334,172.67324731962395</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>-34.45665872835247,172.67357290190404</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>-34.45596503998073,172.6738879451134</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>-34.45527032895096,172.67419961170663</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>-34.454570343159624,172.67449378206555</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>-34.45385476055095,172.67473618079433</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>-34.45312764851774,172.67494031471017</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>-34.45240379701144,172.67515529552904</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>-34.451722040109665,172.67540608793686</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>-34.45104928468631,172.6756331656058</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>-34.45034406024261,172.67586828893042</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>-34.44961410838964,172.67602239538945</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>-34.448891643644494,172.6762228738096</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>-34.44817000126073,172.67642848034976</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>-34.447440306665136,172.67658429633255</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>-34.446714507786616,172.67676425942273</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>-34.445985422113424,172.67692392206507</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>-34.4452568480882,172.6770867901707</t>
+        </is>
+      </c>
+      <c r="AL221" t="inlineStr">
+        <is>
+          <t>-34.44451314329122,172.67715606500056</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>-34.44378222588999,172.6773045106378</t>
+        </is>
+      </c>
+      <c r="AN221" t="inlineStr">
+        <is>
+          <t>-34.44305416237242,172.67736520433334</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>-34.44233256478078,172.6774147845331</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>-34.441600795068325,172.67752351870806</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>-34.44086230345856,172.6776034533171</t>
+        </is>
+      </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
